--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.64</v>
+        <v>0.51</v>
       </c>
       <c r="L2" t="n">
-        <v>13.22</v>
+        <v>13.28</v>
       </c>
       <c r="M2" t="n">
-        <v>11.56</v>
+        <v>11.62</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>89.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I3" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.62</v>
+        <v>-1.25</v>
       </c>
       <c r="L3" t="n">
-        <v>29.68</v>
+        <v>28.22</v>
       </c>
       <c r="M3" t="n">
-        <v>22.55</v>
+        <v>22.67</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,30 +774,30 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.7</v>
+        <v>83.2</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8.08</v>
+        <v>12.97</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>49.87</v>
       </c>
       <c r="M4" t="n">
-        <v>30.17</v>
+        <v>30.38</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>84.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>46.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-8.699999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>52.5</v>
+        <v>9.76</v>
       </c>
       <c r="M5" t="n">
-        <v>38.91</v>
+        <v>14.63</v>
       </c>
       <c r="N5" t="n">
-        <v>-23.17</v>
+        <v>-10.32</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>68.8</v>
+        <v>67.5</v>
       </c>
       <c r="I6" t="n">
-        <v>89.2</v>
+        <v>45.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,66 +1001,66 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.83</v>
+        <v>-17.97</v>
       </c>
       <c r="L6" t="n">
-        <v>5.51</v>
+        <v>44.36</v>
       </c>
       <c r="M6" t="n">
-        <v>14.57</v>
+        <v>39.34</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.32</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>53.3</v>
+        <v>55.4</v>
       </c>
       <c r="I7" t="n">
-        <v>94.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.26</v>
+        <v>-1.41</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.86</v>
+        <v>-1.34</v>
       </c>
       <c r="M7" t="n">
         <v>11.48</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.36</v>
+        <v>-7.4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>48.3</v>
+        <v>46.2</v>
       </c>
       <c r="I8" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.42</v>
+        <v>-3.07</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>17.93</v>
+        <v>17.96</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.3</v>
+        <v>58.5</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>50.1</v>
+        <v>31.9</v>
       </c>
       <c r="I9" t="n">
-        <v>64.7</v>
+        <v>62.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.08</v>
+        <v>-5.06</v>
       </c>
       <c r="L9" t="n">
-        <v>-13.07</v>
+        <v>-17.19</v>
       </c>
       <c r="M9" t="n">
-        <v>25.86</v>
+        <v>26.35</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.8</v>
+        <v>58.5</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>32.8</v>
+        <v>41.8</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-3.87</v>
+        <v>0.48</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.01</v>
+        <v>-12.54</v>
       </c>
       <c r="M10" t="n">
-        <v>26.36</v>
+        <v>25.93</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>38.9</v>
+        <v>26.6</v>
       </c>
       <c r="I12" t="n">
-        <v>26.1</v>
+        <v>59.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.76</v>
+        <v>-16.52</v>
       </c>
       <c r="L12" t="n">
-        <v>-17.42</v>
+        <v>-5.06</v>
       </c>
       <c r="M12" t="n">
-        <v>46.78</v>
+        <v>27.88</v>
       </c>
       <c r="N12" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.9</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>30.7</v>
+        <v>25.6</v>
       </c>
       <c r="I13" t="n">
-        <v>59.4</v>
+        <v>26.1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-14.4</v>
+        <v>-11.15</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.83</v>
+        <v>-15.74</v>
       </c>
       <c r="M13" t="n">
-        <v>27.78</v>
+        <v>46.78</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="L2" t="n">
-        <v>13.28</v>
+        <v>13.23</v>
       </c>
       <c r="M2" t="n">
         <v>11.62</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>84.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.25</v>
+        <v>-0.83</v>
       </c>
       <c r="L3" t="n">
-        <v>28.22</v>
+        <v>28.76</v>
       </c>
       <c r="M3" t="n">
-        <v>22.67</v>
+        <v>22.63</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>59.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12.97</v>
+        <v>16.8</v>
       </c>
       <c r="L4" t="n">
-        <v>49.87</v>
+        <v>54.94</v>
       </c>
       <c r="M4" t="n">
-        <v>30.38</v>
+        <v>30.94</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>76.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="I5" t="n">
         <v>89.09999999999999</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.369999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="L5" t="n">
-        <v>9.76</v>
+        <v>9.58</v>
       </c>
       <c r="M5" t="n">
-        <v>14.63</v>
+        <v>14.61</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>67.5</v>
+        <v>68</v>
       </c>
       <c r="I6" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-17.97</v>
+        <v>-17.78</v>
       </c>
       <c r="L6" t="n">
-        <v>44.36</v>
+        <v>44.7</v>
       </c>
       <c r="M6" t="n">
-        <v>39.34</v>
+        <v>39.31</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>55.4</v>
+        <v>54.1</v>
       </c>
       <c r="I7" t="n">
         <v>94.8</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.41</v>
+        <v>-2.05</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.34</v>
+        <v>-1.99</v>
       </c>
       <c r="M7" t="n">
-        <v>11.48</v>
+        <v>11.47</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.4</v>
+        <v>-7.47</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="I8" t="n">
         <v>77.2</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.07</v>
+        <v>-2.8</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.23</v>
+        <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>17.96</v>
+        <v>17.95</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>58.5</v>
+        <v>61.4</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>31.9</v>
+        <v>50.5</v>
       </c>
       <c r="I9" t="n">
-        <v>62.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-5.06</v>
+        <v>0.85</v>
       </c>
       <c r="L9" t="n">
-        <v>-17.19</v>
+        <v>-12.21</v>
       </c>
       <c r="M9" t="n">
-        <v>26.35</v>
+        <v>25.9</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.5</v>
+        <v>58.9</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>41.8</v>
+        <v>32.9</v>
       </c>
       <c r="I10" t="n">
-        <v>64.59999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.48</v>
+        <v>-4.53</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.54</v>
+        <v>-16.73</v>
       </c>
       <c r="M10" t="n">
-        <v>25.93</v>
+        <v>26.36</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="I12" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-16.52</v>
+        <v>-16.73</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.06</v>
+        <v>-5.3</v>
       </c>
       <c r="M12" t="n">
-        <v>27.88</v>
+        <v>27.9</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>47.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>25.6</v>
+        <v>26.6</v>
       </c>
       <c r="I13" t="n">
         <v>26.1</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.15</v>
+        <v>-10.62</v>
       </c>
       <c r="L13" t="n">
-        <v>-15.74</v>
+        <v>-15.25</v>
       </c>
       <c r="M13" t="n">
-        <v>46.78</v>
+        <v>46.73</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.5</v>
+        <v>88.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>75.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>1.35</v>
       </c>
       <c r="L2" t="n">
-        <v>13.23</v>
+        <v>12.9</v>
       </c>
       <c r="M2" t="n">
-        <v>11.62</v>
+        <v>11.63</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>85.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-0.83</v>
+        <v>2.34</v>
       </c>
       <c r="L3" t="n">
-        <v>28.76</v>
+        <v>30.16</v>
       </c>
       <c r="M3" t="n">
-        <v>22.63</v>
+        <v>22.62</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>75.7</v>
+        <v>83.8</v>
       </c>
       <c r="I5" t="n">
-        <v>89.09999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.18</v>
+        <v>-9.68</v>
       </c>
       <c r="L5" t="n">
-        <v>9.58</v>
+        <v>53.41</v>
       </c>
       <c r="M5" t="n">
-        <v>14.61</v>
+        <v>39.05</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.32</v>
+        <v>-23.17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>68</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>45.6</v>
+        <v>89.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,66 +1001,66 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-17.78</v>
+        <v>5.49</v>
       </c>
       <c r="L6" t="n">
-        <v>44.7</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
-        <v>39.31</v>
+        <v>14.5</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.32</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>54.1</v>
+        <v>53.8</v>
       </c>
       <c r="I7" t="n">
         <v>94.8</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.05</v>
+        <v>-1.59</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.99</v>
+        <v>-3.21</v>
       </c>
       <c r="M7" t="n">
-        <v>11.47</v>
+        <v>11.49</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.47</v>
+        <v>-7.4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.4</v>
+        <v>60.9</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
         <v>64.59999999999999</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.85</v>
+        <v>0.22</v>
       </c>
       <c r="L9" t="n">
-        <v>-12.21</v>
+        <v>-13.17</v>
       </c>
       <c r="M9" t="n">
-        <v>25.9</v>
+        <v>25.92</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.3</v>
+        <v>51.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>26.2</v>
+        <v>31.4</v>
       </c>
       <c r="I12" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-16.73</v>
+        <v>-13.37</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.3</v>
+        <v>-3.71</v>
       </c>
       <c r="M12" t="n">
-        <v>27.9</v>
+        <v>27.85</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,27 +568,27 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.8</v>
+        <v>85.7</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>76.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.35</v>
+        <v>0.25</v>
       </c>
       <c r="L2" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
         <v>11.63</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.2</v>
+        <v>83.5</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>89.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.34</v>
+        <v>-1.01</v>
       </c>
       <c r="L3" t="n">
-        <v>30.16</v>
+        <v>28.53</v>
       </c>
       <c r="M3" t="n">
-        <v>22.62</v>
+        <v>22.65</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="L4" t="n">
-        <v>54.94</v>
+        <v>54.02</v>
       </c>
       <c r="M4" t="n">
-        <v>30.94</v>
+        <v>30.8</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79</v>
+        <v>79.3</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>83.8</v>
+        <v>76</v>
       </c>
       <c r="I5" t="n">
-        <v>45.9</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-9.68</v>
+        <v>9.35</v>
       </c>
       <c r="L5" t="n">
-        <v>53.41</v>
+        <v>9.74</v>
       </c>
       <c r="M5" t="n">
-        <v>39.05</v>
+        <v>14.63</v>
       </c>
       <c r="N5" t="n">
-        <v>-23.17</v>
+        <v>-10.32</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.8</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>68.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="I6" t="n">
-        <v>89.3</v>
+        <v>45.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,66 +1001,66 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.49</v>
+        <v>-17.26</v>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>45.6</v>
       </c>
       <c r="M6" t="n">
-        <v>14.5</v>
+        <v>39.23</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.32</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>70.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>53.8</v>
+        <v>45.9</v>
       </c>
       <c r="I7" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.59</v>
+        <v>-2.16</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.21</v>
+        <v>-2.09</v>
       </c>
       <c r="M7" t="n">
-        <v>11.49</v>
+        <v>11.47</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.4</v>
+        <v>-7.57</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.3</v>
+        <v>63.4</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>46.7</v>
+        <v>44</v>
       </c>
       <c r="I8" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-2.8</v>
+        <v>-4.18</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05</v>
+        <v>-1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>17.95</v>
+        <v>18.03</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.9</v>
+        <v>58.8</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>32.6</v>
       </c>
       <c r="I9" t="n">
-        <v>64.59999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.22</v>
+        <v>-4.67</v>
       </c>
       <c r="L9" t="n">
-        <v>-13.17</v>
+        <v>-16.86</v>
       </c>
       <c r="M9" t="n">
-        <v>25.92</v>
+        <v>26.36</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.9</v>
+        <v>58.4</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>32.9</v>
+        <v>41.6</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.53</v>
+        <v>0.38</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.73</v>
+        <v>-12.62</v>
       </c>
       <c r="M10" t="n">
-        <v>26.36</v>
+        <v>25.93</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.1</v>
+        <v>49.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>31.4</v>
+        <v>25.5</v>
       </c>
       <c r="I12" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-13.37</v>
+        <v>-17.07</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.71</v>
+        <v>-5.67</v>
       </c>
       <c r="M12" t="n">
-        <v>27.85</v>
+        <v>27.94</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.3</v>
+        <v>46.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>26.6</v>
+        <v>25.1</v>
       </c>
       <c r="I13" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.62</v>
+        <v>-11.41</v>
       </c>
       <c r="L13" t="n">
-        <v>-15.25</v>
+        <v>-15.99</v>
       </c>
       <c r="M13" t="n">
-        <v>46.73</v>
+        <v>46.81</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>85.7</v>
+        <v>85.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>67.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.25</v>
+        <v>-0.11</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>12.59</v>
       </c>
       <c r="M2" t="n">
-        <v>11.63</v>
+        <v>11.65</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>84.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.01</v>
+        <v>-1.31</v>
       </c>
       <c r="L3" t="n">
-        <v>28.53</v>
+        <v>28.14</v>
       </c>
       <c r="M3" t="n">
-        <v>22.65</v>
+        <v>22.67</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16.1</v>
+        <v>16.14</v>
       </c>
       <c r="L4" t="n">
-        <v>54.02</v>
+        <v>54.06</v>
       </c>
       <c r="M4" t="n">
-        <v>30.8</v>
+        <v>30.81</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="I5" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.35</v>
+        <v>8.94</v>
       </c>
       <c r="L5" t="n">
-        <v>9.74</v>
+        <v>9.33</v>
       </c>
       <c r="M5" t="n">
-        <v>14.63</v>
+        <v>14.58</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>69.2</v>
+        <v>68.2</v>
       </c>
       <c r="I6" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-17.26</v>
+        <v>-17.69</v>
       </c>
       <c r="L6" t="n">
-        <v>45.6</v>
+        <v>44.85</v>
       </c>
       <c r="M6" t="n">
-        <v>39.23</v>
+        <v>39.29</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>45.9</v>
+        <v>45.2</v>
       </c>
       <c r="I7" t="n">
-        <v>94.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.16</v>
+        <v>-2.56</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.09</v>
+        <v>-2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>11.47</v>
+        <v>11.49</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.57</v>
+        <v>-7.95</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.4</v>
+        <v>63.2</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>44</v>
+        <v>43.4</v>
       </c>
       <c r="I8" t="n">
         <v>77.09999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.18</v>
+        <v>-4.48</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.37</v>
+        <v>-1.69</v>
       </c>
       <c r="M8" t="n">
-        <v>18.03</v>
+        <v>18.06</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>58.8</v>
+        <v>58.5</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>32.6</v>
+        <v>31.7</v>
       </c>
       <c r="I9" t="n">
         <v>62.2</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-4.67</v>
+        <v>-5.15</v>
       </c>
       <c r="L9" t="n">
-        <v>-16.86</v>
+        <v>-17.28</v>
       </c>
       <c r="M9" t="n">
-        <v>26.36</v>
+        <v>26.35</v>
       </c>
       <c r="N9" t="n">
         <v>-25.29</v>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="I10" t="n">
         <v>64.59999999999999</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.62</v>
+        <v>-12.51</v>
       </c>
       <c r="M10" t="n">
-        <v>25.93</v>
+        <v>25.92</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1604,7 +1604,7 @@
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="I12" t="n">
         <v>59.2</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-17.07</v>
+        <v>-17.06</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.67</v>
+        <v>-5.66</v>
       </c>
       <c r="M12" t="n">
         <v>27.94</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="I13" t="n">
         <v>26</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.41</v>
+        <v>-11.66</v>
       </c>
       <c r="L13" t="n">
-        <v>-15.99</v>
+        <v>-16.23</v>
       </c>
       <c r="M13" t="n">
-        <v>46.81</v>
+        <v>46.84</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>66.7</v>
+        <v>66.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="L2" t="n">
-        <v>12.59</v>
+        <v>12.64</v>
       </c>
       <c r="M2" t="n">
         <v>11.65</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.31</v>
+        <v>-1.34</v>
       </c>
       <c r="L3" t="n">
-        <v>28.14</v>
+        <v>28.1</v>
       </c>
       <c r="M3" t="n">
-        <v>22.67</v>
+        <v>22.68</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16.14</v>
+        <v>16.87</v>
       </c>
       <c r="L4" t="n">
-        <v>54.06</v>
+        <v>55.03</v>
       </c>
       <c r="M4" t="n">
-        <v>30.81</v>
+        <v>30.95</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>75.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>89.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.94</v>
+        <v>9.1</v>
       </c>
       <c r="L5" t="n">
-        <v>9.33</v>
+        <v>9.49</v>
       </c>
       <c r="M5" t="n">
-        <v>14.58</v>
+        <v>14.6</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>68.2</v>
+        <v>67.5</v>
       </c>
       <c r="I6" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-17.69</v>
+        <v>-17.96</v>
       </c>
       <c r="L6" t="n">
-        <v>44.85</v>
+        <v>44.37</v>
       </c>
       <c r="M6" t="n">
-        <v>39.29</v>
+        <v>39.33</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="I7" t="n">
-        <v>94.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.56</v>
+        <v>-2.41</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.5</v>
+        <v>-2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.95</v>
+        <v>-7.81</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="I8" t="n">
         <v>77.09999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.48</v>
+        <v>-4.39</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.69</v>
+        <v>-1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>18.06</v>
+        <v>18.05</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>58.5</v>
+        <v>61.3</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>31.7</v>
+        <v>50.1</v>
       </c>
       <c r="I9" t="n">
-        <v>62.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-5.15</v>
+        <v>0.64</v>
       </c>
       <c r="L9" t="n">
-        <v>-17.28</v>
+        <v>-12.39</v>
       </c>
       <c r="M9" t="n">
-        <v>26.35</v>
+        <v>25.92</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>41.8</v>
+        <v>32</v>
       </c>
       <c r="I10" t="n">
-        <v>64.59999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>-5.02</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.51</v>
+        <v>-17.16</v>
       </c>
       <c r="M10" t="n">
-        <v>25.92</v>
+        <v>26.35</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="I12" t="n">
         <v>59.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-17.06</v>
+        <v>-17.21</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.66</v>
+        <v>-5.84</v>
       </c>
       <c r="M12" t="n">
-        <v>27.94</v>
+        <v>27.96</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="I13" t="n">
         <v>26</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.66</v>
+        <v>-11.71</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.23</v>
+        <v>-16.28</v>
       </c>
       <c r="M13" t="n">
-        <v>46.84</v>
+        <v>46.85</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,30 +568,30 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>85.5</v>
+        <v>88.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>66.8</v>
+        <v>75.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-0.06</v>
+        <v>0.46</v>
       </c>
       <c r="L2" t="n">
-        <v>12.64</v>
+        <v>13.23</v>
       </c>
       <c r="M2" t="n">
-        <v>11.65</v>
+        <v>11.62</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>84.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.34</v>
+        <v>-0.83</v>
       </c>
       <c r="L3" t="n">
-        <v>28.1</v>
+        <v>28.76</v>
       </c>
       <c r="M3" t="n">
-        <v>22.68</v>
+        <v>22.63</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16.87</v>
+        <v>18.48</v>
       </c>
       <c r="L4" t="n">
-        <v>55.03</v>
+        <v>55.31</v>
       </c>
       <c r="M4" t="n">
-        <v>30.95</v>
+        <v>30.87</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -885,7 +885,7 @@
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>75.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="I5" t="n">
         <v>89.09999999999999</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.1</v>
+        <v>9.18</v>
       </c>
       <c r="L5" t="n">
-        <v>9.49</v>
+        <v>9.58</v>
       </c>
       <c r="M5" t="n">
-        <v>14.6</v>
+        <v>14.61</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>67.5</v>
+        <v>68</v>
       </c>
       <c r="I6" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-17.96</v>
+        <v>-17.78</v>
       </c>
       <c r="L6" t="n">
-        <v>44.37</v>
+        <v>44.7</v>
       </c>
       <c r="M6" t="n">
-        <v>39.33</v>
+        <v>39.31</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>45.5</v>
+        <v>54.1</v>
       </c>
       <c r="I7" t="n">
-        <v>94.5</v>
+        <v>94.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.41</v>
+        <v>-2.05</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.35</v>
+        <v>-1.99</v>
       </c>
       <c r="M7" t="n">
-        <v>11.48</v>
+        <v>11.47</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.81</v>
+        <v>-7.47</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.3</v>
+        <v>63.1</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>43.6</v>
+        <v>43.1</v>
       </c>
       <c r="I8" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.39</v>
+        <v>-4.59</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.59</v>
+        <v>-1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>18.05</v>
+        <v>17.99</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.3</v>
+        <v>61.4</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="I9" t="n">
         <v>64.59999999999999</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="L9" t="n">
-        <v>-12.39</v>
+        <v>-12.21</v>
       </c>
       <c r="M9" t="n">
-        <v>25.92</v>
+        <v>25.9</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.6</v>
+        <v>59.8</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>35.5</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-5.02</v>
+        <v>-1.49</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.16</v>
+        <v>-18.21</v>
       </c>
       <c r="M10" t="n">
-        <v>26.35</v>
+        <v>26.32</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>25.3</v>
+        <v>26.2</v>
       </c>
       <c r="I12" t="n">
         <v>59.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-17.21</v>
+        <v>-16.73</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.84</v>
+        <v>-5.3</v>
       </c>
       <c r="M12" t="n">
-        <v>27.96</v>
+        <v>27.9</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.71</v>
+        <v>-10.45</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.28</v>
+        <v>-17.89</v>
       </c>
       <c r="M13" t="n">
-        <v>46.85</v>
+        <v>46.65</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>75.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>13.23</v>
+        <v>15.3</v>
       </c>
       <c r="M2" t="n">
-        <v>11.62</v>
+        <v>11.59</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>85.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-0.83</v>
+        <v>-1.08</v>
       </c>
       <c r="L3" t="n">
-        <v>28.76</v>
+        <v>30.68</v>
       </c>
       <c r="M3" t="n">
         <v>22.63</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>18.48</v>
+        <v>20.4</v>
       </c>
       <c r="L4" t="n">
-        <v>55.31</v>
+        <v>57.82</v>
       </c>
       <c r="M4" t="n">
-        <v>30.87</v>
+        <v>30.96</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>75.7</v>
+        <v>76.3</v>
       </c>
       <c r="I5" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.18</v>
+        <v>8.73</v>
       </c>
       <c r="L5" t="n">
-        <v>9.58</v>
+        <v>11.13</v>
       </c>
       <c r="M5" t="n">
-        <v>14.61</v>
+        <v>14.59</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>68</v>
+        <v>72.2</v>
       </c>
       <c r="I6" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-17.78</v>
+        <v>-16.92</v>
       </c>
       <c r="L6" t="n">
-        <v>44.7</v>
+        <v>49.26</v>
       </c>
       <c r="M6" t="n">
         <v>39.31</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>68.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>54.1</v>
+        <v>46.3</v>
       </c>
       <c r="I7" t="n">
-        <v>94.8</v>
+        <v>94.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.05</v>
+        <v>-2.34</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.99</v>
+        <v>-1.27</v>
       </c>
       <c r="M7" t="n">
-        <v>11.47</v>
+        <v>11.41</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.47</v>
+        <v>-7.89</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.1</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>43.1</v>
+        <v>59.2</v>
       </c>
       <c r="I8" t="n">
-        <v>77.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,66 +1211,62 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.59</v>
+        <v>4.07</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.96</v>
+        <v>-5.33</v>
       </c>
       <c r="M8" t="n">
-        <v>17.99</v>
+        <v>25.93</v>
       </c>
       <c r="N8" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1276,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1299,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.4</v>
+        <v>63.3</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>50.5</v>
+        <v>43.6</v>
       </c>
       <c r="I9" t="n">
-        <v>64.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1312,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.85</v>
+        <v>-4.33</v>
       </c>
       <c r="L9" t="n">
-        <v>-12.21</v>
+        <v>-1.69</v>
       </c>
       <c r="M9" t="n">
-        <v>25.9</v>
+        <v>17.99</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.8</v>
+        <v>60.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>35.5</v>
+        <v>37.3</v>
       </c>
       <c r="I10" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.49</v>
+        <v>-0.46</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.21</v>
+        <v>-17.36</v>
       </c>
       <c r="M10" t="n">
-        <v>26.32</v>
+        <v>26.37</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1604,7 +1604,7 @@
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="I12" t="n">
         <v>59.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-16.73</v>
+        <v>-17.66</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.3</v>
+        <v>-3.92</v>
       </c>
       <c r="M12" t="n">
-        <v>27.9</v>
+        <v>27.91</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>24.9</v>
+        <v>26.8</v>
       </c>
       <c r="I13" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.45</v>
+        <v>-9.44</v>
       </c>
       <c r="L13" t="n">
-        <v>-17.89</v>
+        <v>-16.96</v>
       </c>
       <c r="M13" t="n">
-        <v>46.65</v>
+        <v>46.52</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,27 +568,27 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="L2" t="n">
-        <v>15.3</v>
+        <v>15.18</v>
       </c>
       <c r="M2" t="n">
         <v>11.59</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.08</v>
+        <v>-0.99</v>
       </c>
       <c r="L3" t="n">
-        <v>30.68</v>
+        <v>30.8</v>
       </c>
       <c r="M3" t="n">
         <v>22.63</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20.4</v>
+        <v>20.47</v>
       </c>
       <c r="L4" t="n">
-        <v>57.82</v>
+        <v>57.91</v>
       </c>
       <c r="M4" t="n">
         <v>30.96</v>
@@ -885,7 +885,7 @@
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>89.2</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.73</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>11.13</v>
+        <v>11.03</v>
       </c>
       <c r="M5" t="n">
         <v>14.59</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>45.5</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-16.92</v>
+        <v>-16.96</v>
       </c>
       <c r="L6" t="n">
-        <v>49.26</v>
+        <v>49.19</v>
       </c>
       <c r="M6" t="n">
         <v>39.31</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
       <c r="I7" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.34</v>
+        <v>-2.43</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.27</v>
+        <v>-1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>11.41</v>
+        <v>11.42</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.89</v>
+        <v>-7.98</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="I8" t="n">
         <v>64.59999999999999</v>
@@ -1301,7 +1301,7 @@
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-4.33</v>
+        <v>-4.25</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.69</v>
+        <v>-1.61</v>
       </c>
       <c r="M9" t="n">
         <v>17.99</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.4</v>
+        <v>60.1</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>37.3</v>
+        <v>36.5</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-0.46</v>
+        <v>-0.9</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.36</v>
+        <v>-17.72</v>
       </c>
       <c r="M10" t="n">
-        <v>26.37</v>
+        <v>26.36</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.3</v>
+        <v>48.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>26.1</v>
+        <v>24.4</v>
       </c>
       <c r="I12" t="n">
         <v>59.2</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-17.66</v>
+        <v>-18.49</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.92</v>
+        <v>-4.89</v>
       </c>
       <c r="M12" t="n">
         <v>27.91</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.5</v>
+        <v>47.1</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>26.8</v>
+        <v>25.6</v>
       </c>
       <c r="I13" t="n">
         <v>26.4</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.44</v>
+        <v>-10.1</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.96</v>
+        <v>-17.57</v>
       </c>
       <c r="M13" t="n">
-        <v>46.52</v>
+        <v>46.53</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,27 +568,27 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>86.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>69.2</v>
+        <v>77.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="L2" t="n">
-        <v>15.18</v>
+        <v>15.26</v>
       </c>
       <c r="M2" t="n">
         <v>11.59</v>
@@ -675,7 +675,7 @@
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-0.99</v>
+        <v>-0.91</v>
       </c>
       <c r="L3" t="n">
-        <v>30.8</v>
+        <v>30.91</v>
       </c>
       <c r="M3" t="n">
         <v>22.63</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20.47</v>
+        <v>20.64</v>
       </c>
       <c r="L4" t="n">
-        <v>57.91</v>
+        <v>58.13</v>
       </c>
       <c r="M4" t="n">
-        <v>30.96</v>
+        <v>30.97</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,27 +879,27 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>76.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="I5" t="n">
-        <v>89.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>11.03</v>
+        <v>11.28</v>
       </c>
       <c r="M5" t="n">
         <v>14.59</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>45.5</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-16.96</v>
+        <v>-16.81</v>
       </c>
       <c r="L6" t="n">
-        <v>49.19</v>
+        <v>49.46</v>
       </c>
       <c r="M6" t="n">
-        <v>39.31</v>
+        <v>39.32</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>46.1</v>
+        <v>55.2</v>
       </c>
       <c r="I7" t="n">
-        <v>94.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.43</v>
+        <v>-1.88</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.36</v>
+        <v>-0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>11.42</v>
+        <v>11.4</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.98</v>
+        <v>-7.47</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>59.1</v>
+        <v>59.3</v>
       </c>
       <c r="I8" t="n">
         <v>64.59999999999999</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.33</v>
+        <v>-5.28</v>
       </c>
       <c r="M8" t="n">
         <v>25.93</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-4.25</v>
+        <v>-4.12</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.61</v>
+        <v>-1.48</v>
       </c>
       <c r="M9" t="n">
-        <v>17.99</v>
+        <v>17.98</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.1</v>
+        <v>60.3</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-0.9</v>
+        <v>-0.61</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.72</v>
+        <v>-17.48</v>
       </c>
       <c r="M10" t="n">
-        <v>26.36</v>
+        <v>26.37</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="I12" t="n">
         <v>59.2</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-18.49</v>
+        <v>-18.57</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.89</v>
+        <v>-4.98</v>
       </c>
       <c r="M12" t="n">
         <v>27.91</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>25.6</v>
+        <v>26.4</v>
       </c>
       <c r="I13" t="n">
         <v>26.4</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.1</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-17.57</v>
+        <v>-17.14</v>
       </c>
       <c r="M13" t="n">
-        <v>46.53</v>
+        <v>46.52</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,30 +568,30 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.3</v>
+        <v>68.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.52</v>
+        <v>-0.05</v>
       </c>
       <c r="L2" t="n">
-        <v>15.26</v>
+        <v>14.61</v>
       </c>
       <c r="M2" t="n">
-        <v>11.59</v>
+        <v>11.6</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="I3" t="n">
         <v>74.2</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-0.91</v>
+        <v>-1.78</v>
       </c>
       <c r="L3" t="n">
-        <v>30.91</v>
+        <v>29.75</v>
       </c>
       <c r="M3" t="n">
         <v>22.63</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20.64</v>
+        <v>20.03</v>
       </c>
       <c r="L4" t="n">
-        <v>58.13</v>
+        <v>55.49</v>
       </c>
       <c r="M4" t="n">
-        <v>30.97</v>
+        <v>30.91</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,27 +879,27 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>84.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.869999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="L5" t="n">
-        <v>11.28</v>
+        <v>10.66</v>
       </c>
       <c r="M5" t="n">
         <v>14.59</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>75</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>72.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-16.81</v>
+        <v>-18.18</v>
       </c>
       <c r="L6" t="n">
-        <v>49.46</v>
+        <v>47</v>
       </c>
       <c r="M6" t="n">
-        <v>39.32</v>
+        <v>39.31</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>55.2</v>
+        <v>46.5</v>
       </c>
       <c r="I7" t="n">
-        <v>94.8</v>
+        <v>94.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-1.88</v>
+        <v>-2.25</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8</v>
+        <v>-1.18</v>
       </c>
       <c r="M7" t="n">
-        <v>11.4</v>
+        <v>11.41</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.47</v>
+        <v>-7.81</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>59.3</v>
+        <v>45.7</v>
       </c>
       <c r="I8" t="n">
-        <v>64.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,62 +1211,66 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.13</v>
+        <v>-3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.28</v>
+        <v>0.19</v>
       </c>
       <c r="M8" t="n">
-        <v>25.93</v>
+        <v>17.99</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1298,13 +1302,13 @@
         <v>63.4</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>44</v>
+        <v>56.3</v>
       </c>
       <c r="I9" t="n">
-        <v>77.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-4.12</v>
+        <v>2.54</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.48</v>
+        <v>-6.72</v>
       </c>
       <c r="M9" t="n">
-        <v>17.98</v>
+        <v>25.9</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.3</v>
+        <v>60.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-0.61</v>
+        <v>-0.43</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.48</v>
+        <v>-17.43</v>
       </c>
       <c r="M10" t="n">
-        <v>26.37</v>
+        <v>26.33</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="I12" t="n">
         <v>59.2</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-18.57</v>
+        <v>-18.54</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.98</v>
+        <v>-4.94</v>
       </c>
       <c r="M12" t="n">
         <v>27.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.3</v>
+        <v>48.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>26.4</v>
+        <v>29.2</v>
       </c>
       <c r="I13" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.640000000000001</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-17.14</v>
+        <v>-15.29</v>
       </c>
       <c r="M13" t="n">
-        <v>46.52</v>
+        <v>46.45</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,30 +568,30 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>86</v>
+        <v>89.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>68.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-0.05</v>
+        <v>0.96</v>
       </c>
       <c r="L2" t="n">
-        <v>14.61</v>
+        <v>17.53</v>
       </c>
       <c r="M2" t="n">
-        <v>11.6</v>
+        <v>11.68</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>84.7</v>
+        <v>89.8</v>
       </c>
       <c r="I3" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.78</v>
+        <v>-0.13</v>
       </c>
       <c r="L3" t="n">
-        <v>29.75</v>
+        <v>34.25</v>
       </c>
       <c r="M3" t="n">
-        <v>22.63</v>
+        <v>22.7</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20.03</v>
+        <v>19.66</v>
       </c>
       <c r="L4" t="n">
-        <v>55.49</v>
+        <v>55.01</v>
       </c>
       <c r="M4" t="n">
-        <v>30.91</v>
+        <v>30.95</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,30 +879,30 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>75.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>89.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.26</v>
+        <v>9.01</v>
       </c>
       <c r="L5" t="n">
-        <v>10.66</v>
+        <v>12.97</v>
       </c>
       <c r="M5" t="n">
-        <v>14.59</v>
+        <v>14.61</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>69.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="I6" t="n">
-        <v>45.6</v>
+        <v>45.4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-18.18</v>
+        <v>-16.45</v>
       </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>54.24</v>
       </c>
       <c r="M6" t="n">
-        <v>39.31</v>
+        <v>39.44</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68.3</v>
+        <v>71.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>46.5</v>
+        <v>55.2</v>
       </c>
       <c r="I7" t="n">
         <v>94.5</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.25</v>
+        <v>-2.53</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.18</v>
+        <v>0.38</v>
       </c>
       <c r="M7" t="n">
         <v>11.41</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>45.7</v>
+        <v>59.9</v>
       </c>
       <c r="I8" t="n">
-        <v>77.2</v>
+        <v>64.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,66 +1211,62 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>0.19</v>
+        <v>-4.04</v>
       </c>
       <c r="M8" t="n">
-        <v>17.99</v>
+        <v>26.02</v>
       </c>
       <c r="N8" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1276,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1299,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>56.3</v>
+        <v>47</v>
       </c>
       <c r="I9" t="n">
-        <v>64.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1312,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.54</v>
+        <v>-3.03</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.72</v>
+        <v>0.88</v>
       </c>
       <c r="M9" t="n">
-        <v>25.9</v>
+        <v>18.02</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.4</v>
+        <v>61.2</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>37.3</v>
+        <v>40</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-0.43</v>
+        <v>1.08</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.43</v>
+        <v>-16.17</v>
       </c>
       <c r="M10" t="n">
-        <v>26.33</v>
+        <v>26.48</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="G12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>24.3</v>
+        <v>31.7</v>
       </c>
       <c r="I12" t="n">
-        <v>59.2</v>
+        <v>26.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-18.54</v>
+        <v>-7.04</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.94</v>
+        <v>-14.04</v>
       </c>
       <c r="M12" t="n">
-        <v>27.91</v>
+        <v>46.57</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48.3</v>
+        <v>48.8</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>29.2</v>
+        <v>24.7</v>
       </c>
       <c r="I13" t="n">
-        <v>26.5</v>
+        <v>59.2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-8.390000000000001</v>
+        <v>-19</v>
       </c>
       <c r="L13" t="n">
-        <v>-15.29</v>
+        <v>-3.61</v>
       </c>
       <c r="M13" t="n">
-        <v>46.45</v>
+        <v>27.91</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>89.7</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="L2" t="n">
-        <v>17.53</v>
+        <v>17.36</v>
       </c>
       <c r="M2" t="n">
-        <v>11.68</v>
+        <v>11.66</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>89.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>74.09999999999999</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-0.13</v>
+        <v>0.25</v>
       </c>
       <c r="L3" t="n">
-        <v>34.25</v>
+        <v>34.76</v>
       </c>
       <c r="M3" t="n">
-        <v>22.7</v>
+        <v>22.74</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>59.2</v>
+        <v>59</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19.66</v>
+        <v>22.32</v>
       </c>
       <c r="L4" t="n">
-        <v>55.01</v>
+        <v>58.46</v>
       </c>
       <c r="M4" t="n">
-        <v>30.95</v>
+        <v>31.13</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -885,7 +885,7 @@
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="I5" t="n">
         <v>89.09999999999999</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.01</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>12.97</v>
+        <v>13.01</v>
       </c>
       <c r="M5" t="n">
         <v>14.61</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>76.2</v>
+        <v>77</v>
       </c>
       <c r="I6" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-16.45</v>
+        <v>-16.12</v>
       </c>
       <c r="L6" t="n">
-        <v>54.24</v>
+        <v>54.85</v>
       </c>
       <c r="M6" t="n">
-        <v>39.44</v>
+        <v>39.48</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>55.2</v>
+        <v>46.7</v>
       </c>
       <c r="I7" t="n">
         <v>94.5</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.53</v>
+        <v>-2.79</v>
       </c>
       <c r="L7" t="n">
-        <v>0.38</v>
+        <v>0.1</v>
       </c>
       <c r="M7" t="n">
         <v>11.41</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>59.9</v>
+        <v>46.9</v>
       </c>
       <c r="I8" t="n">
-        <v>64.5</v>
+        <v>77.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,62 +1211,66 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>-3.09</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.04</v>
+        <v>0.82</v>
       </c>
       <c r="M8" t="n">
-        <v>26.02</v>
+        <v>18.01</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1298,13 +1302,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>47</v>
+        <v>59.2</v>
       </c>
       <c r="I9" t="n">
-        <v>77.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-3.03</v>
+        <v>3.58</v>
       </c>
       <c r="L9" t="n">
-        <v>0.88</v>
+        <v>-4.38</v>
       </c>
       <c r="M9" t="n">
-        <v>18.02</v>
+        <v>25.99</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="I10" t="n">
         <v>62</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.17</v>
+        <v>-16.27</v>
       </c>
       <c r="M10" t="n">
-        <v>26.48</v>
+        <v>26.47</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>31.7</v>
+        <v>25.2</v>
       </c>
       <c r="I12" t="n">
-        <v>26.4</v>
+        <v>59.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.04</v>
+        <v>-18.74</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.04</v>
+        <v>-3.29</v>
       </c>
       <c r="M12" t="n">
-        <v>46.57</v>
+        <v>27.93</v>
       </c>
       <c r="N12" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>24.7</v>
+        <v>31.1</v>
       </c>
       <c r="I13" t="n">
-        <v>59.2</v>
+        <v>26.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-19</v>
+        <v>-7.37</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.61</v>
+        <v>-14.34</v>
       </c>
       <c r="M13" t="n">
-        <v>27.91</v>
+        <v>46.55</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.7</v>
+        <v>89.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="L2" t="n">
-        <v>17.36</v>
+        <v>17.54</v>
       </c>
       <c r="M2" t="n">
-        <v>11.66</v>
+        <v>11.68</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="I3" t="n">
         <v>74.09999999999999</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="L3" t="n">
-        <v>34.76</v>
+        <v>34.78</v>
       </c>
       <c r="M3" t="n">
         <v>22.74</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>22.32</v>
+        <v>22.08</v>
       </c>
       <c r="L4" t="n">
-        <v>58.46</v>
+        <v>58.14</v>
       </c>
       <c r="M4" t="n">
-        <v>31.13</v>
+        <v>31.11</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>86</v>
+        <v>86.3</v>
       </c>
       <c r="I5" t="n">
         <v>89.09999999999999</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.050000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>13.01</v>
+        <v>13.18</v>
       </c>
       <c r="M5" t="n">
-        <v>14.61</v>
+        <v>14.63</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>77</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>45.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-16.12</v>
+        <v>-15.9</v>
       </c>
       <c r="L6" t="n">
-        <v>54.85</v>
+        <v>55.25</v>
       </c>
       <c r="M6" t="n">
-        <v>39.48</v>
+        <v>39.5</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>46.7</v>
+        <v>55.2</v>
       </c>
       <c r="I7" t="n">
         <v>94.5</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.79</v>
+        <v>-2.53</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="M7" t="n">
         <v>11.41</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
       <c r="I8" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.09</v>
+        <v>-2.99</v>
       </c>
       <c r="L8" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="M8" t="n">
-        <v>18.01</v>
+        <v>18.02</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="I9" t="n">
         <v>64.5</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.58</v>
+        <v>3.73</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.38</v>
+        <v>-4.24</v>
       </c>
       <c r="M9" t="n">
-        <v>25.99</v>
+        <v>26</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>61.2</v>
+        <v>60.9</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>39.8</v>
+        <v>39</v>
       </c>
       <c r="I10" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.96</v>
+        <v>0.55</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.27</v>
+        <v>-16.61</v>
       </c>
       <c r="M10" t="n">
-        <v>26.47</v>
+        <v>26.43</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="I12" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-18.74</v>
+        <v>-18.2</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.29</v>
+        <v>-2.66</v>
       </c>
       <c r="M12" t="n">
-        <v>27.93</v>
+        <v>27.97</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="I13" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-7.37</v>
+        <v>-6.88</v>
       </c>
       <c r="L13" t="n">
-        <v>-14.34</v>
+        <v>-13.9</v>
       </c>
       <c r="M13" t="n">
-        <v>46.55</v>
+        <v>46.58</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,30 +568,30 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>86</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.98</v>
+        <v>-0.05</v>
       </c>
       <c r="L2" t="n">
-        <v>17.54</v>
+        <v>14.61</v>
       </c>
       <c r="M2" t="n">
-        <v>11.68</v>
+        <v>11.63</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>90.7</v>
+        <v>84.7</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.27</v>
+        <v>-1.78</v>
       </c>
       <c r="L3" t="n">
-        <v>34.78</v>
+        <v>29.75</v>
       </c>
       <c r="M3" t="n">
-        <v>22.74</v>
+        <v>22.66</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -879,30 +879,30 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>86.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>89.09999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.210000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="L5" t="n">
-        <v>13.18</v>
+        <v>10.66</v>
       </c>
       <c r="M5" t="n">
-        <v>14.63</v>
+        <v>14.61</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>77.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-15.9</v>
+        <v>-18.18</v>
       </c>
       <c r="L6" t="n">
-        <v>55.25</v>
+        <v>47</v>
       </c>
       <c r="M6" t="n">
-        <v>39.5</v>
+        <v>39.38</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.3</v>
+        <v>68.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>55.2</v>
+        <v>46.5</v>
       </c>
       <c r="I7" t="n">
         <v>94.5</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.53</v>
+        <v>-2.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0.38</v>
+        <v>-1.18</v>
       </c>
       <c r="M7" t="n">
-        <v>11.41</v>
+        <v>11.43</v>
       </c>
       <c r="N7" t="n">
         <v>-7.81</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.5</v>
+        <v>63.4</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>59.5</v>
+        <v>56.3</v>
       </c>
       <c r="I9" t="n">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.73</v>
+        <v>2.54</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.24</v>
+        <v>-6.72</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>25.96</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,83 +1598,83 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="G12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H12" t="n">
+        <v>32</v>
+      </c>
+      <c r="I12" t="n">
         <v>26.3</v>
       </c>
-      <c r="I12" t="n">
-        <v>59.1</v>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-18.2</v>
+        <v>-6.88</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.66</v>
+        <v>-13.9</v>
       </c>
       <c r="M12" t="n">
-        <v>27.97</v>
+        <v>46.58</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>32</v>
+        <v>24.3</v>
       </c>
       <c r="I13" t="n">
-        <v>26.3</v>
+        <v>59.2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-6.88</v>
+        <v>-18.54</v>
       </c>
       <c r="L13" t="n">
-        <v>-13.9</v>
+        <v>-4.94</v>
       </c>
       <c r="M13" t="n">
-        <v>46.58</v>
+        <v>27.95</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,30 +568,30 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>86</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>68.2</v>
+        <v>80.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-0.05</v>
+        <v>2.23</v>
       </c>
       <c r="L2" t="n">
-        <v>14.61</v>
+        <v>16.91</v>
       </c>
       <c r="M2" t="n">
-        <v>11.63</v>
+        <v>11.6</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>84.7</v>
+        <v>95</v>
       </c>
       <c r="I3" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-1.78</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>29.75</v>
+        <v>35.07</v>
       </c>
       <c r="M3" t="n">
-        <v>22.66</v>
+        <v>22.59</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>22.08</v>
+        <v>20.66</v>
       </c>
       <c r="L4" t="n">
-        <v>58.14</v>
+        <v>57.8</v>
       </c>
       <c r="M4" t="n">
-        <v>31.11</v>
+        <v>30.82</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,30 +879,30 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="G5" t="n">
         <v>78</v>
       </c>
       <c r="H5" t="n">
-        <v>75.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="I5" t="n">
         <v>89.09999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.26</v>
+        <v>7.54</v>
       </c>
       <c r="L5" t="n">
-        <v>10.66</v>
+        <v>13.84</v>
       </c>
       <c r="M5" t="n">
-        <v>14.61</v>
+        <v>14.6</v>
       </c>
       <c r="N5" t="n">
         <v>-10.32</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>69.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-18.18</v>
+        <v>-10.7</v>
       </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>55.37</v>
       </c>
       <c r="M6" t="n">
-        <v>39.38</v>
+        <v>39.19</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1095,7 +1095,7 @@
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="I7" t="n">
         <v>94.5</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.25</v>
+        <v>-3.36</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.18</v>
+        <v>0.65</v>
       </c>
       <c r="M7" t="n">
-        <v>11.43</v>
+        <v>11.41</v>
       </c>
       <c r="N7" t="n">
         <v>-7.81</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.5</v>
+        <v>66.3</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>47.1</v>
+        <v>64.8</v>
       </c>
       <c r="I8" t="n">
-        <v>77.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,66 +1211,62 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-2.99</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>18.02</v>
+        <v>25.96</v>
       </c>
       <c r="N8" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1276,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1299,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63.4</v>
+        <v>64.5</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>56.3</v>
+        <v>47.1</v>
       </c>
       <c r="I9" t="n">
-        <v>64.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1312,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.54</v>
+        <v>-3.71</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.72</v>
+        <v>2.24</v>
       </c>
       <c r="M9" t="n">
-        <v>25.96</v>
+        <v>17.98</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.9</v>
+        <v>62.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>39</v>
+        <v>43.2</v>
       </c>
       <c r="I10" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.55</v>
+        <v>3.19</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.61</v>
+        <v>-15.22</v>
       </c>
       <c r="M10" t="n">
-        <v>26.43</v>
+        <v>26.39</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.2</v>
+        <v>51.1</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>32</v>
+        <v>31.4</v>
       </c>
       <c r="I12" t="n">
-        <v>26.3</v>
+        <v>59.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-6.88</v>
+        <v>-15.37</v>
       </c>
       <c r="L12" t="n">
-        <v>-13.9</v>
+        <v>-0.29</v>
       </c>
       <c r="M12" t="n">
-        <v>46.58</v>
+        <v>27.99</v>
       </c>
       <c r="N12" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48.7</v>
+        <v>50.1</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>24.3</v>
+        <v>34.5</v>
       </c>
       <c r="I13" t="n">
-        <v>59.2</v>
+        <v>26.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-18.54</v>
+        <v>-6.74</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.94</v>
+        <v>-10.57</v>
       </c>
       <c r="M13" t="n">
-        <v>27.95</v>
+        <v>46.53</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="L2" t="n">
-        <v>16.91</v>
+        <v>16.58</v>
       </c>
       <c r="M2" t="n">
-        <v>11.6</v>
+        <v>11.59</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>86.8</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>74.3</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="L3" t="n">
-        <v>35.07</v>
+        <v>34.67</v>
       </c>
       <c r="M3" t="n">
-        <v>22.59</v>
+        <v>22.56</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20.66</v>
+        <v>17.62</v>
       </c>
       <c r="L4" t="n">
-        <v>57.8</v>
+        <v>53.83</v>
       </c>
       <c r="M4" t="n">
-        <v>30.82</v>
+        <v>30.87</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,13 +882,13 @@
         <v>82.3</v>
       </c>
       <c r="G5" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>84.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>89.09999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7.54</v>
+        <v>-10.02</v>
       </c>
       <c r="L5" t="n">
-        <v>13.84</v>
+        <v>56.55</v>
       </c>
       <c r="M5" t="n">
-        <v>14.6</v>
+        <v>39.26</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.32</v>
+        <v>-23.17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>91.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I6" t="n">
-        <v>45.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,66 +1001,66 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-10.7</v>
+        <v>7.34</v>
       </c>
       <c r="L6" t="n">
-        <v>55.37</v>
+        <v>13.63</v>
       </c>
       <c r="M6" t="n">
-        <v>39.19</v>
+        <v>14.59</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.32</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68.3</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>46.4</v>
+        <v>45.6</v>
       </c>
       <c r="I7" t="n">
         <v>94.5</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.36</v>
+        <v>-3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.65</v>
+        <v>0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>11.41</v>
+        <v>11.42</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.81</v>
+        <v>-7.89</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66.3</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>64.8</v>
+        <v>63.8</v>
       </c>
       <c r="I8" t="n">
         <v>64.59999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>4.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>25.96</v>
+        <v>25.94</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.5</v>
+        <v>64.3</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-3.71</v>
+        <v>-3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="M9" t="n">
-        <v>17.98</v>
+        <v>17.97</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62.4</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>43.2</v>
+        <v>42.1</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.19</v>
+        <v>2.58</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.22</v>
+        <v>-15.73</v>
       </c>
       <c r="M10" t="n">
-        <v>26.39</v>
+        <v>26.37</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.1</v>
+        <v>50.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>31.4</v>
+        <v>28.7</v>
       </c>
       <c r="I12" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-15.37</v>
+        <v>-16.66</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.29</v>
+        <v>-1.81</v>
       </c>
       <c r="M12" t="n">
-        <v>27.99</v>
+        <v>27.9</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.1</v>
+        <v>49.1</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>34.5</v>
+        <v>31.7</v>
       </c>
       <c r="I13" t="n">
         <v>26.4</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-6.74</v>
+        <v>-8.25</v>
       </c>
       <c r="L13" t="n">
-        <v>-10.57</v>
+        <v>-12.01</v>
       </c>
       <c r="M13" t="n">
-        <v>46.53</v>
+        <v>46.51</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="L2" t="n">
-        <v>16.58</v>
+        <v>16.6</v>
       </c>
       <c r="M2" t="n">
         <v>11.59</v>
@@ -675,7 +675,7 @@
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>74.3</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="L3" t="n">
-        <v>34.67</v>
+        <v>34.78</v>
       </c>
       <c r="M3" t="n">
-        <v>22.56</v>
+        <v>22.57</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>17.62</v>
+        <v>17.59</v>
       </c>
       <c r="L4" t="n">
-        <v>53.83</v>
+        <v>53.78</v>
       </c>
       <c r="M4" t="n">
         <v>30.87</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>93.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-10.02</v>
+        <v>-10.22</v>
       </c>
       <c r="L5" t="n">
-        <v>56.55</v>
+        <v>56.19</v>
       </c>
       <c r="M5" t="n">
-        <v>39.26</v>
+        <v>39.23</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>68.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>45.6</v>
+        <v>46.3</v>
       </c>
       <c r="I7" t="n">
         <v>94.5</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.8</v>
+        <v>-3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>0.19</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>11.42</v>
+        <v>11.41</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.89</v>
+        <v>-7.81</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>63.8</v>
+        <v>63.9</v>
       </c>
       <c r="I8" t="n">
         <v>64.59999999999999</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="L8" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="M8" t="n">
         <v>25.94</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>46.7</v>
+        <v>46.4</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-3.95</v>
+        <v>-4.08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
         <v>17.97</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.73</v>
+        <v>-15.94</v>
       </c>
       <c r="M10" t="n">
         <v>26.37</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="I12" t="n">
         <v>59.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-16.66</v>
+        <v>-17.06</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.81</v>
+        <v>-2.28</v>
       </c>
       <c r="M12" t="n">
-        <v>27.9</v>
+        <v>27.89</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1709,7 +1709,7 @@
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="I13" t="n">
         <v>26.4</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-8.25</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-12.01</v>
+        <v>-12.07</v>
       </c>
       <c r="M13" t="n">
         <v>46.51</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80</v>
+        <v>81.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.96</v>
+        <v>2.87</v>
       </c>
       <c r="L2" t="n">
-        <v>16.6</v>
+        <v>16.75</v>
       </c>
       <c r="M2" t="n">
-        <v>11.59</v>
+        <v>11.65</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.52</v>
+        <v>7.04</v>
       </c>
       <c r="L3" t="n">
-        <v>34.78</v>
+        <v>36.75</v>
       </c>
       <c r="M3" t="n">
-        <v>22.57</v>
+        <v>22.6</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I4" t="n">
-        <v>59.4</v>
+        <v>45.6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>17.59</v>
+        <v>-7.93</v>
       </c>
       <c r="L4" t="n">
-        <v>53.78</v>
+        <v>58.87</v>
       </c>
       <c r="M4" t="n">
-        <v>30.87</v>
+        <v>39.27</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.33</v>
+        <v>-23.17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>45.7</v>
+        <v>59</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-10.22</v>
+        <v>17.92</v>
       </c>
       <c r="L5" t="n">
-        <v>56.19</v>
+        <v>57.35</v>
       </c>
       <c r="M5" t="n">
-        <v>39.23</v>
+        <v>31.12</v>
       </c>
       <c r="N5" t="n">
-        <v>-23.17</v>
+        <v>-20.33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>82.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>84.3</v>
+        <v>79.7</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7.34</v>
+        <v>4.33</v>
       </c>
       <c r="L6" t="n">
-        <v>13.63</v>
+        <v>12.2</v>
       </c>
       <c r="M6" t="n">
-        <v>14.59</v>
+        <v>14.6</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>46.3</v>
+        <v>43</v>
       </c>
       <c r="I7" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.45</v>
+        <v>-5.09</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.24</v>
       </c>
       <c r="M7" t="n">
-        <v>11.41</v>
+        <v>11.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.81</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.59</v>
+        <v>7.23</v>
       </c>
       <c r="L8" t="n">
-        <v>0.52</v>
+        <v>-3.69</v>
       </c>
       <c r="M8" t="n">
-        <v>25.94</v>
+        <v>25.89</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.2</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>46.4</v>
+        <v>48.7</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-4.08</v>
+        <v>-2.82</v>
       </c>
       <c r="L9" t="n">
-        <v>1.85</v>
+        <v>2.99</v>
       </c>
       <c r="M9" t="n">
-        <v>17.97</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>61.8</v>
+        <v>63.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>41.6</v>
+        <v>46.2</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2.32</v>
+        <v>4.82</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.94</v>
+        <v>-13.65</v>
       </c>
       <c r="M10" t="n">
-        <v>26.37</v>
+        <v>26.39</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.9</v>
+        <v>51.2</v>
       </c>
       <c r="G12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>27.9</v>
+        <v>37.8</v>
       </c>
       <c r="I12" t="n">
-        <v>59.2</v>
+        <v>26.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-17.06</v>
+        <v>-4.03</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.28</v>
+        <v>-10.58</v>
       </c>
       <c r="M12" t="n">
-        <v>27.89</v>
+        <v>46.41</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.1</v>
+        <v>50.5</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>31.6</v>
+        <v>29.8</v>
       </c>
       <c r="I13" t="n">
-        <v>26.4</v>
+        <v>59.1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-8.300000000000001</v>
+        <v>-13.58</v>
       </c>
       <c r="L13" t="n">
-        <v>-12.07</v>
+        <v>-5.64</v>
       </c>
       <c r="M13" t="n">
-        <v>46.51</v>
+        <v>28.03</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.87</v>
+        <v>3.22</v>
       </c>
       <c r="L2" t="n">
-        <v>16.75</v>
+        <v>17.14</v>
       </c>
       <c r="M2" t="n">
-        <v>11.65</v>
+        <v>11.69</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.04</v>
+        <v>7.52</v>
       </c>
       <c r="L3" t="n">
-        <v>36.75</v>
+        <v>37.36</v>
       </c>
       <c r="M3" t="n">
-        <v>22.6</v>
+        <v>22.64</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.7</v>
+        <v>84.3</v>
       </c>
       <c r="G4" t="n">
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>97.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-7.93</v>
+        <v>-7.14</v>
       </c>
       <c r="L4" t="n">
-        <v>58.87</v>
+        <v>60.23</v>
       </c>
       <c r="M4" t="n">
-        <v>39.27</v>
+        <v>39.37</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>59</v>
+        <v>58.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>17.92</v>
+        <v>19.67</v>
       </c>
       <c r="L5" t="n">
-        <v>57.35</v>
+        <v>59.68</v>
       </c>
       <c r="M5" t="n">
-        <v>31.12</v>
+        <v>31.26</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>79.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>12.2</v>
+        <v>12.38</v>
       </c>
       <c r="M6" t="n">
         <v>14.6</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="I7" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.09</v>
+        <v>-5.22</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.24</v>
+        <v>-1.38</v>
       </c>
       <c r="M7" t="n">
         <v>11.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.029999999999999</v>
+        <v>-8.16</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>64.09999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>64.7</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7.23</v>
+        <v>7.39</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.69</v>
+        <v>-3.55</v>
       </c>
       <c r="M8" t="n">
         <v>25.89</v>
@@ -1295,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>65.2</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="I9" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.82</v>
+        <v>-2.58</v>
       </c>
       <c r="L9" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>18.01</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63.4</v>
+        <v>63.8</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4.82</v>
+        <v>5.47</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.65</v>
+        <v>-13.12</v>
       </c>
       <c r="M10" t="n">
-        <v>26.39</v>
+        <v>26.41</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>37.8</v>
+        <v>31.3</v>
       </c>
       <c r="I12" t="n">
-        <v>26.6</v>
+        <v>59</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.03</v>
+        <v>-12.79</v>
       </c>
       <c r="L12" t="n">
-        <v>-10.58</v>
+        <v>-4.77</v>
       </c>
       <c r="M12" t="n">
-        <v>46.41</v>
+        <v>28.07</v>
       </c>
       <c r="N12" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>29.8</v>
+        <v>36.9</v>
       </c>
       <c r="I13" t="n">
-        <v>59.1</v>
+        <v>26.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-13.58</v>
+        <v>-4.47</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.64</v>
+        <v>-10.99</v>
       </c>
       <c r="M13" t="n">
-        <v>28.03</v>
+        <v>46.4</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.22</v>
+        <v>1.42</v>
       </c>
       <c r="L2" t="n">
-        <v>17.14</v>
+        <v>16.69</v>
       </c>
       <c r="M2" t="n">
-        <v>11.69</v>
+        <v>11.63</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>88.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>94.7</v>
       </c>
       <c r="I3" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.52</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>37.36</v>
+        <v>35.35</v>
       </c>
       <c r="M3" t="n">
-        <v>22.64</v>
+        <v>22.56</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.3</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.5</v>
+        <v>58.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-7.14</v>
+        <v>19.67</v>
       </c>
       <c r="L4" t="n">
-        <v>60.23</v>
+        <v>59.68</v>
       </c>
       <c r="M4" t="n">
-        <v>39.37</v>
+        <v>31.26</v>
       </c>
       <c r="N4" t="n">
-        <v>-23.17</v>
+        <v>-20.33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>58.8</v>
+        <v>45.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19.67</v>
+        <v>-9.98</v>
       </c>
       <c r="L5" t="n">
-        <v>59.68</v>
+        <v>55.05</v>
       </c>
       <c r="M5" t="n">
-        <v>31.26</v>
+        <v>39.18</v>
       </c>
       <c r="N5" t="n">
-        <v>-20.33</v>
+        <v>-23.17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.7</v>
+        <v>81.5</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>5.65</v>
       </c>
       <c r="L6" t="n">
-        <v>12.38</v>
+        <v>13.65</v>
       </c>
       <c r="M6" t="n">
-        <v>14.6</v>
+        <v>14.63</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>67.7</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.8</v>
+        <v>44.6</v>
       </c>
       <c r="I7" t="n">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.22</v>
+        <v>-4.25</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.38</v>
+        <v>-0.46</v>
       </c>
       <c r="M7" t="n">
         <v>11.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.16</v>
+        <v>-7.81</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66.2</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>64.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="I8" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7.39</v>
+        <v>7.58</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.55</v>
+        <v>-0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>25.89</v>
+        <v>25.94</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="G12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>31.3</v>
+        <v>36.9</v>
       </c>
       <c r="I12" t="n">
-        <v>59</v>
+        <v>26.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-12.79</v>
+        <v>-4.47</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.77</v>
+        <v>-10.99</v>
       </c>
       <c r="M12" t="n">
-        <v>28.07</v>
+        <v>46.4</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.9</v>
+        <v>49.6</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>36.9</v>
+        <v>27.1</v>
       </c>
       <c r="I13" t="n">
-        <v>26.6</v>
+        <v>59</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-4.47</v>
+        <v>-17.04</v>
       </c>
       <c r="L13" t="n">
-        <v>-10.99</v>
+        <v>-3.52</v>
       </c>
       <c r="M13" t="n">
-        <v>46.4</v>
+        <v>28.08</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.42</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>16.69</v>
+        <v>17.69</v>
       </c>
       <c r="M2" t="n">
-        <v>11.63</v>
+        <v>11.75</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.3</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>8.44</v>
       </c>
       <c r="L3" t="n">
-        <v>35.35</v>
+        <v>38.55</v>
       </c>
       <c r="M3" t="n">
-        <v>22.56</v>
+        <v>22.75</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>58.8</v>
+        <v>45.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19.67</v>
+        <v>-7.42</v>
       </c>
       <c r="L4" t="n">
-        <v>59.68</v>
+        <v>59.76</v>
       </c>
       <c r="M4" t="n">
-        <v>31.26</v>
+        <v>39.33</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.33</v>
+        <v>-23.17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>45.7</v>
+        <v>58.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-9.98</v>
+        <v>22.16</v>
       </c>
       <c r="L5" t="n">
-        <v>55.05</v>
+        <v>63</v>
       </c>
       <c r="M5" t="n">
-        <v>39.18</v>
+        <v>31.59</v>
       </c>
       <c r="N5" t="n">
-        <v>-23.17</v>
+        <v>-20.33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.5</v>
+        <v>80.8</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>82.3</v>
+        <v>80.5</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.65</v>
+        <v>4.73</v>
       </c>
       <c r="L6" t="n">
-        <v>13.65</v>
+        <v>12.63</v>
       </c>
       <c r="M6" t="n">
-        <v>14.63</v>
+        <v>14.61</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>44.6</v>
+        <v>42.5</v>
       </c>
       <c r="I7" t="n">
-        <v>94.5</v>
+        <v>94.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.25</v>
+        <v>-5.38</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.46</v>
+        <v>-1.54</v>
       </c>
       <c r="M7" t="n">
-        <v>11.43</v>
+        <v>11.44</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.81</v>
+        <v>-8.32</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>65.8</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>66.8</v>
+        <v>63.3</v>
       </c>
       <c r="I8" t="n">
         <v>64.59999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7.58</v>
+        <v>6.77</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.42</v>
+        <v>-4.1</v>
       </c>
       <c r="M8" t="n">
-        <v>25.94</v>
+        <v>25.9</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1295,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65.2</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>49.2</v>
+        <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.58</v>
+        <v>-2.86</v>
       </c>
       <c r="L9" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="M9" t="n">
-        <v>18.01</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63.8</v>
+        <v>64</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="I10" t="n">
         <v>62.1</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5.47</v>
+        <v>5.9</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.12</v>
+        <v>-12.76</v>
       </c>
       <c r="M10" t="n">
-        <v>26.41</v>
+        <v>26.43</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.9</v>
+        <v>52.1</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>36.9</v>
+        <v>40.3</v>
       </c>
       <c r="I12" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.47</v>
+        <v>-2.65</v>
       </c>
       <c r="L12" t="n">
-        <v>-10.99</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>46.4</v>
+        <v>46.49</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.6</v>
+        <v>51.3</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>27.1</v>
+        <v>32</v>
       </c>
       <c r="I13" t="n">
         <v>59</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-17.04</v>
+        <v>-12.45</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.52</v>
+        <v>-4.41</v>
       </c>
       <c r="M13" t="n">
-        <v>28.08</v>
+        <v>28.09</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>17.69</v>
+        <v>17.86</v>
       </c>
       <c r="M2" t="n">
-        <v>11.75</v>
+        <v>11.77</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.44</v>
+        <v>8.84</v>
       </c>
       <c r="L3" t="n">
-        <v>38.55</v>
+        <v>39.05</v>
       </c>
       <c r="M3" t="n">
-        <v>22.75</v>
+        <v>22.81</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.5</v>
+        <v>45.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-7.42</v>
+        <v>-5.49</v>
       </c>
       <c r="L4" t="n">
-        <v>59.76</v>
+        <v>63.08</v>
       </c>
       <c r="M4" t="n">
-        <v>39.33</v>
+        <v>39.62</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.3</v>
+        <v>58.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>22.16</v>
+        <v>19.5</v>
       </c>
       <c r="L5" t="n">
-        <v>63</v>
+        <v>59.46</v>
       </c>
       <c r="M5" t="n">
-        <v>31.59</v>
+        <v>31.25</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.73</v>
+        <v>5.04</v>
       </c>
       <c r="L6" t="n">
-        <v>12.63</v>
+        <v>12.96</v>
       </c>
       <c r="M6" t="n">
-        <v>14.61</v>
+        <v>14.63</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.5</v>
+        <v>43</v>
       </c>
       <c r="I7" t="n">
-        <v>94.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.38</v>
+        <v>-5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.54</v>
+        <v>-1.26</v>
       </c>
       <c r="M7" t="n">
-        <v>11.44</v>
+        <v>11.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.32</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="I8" t="n">
         <v>64.59999999999999</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6.77</v>
+        <v>6.73</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.1</v>
+        <v>-4.14</v>
       </c>
       <c r="M8" t="n">
         <v>25.9</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.86</v>
+        <v>-2.98</v>
       </c>
       <c r="L9" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>64</v>
+        <v>62.8</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>48.2</v>
+        <v>44.5</v>
       </c>
       <c r="I10" t="n">
         <v>62.1</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5.9</v>
+        <v>3.87</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.76</v>
+        <v>-14.44</v>
       </c>
       <c r="M10" t="n">
-        <v>26.43</v>
+        <v>26.39</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.1</v>
+        <v>54.3</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>40.3</v>
+        <v>40.9</v>
       </c>
       <c r="I12" t="n">
-        <v>26.5</v>
+        <v>58.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-2.65</v>
+        <v>-11.99</v>
       </c>
       <c r="L12" t="n">
-        <v>-9.300000000000001</v>
+        <v>-3.9</v>
       </c>
       <c r="M12" t="n">
-        <v>46.49</v>
+        <v>28.14</v>
       </c>
       <c r="N12" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1706,13 +1706,13 @@
         <v>51.3</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I13" t="n">
-        <v>59</v>
+        <v>26.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.45</v>
+        <v>-3.91</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.41</v>
+        <v>-10.47</v>
       </c>
       <c r="M13" t="n">
-        <v>28.09</v>
+        <v>46.42</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="L2" t="n">
-        <v>17.86</v>
+        <v>17.85</v>
       </c>
       <c r="M2" t="n">
         <v>11.77</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.84</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>39.05</v>
+        <v>39.43</v>
       </c>
       <c r="M3" t="n">
-        <v>22.81</v>
+        <v>22.86</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="G4" t="n">
         <v>88</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-5.49</v>
+        <v>-5.25</v>
       </c>
       <c r="L4" t="n">
-        <v>63.08</v>
+        <v>63.49</v>
       </c>
       <c r="M4" t="n">
-        <v>39.62</v>
+        <v>39.67</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19.5</v>
+        <v>19.57</v>
       </c>
       <c r="L5" t="n">
-        <v>59.46</v>
+        <v>59.55</v>
       </c>
       <c r="M5" t="n">
         <v>31.25</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>81.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="I6" t="n">
-        <v>89.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.04</v>
+        <v>5.58</v>
       </c>
       <c r="L6" t="n">
-        <v>12.96</v>
+        <v>13.55</v>
       </c>
       <c r="M6" t="n">
-        <v>14.63</v>
+        <v>14.67</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67.09999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
       <c r="I7" t="n">
-        <v>94.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.1</v>
+        <v>-4.94</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.26</v>
+        <v>-1.09</v>
       </c>
       <c r="M7" t="n">
-        <v>11.43</v>
+        <v>11.42</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.050000000000001</v>
+        <v>-7.89</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.8</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>63.2</v>
+        <v>63.9</v>
       </c>
       <c r="I8" t="n">
         <v>64.59999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6.73</v>
+        <v>7.12</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.14</v>
+        <v>-3.79</v>
       </c>
       <c r="M8" t="n">
-        <v>25.9</v>
+        <v>25.89</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>48.4</v>
+        <v>47.8</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.98</v>
+        <v>-3.28</v>
       </c>
       <c r="L9" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>17.99</v>
+        <v>17.98</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="I10" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.87</v>
+        <v>4.18</v>
       </c>
       <c r="L10" t="n">
-        <v>-14.44</v>
+        <v>-14.18</v>
       </c>
       <c r="M10" t="n">
         <v>26.39</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>54.3</v>
+        <v>51.7</v>
       </c>
       <c r="G12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>40.9</v>
+        <v>39.3</v>
       </c>
       <c r="I12" t="n">
-        <v>58.9</v>
+        <v>26.5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-11.99</v>
+        <v>-3.18</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.9</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>28.14</v>
+        <v>46.45</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1706,13 +1706,13 @@
         <v>51.3</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>38</v>
+        <v>32.3</v>
       </c>
       <c r="I13" t="n">
-        <v>26.6</v>
+        <v>58.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-3.91</v>
+        <v>-12.3</v>
       </c>
       <c r="L13" t="n">
-        <v>-10.47</v>
+        <v>-4.24</v>
       </c>
       <c r="M13" t="n">
-        <v>46.42</v>
+        <v>28.11</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>83.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.84</v>
+        <v>3.22</v>
       </c>
       <c r="L2" t="n">
-        <v>17.85</v>
+        <v>17.14</v>
       </c>
       <c r="M2" t="n">
-        <v>11.77</v>
+        <v>11.69</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>73.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.130000000000001</v>
+        <v>7.52</v>
       </c>
       <c r="L3" t="n">
-        <v>39.43</v>
+        <v>37.36</v>
       </c>
       <c r="M3" t="n">
-        <v>22.86</v>
+        <v>22.64</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -780,10 +780,10 @@
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-5.25</v>
+        <v>-7.14</v>
       </c>
       <c r="L4" t="n">
-        <v>63.49</v>
+        <v>60.23</v>
       </c>
       <c r="M4" t="n">
-        <v>39.67</v>
+        <v>39.37</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.8</v>
+        <v>58.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19.57</v>
+        <v>19.06</v>
       </c>
       <c r="L5" t="n">
-        <v>59.55</v>
+        <v>61.06</v>
       </c>
       <c r="M5" t="n">
-        <v>31.25</v>
+        <v>31.2</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>82.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>89</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.58</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>13.55</v>
+        <v>12.38</v>
       </c>
       <c r="M6" t="n">
-        <v>14.67</v>
+        <v>14.6</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>43.3</v>
+        <v>42.8</v>
       </c>
       <c r="I7" t="n">
-        <v>94.5</v>
+        <v>94.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.94</v>
+        <v>-5.22</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.09</v>
+        <v>-1.38</v>
       </c>
       <c r="M7" t="n">
-        <v>11.42</v>
+        <v>11.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.89</v>
+        <v>-8.16</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>63.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7.12</v>
+        <v>7.39</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.79</v>
+        <v>-3.55</v>
       </c>
       <c r="M8" t="n">
         <v>25.89</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.7</v>
+        <v>65.3</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>47.8</v>
+        <v>49.4</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-3.28</v>
+        <v>-2.98</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>4.19</v>
       </c>
       <c r="M9" t="n">
-        <v>17.98</v>
+        <v>17.99</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>64.5</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>45.1</v>
+        <v>49.5</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4.18</v>
+        <v>7.13</v>
       </c>
       <c r="L10" t="n">
-        <v>-14.18</v>
+        <v>-12.94</v>
       </c>
       <c r="M10" t="n">
-        <v>26.39</v>
+        <v>26.38</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.7</v>
+        <v>52.5</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>39.3</v>
+        <v>41.5</v>
       </c>
       <c r="I12" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-3.18</v>
+        <v>-0.48</v>
       </c>
       <c r="L12" t="n">
-        <v>-9.789999999999999</v>
+        <v>-11.33</v>
       </c>
       <c r="M12" t="n">
-        <v>46.45</v>
+        <v>46.33</v>
       </c>
       <c r="N12" t="n">
         <v>-36.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>51.3</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
         <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>32.3</v>
+        <v>31.3</v>
       </c>
       <c r="I13" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.3</v>
+        <v>-12.79</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.24</v>
+        <v>-4.77</v>
       </c>
       <c r="M13" t="n">
-        <v>28.11</v>
+        <v>28.07</v>
       </c>
       <c r="N13" t="n">
         <v>-26.43</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="L2" t="n">
-        <v>17.14</v>
+        <v>19.26</v>
       </c>
       <c r="M2" t="n">
-        <v>11.69</v>
+        <v>11.7</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.52</v>
+        <v>10.54</v>
       </c>
       <c r="L3" t="n">
-        <v>37.36</v>
+        <v>42.2</v>
       </c>
       <c r="M3" t="n">
-        <v>22.64</v>
+        <v>22.71</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-7.14</v>
+        <v>-3.47</v>
       </c>
       <c r="L4" t="n">
-        <v>60.23</v>
+        <v>69.52</v>
       </c>
       <c r="M4" t="n">
-        <v>39.37</v>
+        <v>39.39</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19.06</v>
+        <v>20.89</v>
       </c>
       <c r="L5" t="n">
-        <v>61.06</v>
+        <v>63.53</v>
       </c>
       <c r="M5" t="n">
-        <v>31.2</v>
+        <v>31.29</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="L6" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="M6" t="n">
-        <v>14.6</v>
+        <v>14.62</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.8</v>
+        <v>42.2</v>
       </c>
       <c r="I7" t="n">
         <v>94.3</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.22</v>
+        <v>-5.64</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.38</v>
+        <v>-1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>11.43</v>
+        <v>11.42</v>
       </c>
       <c r="N7" t="n">
         <v>-8.16</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>64.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="I8" t="n">
         <v>64.7</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7.39</v>
+        <v>5.63</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.55</v>
+        <v>-0.77</v>
       </c>
       <c r="M8" t="n">
-        <v>25.89</v>
+        <v>25.87</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>49.4</v>
+        <v>50.4</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.98</v>
+        <v>-2.47</v>
       </c>
       <c r="L9" t="n">
-        <v>4.19</v>
+        <v>4.74</v>
       </c>
       <c r="M9" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>64.5</v>
+        <v>64.3</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7.13</v>
+        <v>6.82</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.94</v>
+        <v>-13.19</v>
       </c>
       <c r="M10" t="n">
-        <v>26.38</v>
+        <v>26.45</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>41.5</v>
+        <v>35.5</v>
       </c>
       <c r="I12" t="n">
-        <v>26.7</v>
+        <v>59</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-0.48</v>
+        <v>-10.89</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.33</v>
+        <v>-2.06</v>
       </c>
       <c r="M12" t="n">
-        <v>46.33</v>
+        <v>28.06</v>
       </c>
       <c r="N12" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>52.3</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>31.3</v>
+        <v>40.9</v>
       </c>
       <c r="I13" t="n">
-        <v>59</v>
+        <v>26.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.79</v>
+        <v>-0.8</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.77</v>
+        <v>-11.61</v>
       </c>
       <c r="M13" t="n">
-        <v>28.07</v>
+        <v>46.31</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.5</v>
+        <v>91.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>84.5</v>
+        <v>83.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.15</v>
+        <v>3.81</v>
       </c>
       <c r="L2" t="n">
-        <v>19.26</v>
+        <v>18.87</v>
       </c>
       <c r="M2" t="n">
-        <v>11.7</v>
+        <v>11.69</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10.54</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>42.2</v>
+        <v>41.47</v>
       </c>
       <c r="M3" t="n">
-        <v>22.71</v>
+        <v>22.67</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-3.47</v>
+        <v>-4.01</v>
       </c>
       <c r="L4" t="n">
-        <v>69.52</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>39.39</v>
+        <v>39.36</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20.89</v>
+        <v>20.48</v>
       </c>
       <c r="L5" t="n">
-        <v>63.53</v>
+        <v>62.98</v>
       </c>
       <c r="M5" t="n">
-        <v>31.29</v>
+        <v>31.28</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="L6" t="n">
-        <v>13.26</v>
+        <v>13.24</v>
       </c>
       <c r="M6" t="n">
         <v>14.62</v>
@@ -1095,10 +1095,10 @@
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="I7" t="n">
-        <v>94.3</v>
+        <v>94.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.64</v>
+        <v>-5.77</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4</v>
+        <v>-1.54</v>
       </c>
       <c r="M7" t="n">
         <v>11.42</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.16</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>64.2</v>
+        <v>63.3</v>
       </c>
       <c r="I8" t="n">
         <v>64.7</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.63</v>
+        <v>5.11</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.77</v>
+        <v>-1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>25.87</v>
+        <v>25.88</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.47</v>
+        <v>-2.72</v>
       </c>
       <c r="L9" t="n">
-        <v>4.74</v>
+        <v>4.47</v>
       </c>
       <c r="M9" t="n">
         <v>18</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>64.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>49</v>
+        <v>50.6</v>
       </c>
       <c r="I10" t="n">
         <v>62.1</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6.82</v>
+        <v>7.74</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.19</v>
+        <v>-12.45</v>
       </c>
       <c r="M10" t="n">
-        <v>26.45</v>
+        <v>26.42</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="I12" t="n">
         <v>59</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.89</v>
+        <v>-11.16</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.06</v>
+        <v>-2.35</v>
       </c>
       <c r="M12" t="n">
-        <v>28.06</v>
+        <v>28.07</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>52.3</v>
+        <v>51.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>40.9</v>
+        <v>38.5</v>
       </c>
       <c r="I13" t="n">
         <v>26.7</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-0.8</v>
+        <v>-2.11</v>
       </c>
       <c r="L13" t="n">
-        <v>-11.61</v>
+        <v>-12.78</v>
       </c>
       <c r="M13" t="n">
-        <v>46.31</v>
+        <v>46.3</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.81</v>
+        <v>3.87</v>
       </c>
       <c r="L2" t="n">
-        <v>18.87</v>
+        <v>18.94</v>
       </c>
       <c r="M2" t="n">
         <v>11.69</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.970000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="L3" t="n">
-        <v>41.47</v>
+        <v>41.77</v>
       </c>
       <c r="M3" t="n">
-        <v>22.67</v>
+        <v>22.69</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-4.01</v>
+        <v>-3.59</v>
       </c>
       <c r="L4" t="n">
-        <v>68.56999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="M4" t="n">
-        <v>39.36</v>
+        <v>39.38</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20.48</v>
+        <v>21.87</v>
       </c>
       <c r="L5" t="n">
-        <v>62.98</v>
+        <v>64.86</v>
       </c>
       <c r="M5" t="n">
-        <v>31.28</v>
+        <v>31.33</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>79.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.86</v>
+        <v>3.52</v>
       </c>
       <c r="L6" t="n">
-        <v>13.24</v>
+        <v>12.87</v>
       </c>
       <c r="M6" t="n">
-        <v>14.62</v>
+        <v>14.61</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="I7" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.77</v>
+        <v>-6.05</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.54</v>
+        <v>-1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>11.42</v>
+        <v>11.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.220000000000001</v>
+        <v>-8.49</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="I8" t="n">
         <v>64.7</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.26</v>
+        <v>-1.3</v>
       </c>
       <c r="M8" t="n">
         <v>25.88</v>
@@ -1301,7 +1301,7 @@
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.72</v>
+        <v>-2.83</v>
       </c>
       <c r="L9" t="n">
-        <v>4.47</v>
+        <v>4.35</v>
       </c>
       <c r="M9" t="n">
         <v>18</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>64.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="I10" t="n">
         <v>62.1</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7.74</v>
+        <v>7.9</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.45</v>
+        <v>-12.31</v>
       </c>
       <c r="M10" t="n">
-        <v>26.42</v>
+        <v>26.41</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="I12" t="n">
         <v>59</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-11.16</v>
+        <v>-11.25</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.35</v>
+        <v>-2.45</v>
       </c>
       <c r="M12" t="n">
         <v>28.07</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
       <c r="I13" t="n">
         <v>26.7</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-2.11</v>
+        <v>-2.36</v>
       </c>
       <c r="L13" t="n">
-        <v>-12.78</v>
+        <v>-13</v>
       </c>
       <c r="M13" t="n">
         <v>46.3</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.3</v>
+        <v>91.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>83.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.87</v>
+        <v>4.15</v>
       </c>
       <c r="L2" t="n">
-        <v>18.94</v>
+        <v>19.26</v>
       </c>
       <c r="M2" t="n">
-        <v>11.69</v>
+        <v>11.7</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="L3" t="n">
-        <v>41.77</v>
+        <v>41.71</v>
       </c>
       <c r="M3" t="n">
-        <v>22.69</v>
+        <v>22.68</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-3.59</v>
+        <v>-3.49</v>
       </c>
       <c r="L4" t="n">
-        <v>69.3</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>39.38</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>21.87</v>
+        <v>19.95</v>
       </c>
       <c r="L5" t="n">
-        <v>64.86</v>
+        <v>63.27</v>
       </c>
       <c r="M5" t="n">
-        <v>31.33</v>
+        <v>31.28</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>79.2</v>
+        <v>80.2</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.52</v>
+        <v>4.04</v>
       </c>
       <c r="L6" t="n">
-        <v>12.87</v>
+        <v>13.43</v>
       </c>
       <c r="M6" t="n">
-        <v>14.61</v>
+        <v>14.63</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>41.5</v>
+        <v>42.6</v>
       </c>
       <c r="I7" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.05</v>
+        <v>-5.44</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.83</v>
+        <v>-1.19</v>
       </c>
       <c r="M7" t="n">
         <v>11.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.49</v>
+        <v>-8.16</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>63.2</v>
+        <v>64.5</v>
       </c>
       <c r="I8" t="n">
         <v>64.7</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.07</v>
+        <v>5.79</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3</v>
+        <v>-0.62</v>
       </c>
       <c r="M8" t="n">
-        <v>25.88</v>
+        <v>25.87</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1276,35 +1276,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="I9" t="n">
-        <v>77.2</v>
+        <v>62.1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,35 +1312,35 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.83</v>
+        <v>7.73</v>
       </c>
       <c r="L9" t="n">
-        <v>4.35</v>
+        <v>-14.16</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>26.39</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.62</v>
+        <v>-25.29</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
+          <t>ETF difesa/sicurezza UCITS</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
+          <t>LMT|RTX|BA.L</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1356,22 +1356,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>64.5</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H10" t="n">
-        <v>50.9</v>
+        <v>47.3</v>
       </c>
       <c r="I10" t="n">
-        <v>62.1</v>
+        <v>77.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,35 +1417,35 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7.9</v>
+        <v>-3.37</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.31</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>26.41</v>
+        <v>17.97</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-20.62</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
+          <t>ETF India UCITS / fondo Asia consumer</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>LMT|RTX|BA.L</t>
+          <t>INFY|HDB|RELIANCE.NS</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1461,22 +1461,22 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.2</v>
+        <v>55.5</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>34.8</v>
+        <v>44.4</v>
       </c>
       <c r="I12" t="n">
         <v>59</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-11.25</v>
+        <v>-10.45</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.45</v>
+        <v>-1.57</v>
       </c>
       <c r="M12" t="n">
         <v>28.07</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>51.4</v>
+        <v>50.2</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>38.1</v>
+        <v>34.5</v>
       </c>
       <c r="I13" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-2.36</v>
+        <v>-3.31</v>
       </c>
       <c r="L13" t="n">
-        <v>-13</v>
+        <v>-16.47</v>
       </c>
       <c r="M13" t="n">
-        <v>46.3</v>
+        <v>46.27</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.15</v>
+        <v>3.56</v>
       </c>
       <c r="L2" t="n">
-        <v>19.26</v>
+        <v>20.06</v>
       </c>
       <c r="M2" t="n">
-        <v>11.7</v>
+        <v>11.72</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10.15</v>
+        <v>8.84</v>
       </c>
       <c r="L3" t="n">
-        <v>41.71</v>
+        <v>44.13</v>
       </c>
       <c r="M3" t="n">
         <v>22.68</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-3.49</v>
+        <v>-5.32</v>
       </c>
       <c r="L4" t="n">
-        <v>69.48999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>39.38</v>
+        <v>39.42</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19.95</v>
+        <v>20.49</v>
       </c>
       <c r="L5" t="n">
-        <v>63.27</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>31.28</v>
+        <v>31.36</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.04</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>13.43</v>
+        <v>14.03</v>
       </c>
       <c r="M6" t="n">
         <v>14.63</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>66.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.6</v>
+        <v>41.4</v>
       </c>
       <c r="I7" t="n">
-        <v>94.3</v>
+        <v>94</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.44</v>
+        <v>-5.77</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.19</v>
+        <v>-2.4</v>
       </c>
       <c r="M7" t="n">
-        <v>11.43</v>
+        <v>11.42</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.16</v>
+        <v>-8.57</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66.2</v>
+        <v>65.7</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>64.5</v>
+        <v>63.1</v>
       </c>
       <c r="I8" t="n">
         <v>64.7</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.79</v>
+        <v>6.73</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.62</v>
+        <v>-4.24</v>
       </c>
       <c r="M8" t="n">
         <v>25.87</v>
@@ -1295,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.5</v>
+        <v>63.7</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>49.4</v>
+        <v>47.2</v>
       </c>
       <c r="I9" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7.73</v>
+        <v>6.49</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.16</v>
+        <v>-15.15</v>
       </c>
       <c r="M9" t="n">
-        <v>26.39</v>
+        <v>26.38</v>
       </c>
       <c r="N9" t="n">
         <v>-25.29</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>64.5</v>
+        <v>63.6</v>
       </c>
       <c r="G10" t="n">
         <v>72</v>
       </c>
       <c r="H10" t="n">
-        <v>47.3</v>
+        <v>44.6</v>
       </c>
       <c r="I10" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-3.37</v>
+        <v>-4.74</v>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>0.42</v>
       </c>
       <c r="M10" t="n">
-        <v>17.97</v>
+        <v>18.03</v>
       </c>
       <c r="N10" t="n">
         <v>-20.62</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.5</v>
+        <v>51.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>44.4</v>
+        <v>33.5</v>
       </c>
       <c r="I12" t="n">
-        <v>59</v>
+        <v>58.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.45</v>
+        <v>-11.96</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.57</v>
+        <v>-3.07</v>
       </c>
       <c r="M12" t="n">
-        <v>28.07</v>
+        <v>28.22</v>
       </c>
       <c r="N12" t="n">
         <v>-26.43</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>34.5</v>
+        <v>33.5</v>
       </c>
       <c r="I13" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-3.31</v>
+        <v>-3.89</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.47</v>
+        <v>-16.97</v>
       </c>
       <c r="M13" t="n">
-        <v>46.27</v>
+        <v>46.34</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>20.06</v>
+        <v>19.93</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72</v>
+        <v>11.73</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.84</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>44.13</v>
+        <v>43.96</v>
       </c>
       <c r="M3" t="n">
-        <v>22.68</v>
+        <v>22.69</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-5.32</v>
+        <v>-4.97</v>
       </c>
       <c r="L4" t="n">
-        <v>70.43000000000001</v>
+        <v>71.06</v>
       </c>
       <c r="M4" t="n">
-        <v>39.42</v>
+        <v>39.4</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20.49</v>
+        <v>20.18</v>
       </c>
       <c r="L5" t="n">
-        <v>64.01000000000001</v>
+        <v>63.58</v>
       </c>
       <c r="M5" t="n">
-        <v>31.36</v>
+        <v>31.33</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.8</v>
+        <v>81.2</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>4.38</v>
       </c>
       <c r="L6" t="n">
-        <v>14.03</v>
+        <v>14.72</v>
       </c>
       <c r="M6" t="n">
         <v>14.63</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>41.4</v>
+        <v>40.3</v>
       </c>
       <c r="I7" t="n">
-        <v>94</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.77</v>
+        <v>-6.35</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.4</v>
+        <v>-3.01</v>
       </c>
       <c r="M7" t="n">
-        <v>11.42</v>
+        <v>11.47</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.57</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>63.1</v>
+        <v>62.2</v>
       </c>
       <c r="I8" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6.73</v>
+        <v>6.26</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.24</v>
+        <v>-4.67</v>
       </c>
       <c r="M8" t="n">
-        <v>25.87</v>
+        <v>25.89</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1301,7 +1301,7 @@
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="I9" t="n">
         <v>62.2</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6.49</v>
+        <v>6.44</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.15</v>
+        <v>-15.19</v>
       </c>
       <c r="M9" t="n">
         <v>26.38</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
       <c r="G10" t="n">
         <v>72</v>
       </c>
       <c r="H10" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="I10" t="n">
         <v>77.09999999999999</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.74</v>
+        <v>-4.63</v>
       </c>
       <c r="L10" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="M10" t="n">
         <v>18.03</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.7</v>
+        <v>50.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>33.5</v>
+        <v>30.4</v>
       </c>
       <c r="I12" t="n">
-        <v>58.8</v>
+        <v>58.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-11.96</v>
+        <v>-13.53</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.07</v>
+        <v>-4.79</v>
       </c>
       <c r="M12" t="n">
-        <v>28.22</v>
+        <v>28.45</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.43</v>
+        <v>-26.54</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.8</v>
+        <v>48.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>33.5</v>
+        <v>29.9</v>
       </c>
       <c r="I13" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-3.89</v>
+        <v>-5.85</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.97</v>
+        <v>-18.66</v>
       </c>
       <c r="M13" t="n">
-        <v>46.34</v>
+        <v>46.49</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>84.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>19.93</v>
+        <v>19.82</v>
       </c>
       <c r="M2" t="n">
-        <v>11.73</v>
+        <v>11.74</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.710000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="L3" t="n">
-        <v>43.96</v>
+        <v>43.98</v>
       </c>
       <c r="M3" t="n">
         <v>22.69</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-4.97</v>
+        <v>-4.89</v>
       </c>
       <c r="L4" t="n">
-        <v>71.06</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>39.4</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20.18</v>
+        <v>19.85</v>
       </c>
       <c r="L5" t="n">
-        <v>63.58</v>
+        <v>63.14</v>
       </c>
       <c r="M5" t="n">
-        <v>31.33</v>
+        <v>31.31</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>81.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>14.72</v>
+        <v>14.3</v>
       </c>
       <c r="M6" t="n">
         <v>14.63</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="I7" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.35</v>
+        <v>-6.46</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.01</v>
+        <v>-3.13</v>
       </c>
       <c r="M7" t="n">
-        <v>11.47</v>
+        <v>11.49</v>
       </c>
       <c r="N7" t="n">
-        <v>-9.140000000000001</v>
+        <v>-9.25</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>62.2</v>
+        <v>44.6</v>
       </c>
       <c r="I8" t="n">
-        <v>64.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,62 +1211,66 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6.26</v>
+        <v>-4.72</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.67</v>
+        <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>25.89</v>
+        <v>18.03</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1295,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63.7</v>
+        <v>63.4</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>47.1</v>
+        <v>46.2</v>
       </c>
       <c r="I9" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6.44</v>
+        <v>5.94</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.19</v>
+        <v>-15.59</v>
       </c>
       <c r="M9" t="n">
-        <v>26.38</v>
+        <v>26.4</v>
       </c>
       <c r="N9" t="n">
         <v>-25.29</v>
@@ -1381,7 +1385,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1400,16 +1404,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63.7</v>
+        <v>62.6</v>
       </c>
       <c r="G10" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>44.8</v>
+        <v>54</v>
       </c>
       <c r="I10" t="n">
-        <v>77.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.63</v>
+        <v>6.13</v>
       </c>
       <c r="L10" t="n">
-        <v>0.53</v>
+        <v>-4.78</v>
       </c>
       <c r="M10" t="n">
-        <v>18.03</v>
+        <v>25.9</v>
       </c>
       <c r="N10" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1604,10 +1604,10 @@
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="I12" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-13.53</v>
+        <v>-13.58</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.79</v>
+        <v>-4.84</v>
       </c>
       <c r="M12" t="n">
-        <v>28.45</v>
+        <v>28.46</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.54</v>
+        <v>-26.58</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>29.9</v>
+        <v>28.5</v>
       </c>
       <c r="I13" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-5.85</v>
+        <v>-6.64</v>
       </c>
       <c r="L13" t="n">
-        <v>-18.66</v>
+        <v>-19.34</v>
       </c>
       <c r="M13" t="n">
-        <v>46.49</v>
+        <v>46.58</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.3</v>
+        <v>91.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>83.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>4.04</v>
       </c>
       <c r="L2" t="n">
-        <v>19.82</v>
+        <v>20.61</v>
       </c>
       <c r="M2" t="n">
-        <v>11.74</v>
+        <v>11.7</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.73</v>
+        <v>9.65</v>
       </c>
       <c r="L3" t="n">
-        <v>43.98</v>
+        <v>45.21</v>
       </c>
       <c r="M3" t="n">
-        <v>22.69</v>
+        <v>22.67</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-4.89</v>
+        <v>-3.97</v>
       </c>
       <c r="L4" t="n">
-        <v>71.20999999999999</v>
+        <v>72.87</v>
       </c>
       <c r="M4" t="n">
-        <v>39.4</v>
+        <v>39.38</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19.85</v>
+        <v>13.85</v>
       </c>
       <c r="L5" t="n">
-        <v>63.14</v>
+        <v>63.93</v>
       </c>
       <c r="M5" t="n">
-        <v>31.31</v>
+        <v>31.26</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.09999999999999</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="L6" t="n">
-        <v>14.3</v>
+        <v>13.88</v>
       </c>
       <c r="M6" t="n">
-        <v>14.63</v>
+        <v>14.64</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>40.1</v>
+        <v>41.6</v>
       </c>
       <c r="I7" t="n">
-        <v>93.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.46</v>
+        <v>-5.68</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.13</v>
+        <v>-2.31</v>
       </c>
       <c r="M7" t="n">
-        <v>11.49</v>
+        <v>11.41</v>
       </c>
       <c r="N7" t="n">
-        <v>-9.25</v>
+        <v>-8.49</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.6</v>
+        <v>65.8</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>44.6</v>
+        <v>63.2</v>
       </c>
       <c r="I8" t="n">
-        <v>77.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,66 +1211,62 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.72</v>
+        <v>6.81</v>
       </c>
       <c r="L8" t="n">
-        <v>0.44</v>
+        <v>-4.17</v>
       </c>
       <c r="M8" t="n">
-        <v>18.03</v>
+        <v>25.87</v>
       </c>
       <c r="N8" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1280,35 +1276,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>46.2</v>
+        <v>47.6</v>
       </c>
       <c r="I9" t="n">
-        <v>62.1</v>
+        <v>77.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,35 +1312,35 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5.94</v>
+        <v>-3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.59</v>
+        <v>2.17</v>
       </c>
       <c r="M9" t="n">
-        <v>26.4</v>
+        <v>18.01</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.29</v>
+        <v>-20.62</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
+          <t>ETF India UCITS / fondo Asia consumer</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>LMT|RTX|BA.L</t>
+          <t>INFY|HDB|RELIANCE.NS</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1360,22 +1356,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62.6</v>
+        <v>63.8</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>54</v>
+        <v>47.4</v>
       </c>
       <c r="I10" t="n">
-        <v>64.59999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6.13</v>
+        <v>5.33</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.78</v>
+        <v>-12.83</v>
       </c>
       <c r="M10" t="n">
-        <v>25.9</v>
+        <v>26.39</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.6</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30.3</v>
+        <v>37</v>
       </c>
       <c r="I12" t="n">
-        <v>58.3</v>
+        <v>59</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-13.58</v>
+        <v>-10.2</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.84</v>
+        <v>-1.13</v>
       </c>
       <c r="M12" t="n">
-        <v>28.46</v>
+        <v>28.09</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.58</v>
+        <v>-26.43</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>49.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>28.5</v>
+        <v>33.5</v>
       </c>
       <c r="I13" t="n">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-6.64</v>
+        <v>-4.35</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.34</v>
+        <v>-16.18</v>
       </c>
       <c r="M13" t="n">
-        <v>46.58</v>
+        <v>46.35</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>85.3</v>
+        <v>83.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.04</v>
+        <v>2.84</v>
       </c>
       <c r="L2" t="n">
-        <v>20.61</v>
+        <v>19.75</v>
       </c>
       <c r="M2" t="n">
         <v>11.7</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.65</v>
+        <v>6.93</v>
       </c>
       <c r="L3" t="n">
-        <v>45.21</v>
+        <v>46.4</v>
       </c>
       <c r="M3" t="n">
         <v>22.67</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-3.97</v>
+        <v>-7.7</v>
       </c>
       <c r="L4" t="n">
-        <v>72.87</v>
+        <v>79.61</v>
       </c>
       <c r="M4" t="n">
-        <v>39.38</v>
+        <v>39.39</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13.85</v>
+        <v>14.07</v>
       </c>
       <c r="L5" t="n">
-        <v>63.93</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>31.26</v>
+        <v>31.32</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I6" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.62</v>
+        <v>4.38</v>
       </c>
       <c r="L6" t="n">
-        <v>13.88</v>
+        <v>13.56</v>
       </c>
       <c r="M6" t="n">
-        <v>14.64</v>
+        <v>14.54</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H7" t="n">
-        <v>41.6</v>
+        <v>62.9</v>
       </c>
       <c r="I7" t="n">
-        <v>94.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,37 +1106,33 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.68</v>
+        <v>6.94</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.31</v>
+        <v>-4.9</v>
       </c>
       <c r="M7" t="n">
-        <v>11.41</v>
+        <v>25.87</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.49</v>
+        <v>-22.72</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
         <v>3</v>
       </c>
@@ -1150,22 +1146,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1171,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1190,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.8</v>
+        <v>65.5</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H8" t="n">
-        <v>63.2</v>
+        <v>38.7</v>
       </c>
       <c r="I8" t="n">
-        <v>64.7</v>
+        <v>93.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,33 +1207,37 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6.81</v>
+        <v>-6.8</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.17</v>
+        <v>-4.53</v>
       </c>
       <c r="M8" t="n">
-        <v>25.87</v>
+        <v>11.47</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.72</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>NEE|ENEL.MI|IBE.MC</t>
+        </is>
+      </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
@@ -1251,22 +1251,22 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>47.6</v>
+        <v>48.5</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-3.3</v>
+        <v>-2.82</v>
       </c>
       <c r="L9" t="n">
-        <v>2.17</v>
+        <v>2.68</v>
       </c>
       <c r="M9" t="n">
         <v>18.01</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63.8</v>
+        <v>64.2</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>47.4</v>
+        <v>48.7</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5.33</v>
+        <v>6.06</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.83</v>
+        <v>-12.23</v>
       </c>
       <c r="M10" t="n">
-        <v>26.39</v>
+        <v>26.38</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>50.4</v>
       </c>
       <c r="G12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H12" t="n">
-        <v>37</v>
+        <v>35.3</v>
       </c>
       <c r="I12" t="n">
-        <v>59</v>
+        <v>26.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.2</v>
+        <v>-3.33</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.13</v>
+        <v>-15.28</v>
       </c>
       <c r="M12" t="n">
-        <v>28.09</v>
+        <v>46.34</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.8</v>
+        <v>50.1</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
-        <v>33.5</v>
+        <v>28.6</v>
       </c>
       <c r="I13" t="n">
-        <v>26.7</v>
+        <v>58.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-4.35</v>
+        <v>-16.23</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.18</v>
+        <v>-2.78</v>
       </c>
       <c r="M13" t="n">
-        <v>46.35</v>
+        <v>28.22</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="L2" t="n">
-        <v>19.75</v>
+        <v>19.66</v>
       </c>
       <c r="M2" t="n">
         <v>11.7</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.93</v>
+        <v>7.24</v>
       </c>
       <c r="L3" t="n">
-        <v>46.4</v>
+        <v>46.82</v>
       </c>
       <c r="M3" t="n">
         <v>22.67</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-7.7</v>
+        <v>-7.97</v>
       </c>
       <c r="L4" t="n">
-        <v>79.61</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>39.39</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14.07</v>
+        <v>11.28</v>
       </c>
       <c r="L5" t="n">
-        <v>64.23999999999999</v>
+        <v>60.22</v>
       </c>
       <c r="M5" t="n">
-        <v>31.32</v>
+        <v>31.42</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.7</v>
+        <v>80.3</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.38</v>
+        <v>4.13</v>
       </c>
       <c r="L6" t="n">
-        <v>13.56</v>
+        <v>13.29</v>
       </c>
       <c r="M6" t="n">
         <v>14.54</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.7</v>
+        <v>65.3</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
       </c>
       <c r="H7" t="n">
-        <v>62.9</v>
+        <v>61.8</v>
       </c>
       <c r="I7" t="n">
         <v>64.7</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6.94</v>
+        <v>6.35</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.9</v>
+        <v>-5.42</v>
       </c>
       <c r="M7" t="n">
         <v>25.87</v>
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>74</v>
       </c>
       <c r="H8" t="n">
-        <v>38.7</v>
+        <v>37.9</v>
       </c>
       <c r="I8" t="n">
-        <v>93.3</v>
+        <v>93</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.8</v>
+        <v>-7.21</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.53</v>
+        <v>-4.95</v>
       </c>
       <c r="M8" t="n">
-        <v>11.47</v>
+        <v>11.53</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.619999999999999</v>
+        <v>-10.01</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1295,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="I9" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.82</v>
+        <v>-2.99</v>
       </c>
       <c r="L9" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
         <v>18.01</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>64.2</v>
+        <v>63.8</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>48.7</v>
+        <v>47.4</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6.06</v>
+        <v>5.33</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.23</v>
+        <v>-12.83</v>
       </c>
       <c r="M10" t="n">
-        <v>26.38</v>
+        <v>26.42</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energia e Uranio</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>35.3</v>
+        <v>29.2</v>
       </c>
       <c r="I12" t="n">
-        <v>26.7</v>
+        <v>58.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,66 +1615,66 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-3.33</v>
+        <v>-15.94</v>
       </c>
       <c r="L12" t="n">
-        <v>-15.28</v>
+        <v>-2.44</v>
       </c>
       <c r="M12" t="n">
-        <v>46.34</v>
+        <v>28.19</v>
       </c>
       <c r="N12" t="n">
-        <v>-36.07</v>
+        <v>-26.43</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ETF/ETC o basket</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>URNM.L</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ETF uranium/energy transition o fondo energia</t>
+          <t>ETF global clean energy UCITS</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CCJ|SHEL.L|ENI.MI</t>
+          <t>ENPH|SEDG|VWS.CO</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0-6%</t>
+          <t>0-5%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
+          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Alta volatilita materie prime</t>
+          <t>Drawdown prolungati e rischio politico</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
+          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Energia e Uranio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.1</v>
+        <v>49.3</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>28.6</v>
+        <v>32.1</v>
       </c>
       <c r="I13" t="n">
-        <v>58.8</v>
+        <v>26.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,66 +1720,66 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-16.23</v>
+        <v>-5.08</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.78</v>
+        <v>-16.81</v>
       </c>
       <c r="M13" t="n">
-        <v>28.22</v>
+        <v>46.47</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.43</v>
+        <v>-36.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/ETC o basket</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>URNM.L</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ETF global clean energy UCITS</t>
+          <t>ETF uranium/energy transition o fondo energia</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ENPH|SEDG|VWS.CO</t>
+          <t>CCJ|SHEL.L|ENI.MI</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0-5%</t>
+          <t>0-6%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Transizione energetica ma settore volatile e dipendente dai tassi</t>
+          <t>Domanda energia data center elettrificazione e sicurezza energetica</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Drawdown prolungati e rischio politico</t>
+          <t>Alta volatilita materie prime</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Non aumentare se trend debole; solo monitoraggio o size minima</t>
+          <t>Usare solo come satellite piccolo; verificare strumenti UCITS/ETC</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="L2" t="n">
-        <v>19.66</v>
+        <v>19.62</v>
       </c>
       <c r="M2" t="n">
         <v>11.7</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.24</v>
+        <v>6.98</v>
       </c>
       <c r="L3" t="n">
-        <v>46.82</v>
+        <v>46.46</v>
       </c>
       <c r="M3" t="n">
         <v>22.67</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-7.97</v>
+        <v>-8.32</v>
       </c>
       <c r="L4" t="n">
-        <v>79.06999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>39.39</v>
+        <v>39.38</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.28</v>
+        <v>11.29</v>
       </c>
       <c r="L5" t="n">
-        <v>60.22</v>
+        <v>60.24</v>
       </c>
       <c r="M5" t="n">
         <v>31.42</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.13</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>13.29</v>
+        <v>13.47</v>
       </c>
       <c r="M6" t="n">
         <v>14.54</v>
@@ -1095,7 +1095,7 @@
         <v>68</v>
       </c>
       <c r="H7" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="I7" t="n">
         <v>64.7</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6.35</v>
+        <v>6.42</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.42</v>
+        <v>-5.37</v>
       </c>
       <c r="M7" t="n">
         <v>25.87</v>
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="G8" t="n">
         <v>74</v>
       </c>
       <c r="H8" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="I8" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.21</v>
+        <v>-7.39</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.95</v>
+        <v>-5.13</v>
       </c>
       <c r="M8" t="n">
-        <v>11.53</v>
+        <v>11.56</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.01</v>
+        <v>-10.18</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1295,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.99</v>
+        <v>-2.89</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="M9" t="n">
         <v>18.01</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63.8</v>
+        <v>63.9</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>47.4</v>
+        <v>47.7</v>
       </c>
       <c r="I10" t="n">
         <v>62.1</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5.33</v>
+        <v>5.49</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.83</v>
+        <v>-12.7</v>
       </c>
       <c r="M10" t="n">
-        <v>26.42</v>
+        <v>26.41</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-15.94</v>
+        <v>-15.92</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.44</v>
+        <v>-2.42</v>
       </c>
       <c r="M12" t="n">
         <v>28.19</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>32.1</v>
+        <v>32.7</v>
       </c>
       <c r="I13" t="n">
         <v>26.5</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-5.08</v>
+        <v>-4.76</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.81</v>
+        <v>-16.53</v>
       </c>
       <c r="M13" t="n">
-        <v>46.47</v>
+        <v>46.44</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91</v>
+        <v>90.7</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.74</v>
+        <v>2.24</v>
       </c>
       <c r="L2" t="n">
-        <v>19.62</v>
+        <v>19.04</v>
       </c>
       <c r="M2" t="n">
-        <v>11.7</v>
+        <v>11.72</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.98</v>
+        <v>5.69</v>
       </c>
       <c r="L3" t="n">
-        <v>46.46</v>
+        <v>44.7</v>
       </c>
       <c r="M3" t="n">
-        <v>22.67</v>
+        <v>22.69</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-8.32</v>
+        <v>-9.94</v>
       </c>
       <c r="L4" t="n">
-        <v>78.40000000000001</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>39.38</v>
+        <v>39.4</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>60.24</v>
+        <v>66.11</v>
       </c>
       <c r="M5" t="n">
-        <v>31.42</v>
+        <v>31.35</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>13.47</v>
+        <v>13.58</v>
       </c>
       <c r="M6" t="n">
         <v>14.54</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.3</v>
+        <v>65.7</v>
       </c>
       <c r="G7" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>61.9</v>
+        <v>39.4</v>
       </c>
       <c r="I7" t="n">
-        <v>64.7</v>
+        <v>93.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,33 +1106,37 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6.42</v>
+        <v>-6.42</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.37</v>
+        <v>-4.14</v>
       </c>
       <c r="M7" t="n">
-        <v>25.87</v>
+        <v>11.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-22.72</v>
+        <v>-9.25</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>NEE|ENEL.MI|IBE.MC</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>3</v>
       </c>
@@ -1146,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1190,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65</v>
+        <v>65.3</v>
       </c>
       <c r="G8" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>37.5</v>
+        <v>49.6</v>
       </c>
       <c r="I8" t="n">
-        <v>92.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1207,46 +1211,46 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.39</v>
+        <v>-3.32</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.13</v>
+        <v>5.19</v>
       </c>
       <c r="M8" t="n">
-        <v>11.56</v>
+        <v>18.01</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.18</v>
+        <v>-20.62</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF India UCITS / fondo Asia consumer</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>INFY|HDB|RELIANCE.NS</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1256,17 +1260,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1276,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>48.4</v>
+        <v>47.6</v>
       </c>
       <c r="I9" t="n">
-        <v>77.2</v>
+        <v>62.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,35 +1316,35 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.89</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>2.61</v>
+        <v>-9.9</v>
       </c>
       <c r="M9" t="n">
-        <v>18.01</v>
+        <v>26.36</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.62</v>
+        <v>-25.29</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
+          <t>ETF difesa/sicurezza UCITS</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
+          <t>LMT|RTX|BA.L</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1356,22 +1360,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63.9</v>
+        <v>62.3</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>47.7</v>
+        <v>53</v>
       </c>
       <c r="I10" t="n">
-        <v>62.1</v>
+        <v>64.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5.49</v>
+        <v>5.88</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.7</v>
+        <v>-5.85</v>
       </c>
       <c r="M10" t="n">
-        <v>26.41</v>
+        <v>25.88</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>29.2</v>
+        <v>26.8</v>
       </c>
       <c r="I12" t="n">
-        <v>58.8</v>
+        <v>58.5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-15.92</v>
+        <v>-17.1</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.42</v>
+        <v>-3.78</v>
       </c>
       <c r="M12" t="n">
-        <v>28.19</v>
+        <v>28.34</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.43</v>
+        <v>-26.58</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>32.7</v>
+        <v>31.5</v>
       </c>
       <c r="I13" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-4.76</v>
+        <v>-5.82</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.53</v>
+        <v>-16.38</v>
       </c>
       <c r="M13" t="n">
-        <v>46.44</v>
+        <v>46.32</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.7</v>
+        <v>90.2</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.24</v>
+        <v>2.53</v>
       </c>
       <c r="L2" t="n">
-        <v>19.04</v>
+        <v>16.74</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72</v>
+        <v>11.73</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5.69</v>
+        <v>8.99</v>
       </c>
       <c r="L3" t="n">
-        <v>44.7</v>
+        <v>41.1</v>
       </c>
       <c r="M3" t="n">
-        <v>22.69</v>
+        <v>22.71</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-9.94</v>
+        <v>-1.98</v>
       </c>
       <c r="L4" t="n">
-        <v>75.23999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>39.4</v>
+        <v>39.49</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.7</v>
+        <v>58.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.289999999999999</v>
+        <v>4.48</v>
       </c>
       <c r="L5" t="n">
-        <v>66.11</v>
+        <v>61.87</v>
       </c>
       <c r="M5" t="n">
-        <v>31.35</v>
+        <v>31.46</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.8</v>
+        <v>78.2</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="L6" t="n">
-        <v>13.58</v>
+        <v>12.58</v>
       </c>
       <c r="M6" t="n">
-        <v>14.54</v>
+        <v>14.56</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.7</v>
+        <v>65.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>39.4</v>
+        <v>38.9</v>
       </c>
       <c r="I7" t="n">
-        <v>93.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.42</v>
+        <v>-7</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.14</v>
+        <v>-3.84</v>
       </c>
       <c r="M7" t="n">
-        <v>11.43</v>
+        <v>11.48</v>
       </c>
       <c r="N7" t="n">
-        <v>-9.25</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>49.6</v>
+        <v>46.9</v>
       </c>
       <c r="I8" t="n">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.32</v>
+        <v>-5.13</v>
       </c>
       <c r="L8" t="n">
-        <v>5.19</v>
+        <v>4.31</v>
       </c>
       <c r="M8" t="n">
-        <v>18.01</v>
+        <v>18.12</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63.9</v>
+        <v>61.9</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>47.6</v>
+        <v>41.9</v>
       </c>
       <c r="I9" t="n">
         <v>62.2</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>-1.19</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.9</v>
+        <v>-9.58</v>
       </c>
       <c r="M9" t="n">
         <v>26.36</v>
@@ -1390,30 +1390,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62.3</v>
+        <v>58.6</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>53</v>
+        <v>42.2</v>
       </c>
       <c r="I10" t="n">
-        <v>64.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5.88</v>
+        <v>0.51</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.85</v>
+        <v>-11.95</v>
       </c>
       <c r="M10" t="n">
-        <v>25.88</v>
+        <v>26.09</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="I12" t="n">
-        <v>58.5</v>
+        <v>58.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-17.1</v>
+        <v>-15.08</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.78</v>
+        <v>-6.57</v>
       </c>
       <c r="M12" t="n">
-        <v>28.34</v>
+        <v>28.39</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.58</v>
+        <v>-26.79</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.1</v>
+        <v>46.9</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>31.5</v>
+        <v>25</v>
       </c>
       <c r="I13" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-5.82</v>
+        <v>-9.69</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.38</v>
+        <v>-19.05</v>
       </c>
       <c r="M13" t="n">
-        <v>46.32</v>
+        <v>46.47</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="L2" t="n">
-        <v>16.74</v>
+        <v>16.71</v>
       </c>
       <c r="M2" t="n">
         <v>11.73</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.99</v>
+        <v>9.08</v>
       </c>
       <c r="L3" t="n">
-        <v>41.1</v>
+        <v>41.21</v>
       </c>
       <c r="M3" t="n">
-        <v>22.71</v>
+        <v>22.7</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-1.98</v>
+        <v>-1.66</v>
       </c>
       <c r="L4" t="n">
-        <v>64.09999999999999</v>
+        <v>64.63</v>
       </c>
       <c r="M4" t="n">
-        <v>39.49</v>
+        <v>39.47</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4.48</v>
+        <v>4.89</v>
       </c>
       <c r="L5" t="n">
-        <v>61.87</v>
+        <v>62.51</v>
       </c>
       <c r="M5" t="n">
-        <v>31.46</v>
+        <v>31.44</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>78.2</v>
+        <v>77.8</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="L6" t="n">
-        <v>12.58</v>
+        <v>12.37</v>
       </c>
       <c r="M6" t="n">
-        <v>14.56</v>
+        <v>14.55</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7</v>
+        <v>-7.07</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.84</v>
+        <v>-3.92</v>
       </c>
       <c r="M7" t="n">
         <v>11.48</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.13</v>
+        <v>-5.12</v>
       </c>
       <c r="L8" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="M8" t="n">
         <v>18.12</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="I9" t="n">
         <v>62.2</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-1.19</v>
+        <v>-1.13</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.58</v>
+        <v>-9.51</v>
       </c>
       <c r="M9" t="n">
         <v>26.36</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="L10" t="n">
-        <v>-11.95</v>
+        <v>-11.98</v>
       </c>
       <c r="M10" t="n">
-        <v>26.09</v>
+        <v>26.1</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-15.08</v>
+        <v>-15.22</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.57</v>
+        <v>-6.72</v>
       </c>
       <c r="M12" t="n">
-        <v>28.39</v>
+        <v>28.4</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.79</v>
+        <v>-26.91</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="I13" t="n">
         <v>26.5</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.69</v>
+        <v>-9.48</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.05</v>
+        <v>-18.86</v>
       </c>
       <c r="M13" t="n">
-        <v>46.47</v>
+        <v>46.46</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.2</v>
+        <v>90.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.7</v>
+        <v>82.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="L2" t="n">
-        <v>16.71</v>
+        <v>19.69</v>
       </c>
       <c r="M2" t="n">
-        <v>11.73</v>
+        <v>11.75</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.08</v>
+        <v>7.19</v>
       </c>
       <c r="L3" t="n">
-        <v>41.21</v>
+        <v>46.32</v>
       </c>
       <c r="M3" t="n">
-        <v>22.7</v>
+        <v>22.75</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-1.66</v>
+        <v>-4.85</v>
       </c>
       <c r="L4" t="n">
-        <v>64.63</v>
+        <v>77.89</v>
       </c>
       <c r="M4" t="n">
-        <v>39.47</v>
+        <v>39.49</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4.89</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>62.51</v>
+        <v>66.11</v>
       </c>
       <c r="M5" t="n">
-        <v>31.44</v>
+        <v>31.48</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>77.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.62</v>
+        <v>4.14</v>
       </c>
       <c r="L6" t="n">
-        <v>12.37</v>
+        <v>13.05</v>
       </c>
       <c r="M6" t="n">
-        <v>14.55</v>
+        <v>14.57</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>38.8</v>
+        <v>39.3</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.07</v>
+        <v>-6.59</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.92</v>
+        <v>-3.96</v>
       </c>
       <c r="M7" t="n">
-        <v>11.48</v>
+        <v>11.5</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>46.9</v>
+        <v>49.6</v>
       </c>
       <c r="I8" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.12</v>
+        <v>-3.32</v>
       </c>
       <c r="L8" t="n">
-        <v>4.32</v>
+        <v>5.19</v>
       </c>
       <c r="M8" t="n">
-        <v>18.12</v>
+        <v>18.06</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>42</v>
+        <v>59.3</v>
       </c>
       <c r="I9" t="n">
-        <v>62.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-1.13</v>
+        <v>4.79</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.51</v>
+        <v>-6.33</v>
       </c>
       <c r="M9" t="n">
-        <v>26.36</v>
+        <v>25.9</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.6</v>
+        <v>63.8</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>42.2</v>
+        <v>47.6</v>
       </c>
       <c r="I10" t="n">
-        <v>64.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.47</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>-11.98</v>
+        <v>-9.9</v>
       </c>
       <c r="M10" t="n">
-        <v>26.1</v>
+        <v>26.4</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>27</v>
+        <v>27.4</v>
       </c>
       <c r="I12" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-15.22</v>
+        <v>-17.23</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.72</v>
+        <v>-2.73</v>
       </c>
       <c r="M12" t="n">
-        <v>28.4</v>
+        <v>28.39</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.91</v>
+        <v>-26.58</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>49.1</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>25.4</v>
+        <v>31.5</v>
       </c>
       <c r="I13" t="n">
         <v>26.5</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.48</v>
+        <v>-5.82</v>
       </c>
       <c r="L13" t="n">
-        <v>-18.86</v>
+        <v>-16.38</v>
       </c>
       <c r="M13" t="n">
-        <v>46.46</v>
+        <v>46.5</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.5</v>
+        <v>81.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.29</v>
+        <v>2.79</v>
       </c>
       <c r="L2" t="n">
-        <v>19.69</v>
+        <v>17.03</v>
       </c>
       <c r="M2" t="n">
-        <v>11.75</v>
+        <v>11.73</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.19</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>46.32</v>
+        <v>41.94</v>
       </c>
       <c r="M3" t="n">
-        <v>22.75</v>
+        <v>22.7</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-4.85</v>
+        <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>77.89</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>39.49</v>
+        <v>39.41</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.289999999999999</v>
+        <v>4.48</v>
       </c>
       <c r="L5" t="n">
-        <v>66.11</v>
+        <v>61.87</v>
       </c>
       <c r="M5" t="n">
-        <v>31.48</v>
+        <v>31.46</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>80.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.14</v>
+        <v>2.5</v>
       </c>
       <c r="L6" t="n">
-        <v>13.05</v>
+        <v>12.25</v>
       </c>
       <c r="M6" t="n">
-        <v>14.57</v>
+        <v>14.55</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>39.3</v>
+        <v>38.5</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.59</v>
+        <v>-7.23</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.96</v>
+        <v>-4.09</v>
       </c>
       <c r="M7" t="n">
-        <v>11.5</v>
+        <v>11.48</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-10.29</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65.3</v>
+        <v>64.2</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>49.6</v>
+        <v>46.3</v>
       </c>
       <c r="I8" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.32</v>
+        <v>-5.41</v>
       </c>
       <c r="L8" t="n">
-        <v>5.19</v>
+        <v>4.01</v>
       </c>
       <c r="M8" t="n">
-        <v>18.06</v>
+        <v>18.15</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64.40000000000001</v>
+        <v>61.7</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>59.3</v>
+        <v>41.2</v>
       </c>
       <c r="I9" t="n">
-        <v>64.59999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4.79</v>
+        <v>-1.53</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.33</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>25.9</v>
+        <v>26.38</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63.8</v>
+        <v>59.3</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>47.6</v>
+        <v>44.3</v>
       </c>
       <c r="I10" t="n">
-        <v>62.1</v>
+        <v>64.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.9</v>
+        <v>-10.97</v>
       </c>
       <c r="M10" t="n">
-        <v>26.4</v>
+        <v>25.97</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>27.4</v>
+        <v>27.8</v>
       </c>
       <c r="I12" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-17.23</v>
+        <v>-14.82</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.73</v>
+        <v>-6.27</v>
       </c>
       <c r="M12" t="n">
-        <v>28.39</v>
+        <v>28.37</v>
       </c>
       <c r="N12" t="n">
         <v>-26.58</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.1</v>
+        <v>47.4</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>31.5</v>
+        <v>26.7</v>
       </c>
       <c r="I13" t="n">
         <v>26.5</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-5.82</v>
+        <v>-8.77</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.38</v>
+        <v>-18.23</v>
       </c>
       <c r="M13" t="n">
-        <v>46.5</v>
+        <v>46.43</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="L2" t="n">
-        <v>17.03</v>
+        <v>16.91</v>
       </c>
       <c r="M2" t="n">
         <v>11.73</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="L3" t="n">
-        <v>41.94</v>
+        <v>42.28</v>
       </c>
       <c r="M3" t="n">
         <v>22.7</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.82</v>
+        <v>1.14</v>
       </c>
       <c r="L4" t="n">
-        <v>68.79000000000001</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>39.41</v>
+        <v>39.42</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4.48</v>
+        <v>5.32</v>
       </c>
       <c r="L5" t="n">
-        <v>61.87</v>
+        <v>63.18</v>
       </c>
       <c r="M5" t="n">
-        <v>31.46</v>
+        <v>31.43</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>77.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="L6" t="n">
-        <v>12.25</v>
+        <v>11.72</v>
       </c>
       <c r="M6" t="n">
-        <v>14.55</v>
+        <v>14.54</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>38.5</v>
+        <v>38.9</v>
       </c>
       <c r="I7" t="n">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.23</v>
+        <v>-7</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.09</v>
+        <v>-3.84</v>
       </c>
       <c r="M7" t="n">
         <v>11.48</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.29</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="I8" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.41</v>
+        <v>-5.46</v>
       </c>
       <c r="L8" t="n">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="M8" t="n">
-        <v>18.15</v>
+        <v>18.16</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.7</v>
+        <v>61.2</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>41.2</v>
+        <v>39.8</v>
       </c>
       <c r="I9" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-1.53</v>
+        <v>-2.32</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.880000000000001</v>
+        <v>-10.61</v>
       </c>
       <c r="M9" t="n">
-        <v>26.38</v>
+        <v>26.43</v>
       </c>
       <c r="N9" t="n">
         <v>-25.29</v>
@@ -1410,7 +1410,7 @@
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="I10" t="n">
         <v>64.5</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="L10" t="n">
-        <v>-10.97</v>
+        <v>-10.93</v>
       </c>
       <c r="M10" t="n">
-        <v>25.97</v>
+        <v>25.96</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>27.8</v>
+        <v>29</v>
       </c>
       <c r="I12" t="n">
         <v>58.5</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-14.82</v>
+        <v>-14.25</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.27</v>
+        <v>-5.65</v>
       </c>
       <c r="M12" t="n">
-        <v>28.37</v>
+        <v>28.35</v>
       </c>
       <c r="N12" t="n">
         <v>-26.58</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.4</v>
+        <v>46.9</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>26.7</v>
+        <v>25.1</v>
       </c>
       <c r="I13" t="n">
         <v>26.5</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-8.77</v>
+        <v>-9.68</v>
       </c>
       <c r="L13" t="n">
-        <v>-18.23</v>
+        <v>-19.04</v>
       </c>
       <c r="M13" t="n">
-        <v>46.43</v>
+        <v>46.47</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.68</v>
+        <v>2.51</v>
       </c>
       <c r="L2" t="n">
-        <v>16.91</v>
+        <v>16.71</v>
       </c>
       <c r="M2" t="n">
         <v>11.73</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>9.08</v>
       </c>
       <c r="L3" t="n">
-        <v>42.28</v>
+        <v>41.21</v>
       </c>
       <c r="M3" t="n">
         <v>22.7</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="L4" t="n">
-        <v>69.31999999999999</v>
+        <v>64.63</v>
       </c>
       <c r="M4" t="n">
-        <v>39.42</v>
+        <v>39.47</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.32</v>
+        <v>8.84</v>
       </c>
       <c r="L5" t="n">
-        <v>63.18</v>
+        <v>64.11</v>
       </c>
       <c r="M5" t="n">
-        <v>31.43</v>
+        <v>31.38</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>76.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="L6" t="n">
-        <v>11.72</v>
+        <v>12.37</v>
       </c>
       <c r="M6" t="n">
-        <v>14.54</v>
+        <v>14.55</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7</v>
+        <v>-7.07</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.84</v>
+        <v>-3.92</v>
       </c>
       <c r="M7" t="n">
         <v>11.48</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>46.2</v>
+        <v>44.8</v>
       </c>
       <c r="I8" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.46</v>
+        <v>-6.18</v>
       </c>
       <c r="L8" t="n">
-        <v>3.94</v>
+        <v>3.19</v>
       </c>
       <c r="M8" t="n">
-        <v>18.16</v>
+        <v>18.09</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.2</v>
+        <v>59.8</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>39.8</v>
+        <v>35.8</v>
       </c>
       <c r="I9" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.32</v>
+        <v>-5.58</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.61</v>
+        <v>-10.74</v>
       </c>
       <c r="M9" t="n">
-        <v>26.43</v>
+        <v>26.34</v>
       </c>
       <c r="N9" t="n">
         <v>-25.29</v>
@@ -1404,16 +1404,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.3</v>
+        <v>58.6</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>44.4</v>
+        <v>42.2</v>
       </c>
       <c r="I10" t="n">
-        <v>64.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.67</v>
+        <v>0.47</v>
       </c>
       <c r="L10" t="n">
-        <v>-10.93</v>
+        <v>-11.98</v>
       </c>
       <c r="M10" t="n">
-        <v>25.96</v>
+        <v>26.1</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.1</v>
+        <v>49.4</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>58.5</v>
+        <v>58.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-14.25</v>
+        <v>-15.22</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.65</v>
+        <v>-6.72</v>
       </c>
       <c r="M12" t="n">
-        <v>28.35</v>
+        <v>28.4</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.58</v>
+        <v>-26.91</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="I13" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.68</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.04</v>
+        <v>-19.14</v>
       </c>
       <c r="M13" t="n">
-        <v>46.47</v>
+        <v>46.37</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.2</v>
+        <v>90.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="L2" t="n">
-        <v>16.71</v>
+        <v>17.26</v>
       </c>
       <c r="M2" t="n">
         <v>11.73</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.08</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>41.21</v>
+        <v>42.33</v>
       </c>
       <c r="M3" t="n">
-        <v>22.7</v>
+        <v>22.72</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-1.66</v>
+        <v>-0.45</v>
       </c>
       <c r="L4" t="n">
-        <v>64.63</v>
+        <v>70.64</v>
       </c>
       <c r="M4" t="n">
-        <v>39.47</v>
+        <v>39.54</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.84</v>
+        <v>9.74</v>
       </c>
       <c r="L5" t="n">
-        <v>64.11</v>
+        <v>65.47</v>
       </c>
       <c r="M5" t="n">
-        <v>31.38</v>
+        <v>31.45</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>77.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="L6" t="n">
-        <v>12.37</v>
+        <v>11.92</v>
       </c>
       <c r="M6" t="n">
-        <v>14.55</v>
+        <v>14.53</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>38.8</v>
+        <v>38.3</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1109,10 +1109,10 @@
         <v>-7.07</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.92</v>
+        <v>-4.59</v>
       </c>
       <c r="M7" t="n">
-        <v>11.48</v>
+        <v>11.51</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.7</v>
+        <v>63.3</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>44.8</v>
+        <v>43.8</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.18</v>
+        <v>-6.71</v>
       </c>
       <c r="L8" t="n">
-        <v>3.19</v>
+        <v>2.61</v>
       </c>
       <c r="M8" t="n">
-        <v>18.09</v>
+        <v>18.14</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.8</v>
+        <v>60.2</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>35.8</v>
+        <v>36.9</v>
       </c>
       <c r="I9" t="n">
         <v>62.2</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-5.58</v>
+        <v>-4.99</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.74</v>
+        <v>-10.19</v>
       </c>
       <c r="M9" t="n">
-        <v>26.34</v>
+        <v>26.35</v>
       </c>
       <c r="N9" t="n">
         <v>-25.29</v>
@@ -1404,16 +1404,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.6</v>
+        <v>59.7</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>42.2</v>
+        <v>45.5</v>
       </c>
       <c r="I10" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.47</v>
+        <v>1.36</v>
       </c>
       <c r="L10" t="n">
-        <v>-11.98</v>
+        <v>-8.77</v>
       </c>
       <c r="M10" t="n">
-        <v>26.1</v>
+        <v>26.16</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.4</v>
+        <v>50.8</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>27</v>
+        <v>31.2</v>
       </c>
       <c r="I12" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-15.22</v>
+        <v>-13.49</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.72</v>
+        <v>-3.73</v>
       </c>
       <c r="M12" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1709,10 +1709,10 @@
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="I13" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.720000000000001</v>
+        <v>-9.57</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.14</v>
+        <v>-19</v>
       </c>
       <c r="M13" t="n">
-        <v>46.37</v>
+        <v>46.46</v>
       </c>
       <c r="N13" t="n">
         <v>-36.07</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="L2" t="n">
-        <v>17.26</v>
+        <v>17.3</v>
       </c>
       <c r="M2" t="n">
-        <v>11.73</v>
+        <v>11.74</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.720000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="L3" t="n">
-        <v>42.33</v>
+        <v>42.78</v>
       </c>
       <c r="M3" t="n">
-        <v>22.72</v>
+        <v>22.74</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-0.45</v>
+        <v>-0.75</v>
       </c>
       <c r="L4" t="n">
-        <v>70.64</v>
+        <v>70.14</v>
       </c>
       <c r="M4" t="n">
-        <v>39.54</v>
+        <v>39.53</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.74</v>
+        <v>11.6</v>
       </c>
       <c r="L5" t="n">
-        <v>65.47</v>
+        <v>68.28</v>
       </c>
       <c r="M5" t="n">
-        <v>31.45</v>
+        <v>31.55</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -990,7 +990,7 @@
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="L6" t="n">
-        <v>11.92</v>
+        <v>11.96</v>
       </c>
       <c r="M6" t="n">
         <v>14.53</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>38.3</v>
+        <v>37.8</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.07</v>
+        <v>-7.34</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.59</v>
+        <v>-4.87</v>
       </c>
       <c r="M7" t="n">
-        <v>11.51</v>
+        <v>11.49</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.71</v>
+        <v>-6.79</v>
       </c>
       <c r="L8" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="M8" t="n">
         <v>18.14</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.2</v>
+        <v>60.3</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="I9" t="n">
         <v>62.2</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-4.99</v>
+        <v>-4.85</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.19</v>
+        <v>-10.05</v>
       </c>
       <c r="M9" t="n">
         <v>26.35</v>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.7</v>
+        <v>59.1</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>45.5</v>
+        <v>43.9</v>
       </c>
       <c r="I10" t="n">
         <v>64.3</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.36</v>
+        <v>0.51</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.77</v>
+        <v>-9.52</v>
       </c>
       <c r="M10" t="n">
-        <v>26.16</v>
+        <v>26.11</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>31.2</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
         <v>58.1</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-13.49</v>
+        <v>-14.1</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.73</v>
+        <v>-4.41</v>
       </c>
       <c r="M12" t="n">
-        <v>28.5</v>
+        <v>28.44</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>25.2</v>
+        <v>24.5</v>
       </c>
       <c r="I13" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.57</v>
+        <v>-9.98</v>
       </c>
       <c r="L13" t="n">
-        <v>-19</v>
+        <v>-19.37</v>
       </c>
       <c r="M13" t="n">
         <v>46.46</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.07</v>
+        <v>-36.24</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="L2" t="n">
-        <v>17.3</v>
+        <v>17.04</v>
       </c>
       <c r="M2" t="n">
-        <v>11.74</v>
+        <v>11.73</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10.07</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>42.78</v>
+        <v>41.88</v>
       </c>
       <c r="M3" t="n">
-        <v>22.74</v>
+        <v>22.71</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-0.75</v>
+        <v>-0.47</v>
       </c>
       <c r="L4" t="n">
-        <v>70.14</v>
+        <v>70.61</v>
       </c>
       <c r="M4" t="n">
-        <v>39.53</v>
+        <v>39.54</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.4</v>
+        <v>58.6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.6</v>
+        <v>8.84</v>
       </c>
       <c r="L5" t="n">
-        <v>68.28</v>
+        <v>64.11</v>
       </c>
       <c r="M5" t="n">
-        <v>31.55</v>
+        <v>31.43</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.7</v>
+        <v>79.5</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>77.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.2</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="L6" t="n">
-        <v>11.96</v>
+        <v>11.67</v>
       </c>
       <c r="M6" t="n">
-        <v>14.53</v>
+        <v>14.54</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.09999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>37.8</v>
+        <v>36.9</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.34</v>
+        <v>-7.78</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.87</v>
+        <v>-5.31</v>
       </c>
       <c r="M7" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.2</v>
+        <v>63.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>43.6</v>
+        <v>44.8</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.79</v>
+        <v>-6.18</v>
       </c>
       <c r="L8" t="n">
-        <v>2.52</v>
+        <v>3.19</v>
       </c>
       <c r="M8" t="n">
-        <v>18.14</v>
+        <v>18.12</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.3</v>
+        <v>59.8</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>37.1</v>
+        <v>35.8</v>
       </c>
       <c r="I9" t="n">
         <v>62.2</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-4.85</v>
+        <v>-5.58</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.05</v>
+        <v>-10.74</v>
       </c>
       <c r="M9" t="n">
-        <v>26.35</v>
+        <v>26.37</v>
       </c>
       <c r="N9" t="n">
         <v>-25.29</v>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
       <c r="I10" t="n">
         <v>64.3</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.52</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>26.11</v>
+        <v>26.12</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I12" t="n">
-        <v>58.1</v>
+        <v>58.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-14.1</v>
+        <v>-14.62</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.41</v>
+        <v>-4.99</v>
       </c>
       <c r="M12" t="n">
-        <v>28.44</v>
+        <v>28.41</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="I13" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.98</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.37</v>
+        <v>-19.14</v>
       </c>
       <c r="M13" t="n">
         <v>46.46</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.24</v>
+        <v>-36.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.5</v>
+        <v>80</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.12</v>
+        <v>1.49</v>
       </c>
       <c r="L2" t="n">
-        <v>17.04</v>
+        <v>17.48</v>
       </c>
       <c r="M2" t="n">
-        <v>11.73</v>
+        <v>11.72</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="L3" t="n">
-        <v>41.88</v>
+        <v>44.43</v>
       </c>
       <c r="M3" t="n">
-        <v>22.71</v>
+        <v>22.73</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-0.47</v>
+        <v>-0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>70.61</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>39.54</v>
+        <v>39.52</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.84</v>
+        <v>11.84</v>
       </c>
       <c r="L5" t="n">
-        <v>64.11</v>
+        <v>62.02</v>
       </c>
       <c r="M5" t="n">
-        <v>31.43</v>
+        <v>31.48</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>76.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>89.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="L6" t="n">
-        <v>11.67</v>
+        <v>12.71</v>
       </c>
       <c r="M6" t="n">
-        <v>14.54</v>
+        <v>14.02</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>36.9</v>
+        <v>37.6</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.78</v>
+        <v>-7.22</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.31</v>
+        <v>-5.38</v>
       </c>
       <c r="M7" t="n">
-        <v>11.48</v>
+        <v>11.46</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.7</v>
+        <v>62.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>44.8</v>
+        <v>41.9</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.18</v>
+        <v>-6.89</v>
       </c>
       <c r="L8" t="n">
-        <v>3.19</v>
+        <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>18.12</v>
+        <v>18.1</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>59.8</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>35.8</v>
+        <v>45.8</v>
       </c>
       <c r="I9" t="n">
-        <v>62.2</v>
+        <v>64.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-5.58</v>
+        <v>1.33</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.74</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>26.37</v>
+        <v>26.12</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.2</v>
+        <v>58.7</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>44.2</v>
+        <v>32.5</v>
       </c>
       <c r="I10" t="n">
-        <v>64.3</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.68</v>
+        <v>-5.34</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.380000000000001</v>
+        <v>-15.87</v>
       </c>
       <c r="M10" t="n">
-        <v>26.12</v>
+        <v>26.36</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>29</v>
+        <v>28.3</v>
       </c>
       <c r="I12" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-14.62</v>
+        <v>-16.58</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.99</v>
+        <v>-2.57</v>
       </c>
       <c r="M12" t="n">
-        <v>28.41</v>
+        <v>28.24</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.8</v>
+        <v>44.2</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>24.9</v>
+        <v>17.6</v>
       </c>
       <c r="I13" t="n">
-        <v>26.5</v>
+        <v>25.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.720000000000001</v>
+        <v>-11.95</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.14</v>
+        <v>-25.77</v>
       </c>
       <c r="M13" t="n">
-        <v>46.46</v>
+        <v>46.48</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.07</v>
+        <v>-37.29</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="L2" t="n">
-        <v>17.48</v>
+        <v>17.69</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72</v>
+        <v>11.71</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.27</v>
+        <v>9.33</v>
       </c>
       <c r="L3" t="n">
-        <v>44.43</v>
+        <v>44.51</v>
       </c>
       <c r="M3" t="n">
         <v>22.73</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-0.82</v>
+        <v>-0.39</v>
       </c>
       <c r="L4" t="n">
-        <v>69.95999999999999</v>
+        <v>70.69</v>
       </c>
       <c r="M4" t="n">
         <v>39.52</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.84</v>
+        <v>11.63</v>
       </c>
       <c r="L5" t="n">
-        <v>62.02</v>
+        <v>61.71</v>
       </c>
       <c r="M5" t="n">
-        <v>31.48</v>
+        <v>31.47</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>77.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="I6" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="L6" t="n">
-        <v>12.71</v>
+        <v>12.94</v>
       </c>
       <c r="M6" t="n">
-        <v>14.02</v>
+        <v>14.01</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.22</v>
+        <v>-6.67</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.38</v>
+        <v>-4.81</v>
       </c>
       <c r="M7" t="n">
-        <v>11.46</v>
+        <v>11.47</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.7</v>
+        <v>62.4</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.89</v>
+        <v>-7.26</v>
       </c>
       <c r="L8" t="n">
-        <v>0.27</v>
+        <v>-0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>18.1</v>
+        <v>18.12</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.8</v>
+        <v>60.1</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>45.8</v>
+        <v>46.6</v>
       </c>
       <c r="I9" t="n">
         <v>64.3</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.279999999999999</v>
+        <v>-7.87</v>
       </c>
       <c r="M9" t="n">
-        <v>26.12</v>
+        <v>26.13</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.7</v>
+        <v>58.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-5.34</v>
+        <v>-5.81</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.87</v>
+        <v>-16.29</v>
       </c>
       <c r="M10" t="n">
         <v>26.36</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.9</v>
+        <v>50.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="I12" t="n">
         <v>58.4</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-16.58</v>
+        <v>-16.34</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.57</v>
+        <v>-2.3</v>
       </c>
       <c r="M12" t="n">
         <v>28.24</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44.2</v>
+        <v>43.2</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>17.6</v>
+        <v>15.2</v>
       </c>
       <c r="I13" t="n">
-        <v>25.6</v>
+        <v>24.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.95</v>
+        <v>-13.32</v>
       </c>
       <c r="L13" t="n">
-        <v>-25.77</v>
+        <v>-26.93</v>
       </c>
       <c r="M13" t="n">
-        <v>46.48</v>
+        <v>46.57</v>
       </c>
       <c r="N13" t="n">
-        <v>-37.29</v>
+        <v>-38.27</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="L2" t="n">
-        <v>17.69</v>
+        <v>17.97</v>
       </c>
       <c r="M2" t="n">
         <v>11.71</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>44.51</v>
+        <v>43.8</v>
       </c>
       <c r="M3" t="n">
-        <v>22.73</v>
+        <v>22.71</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-0.39</v>
+        <v>-1.23</v>
       </c>
       <c r="L4" t="n">
-        <v>70.69</v>
+        <v>69.25</v>
       </c>
       <c r="M4" t="n">
         <v>39.52</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.63</v>
+        <v>12.41</v>
       </c>
       <c r="L5" t="n">
-        <v>61.71</v>
+        <v>62.85</v>
       </c>
       <c r="M5" t="n">
-        <v>31.47</v>
+        <v>31.52</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>77.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>90</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.28</v>
+        <v>3.09</v>
       </c>
       <c r="L6" t="n">
-        <v>12.94</v>
+        <v>13.83</v>
       </c>
       <c r="M6" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.67</v>
+        <v>-6.7</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.81</v>
+        <v>-4.84</v>
       </c>
       <c r="M7" t="n">
         <v>11.47</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>41.2</v>
+        <v>42.5</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.26</v>
+        <v>-6.62</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>18.12</v>
+        <v>18.09</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.1</v>
+        <v>59.4</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>46.6</v>
+        <v>44.7</v>
       </c>
       <c r="I9" t="n">
         <v>64.3</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.78</v>
+        <v>0.74</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.87</v>
+        <v>-8.82</v>
       </c>
       <c r="M9" t="n">
-        <v>26.13</v>
+        <v>26.11</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.4</v>
+        <v>58.9</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>31.6</v>
+        <v>33.1</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-5.81</v>
+        <v>-5</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.29</v>
+        <v>-15.57</v>
       </c>
       <c r="M10" t="n">
-        <v>26.36</v>
+        <v>26.37</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>28.8</v>
+        <v>30.2</v>
       </c>
       <c r="I12" t="n">
         <v>58.4</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-16.34</v>
+        <v>-15.63</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.3</v>
+        <v>-1.46</v>
       </c>
       <c r="M12" t="n">
         <v>28.24</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43.2</v>
+        <v>45.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>15.2</v>
+        <v>20.3</v>
       </c>
       <c r="I13" t="n">
-        <v>24.8</v>
+        <v>26.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-13.32</v>
+        <v>-10.46</v>
       </c>
       <c r="L13" t="n">
-        <v>-26.93</v>
+        <v>-24.52</v>
       </c>
       <c r="M13" t="n">
-        <v>46.57</v>
+        <v>46.44</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.27</v>
+        <v>-36.24</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.3</v>
+        <v>90.7</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.91</v>
+        <v>4.13</v>
       </c>
       <c r="L2" t="n">
-        <v>17.97</v>
+        <v>15.9</v>
       </c>
       <c r="M2" t="n">
-        <v>11.71</v>
+        <v>11.75</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.800000000000001</v>
+        <v>15.32</v>
       </c>
       <c r="L3" t="n">
-        <v>43.8</v>
+        <v>42.37</v>
       </c>
       <c r="M3" t="n">
-        <v>22.71</v>
+        <v>22.83</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-1.23</v>
+        <v>11.58</v>
       </c>
       <c r="L4" t="n">
-        <v>69.25</v>
+        <v>66</v>
       </c>
       <c r="M4" t="n">
-        <v>39.52</v>
+        <v>39.65</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12.41</v>
+        <v>10.21</v>
       </c>
       <c r="L5" t="n">
-        <v>62.85</v>
+        <v>61.99</v>
       </c>
       <c r="M5" t="n">
-        <v>31.52</v>
+        <v>31.54</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>79.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>90</v>
+        <v>89.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.09</v>
+        <v>-0.15</v>
       </c>
       <c r="L6" t="n">
-        <v>13.83</v>
+        <v>10.05</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>14.09</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.40000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>38.6</v>
+        <v>39.5</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.7</v>
+        <v>-6.67</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.84</v>
+        <v>-3.52</v>
       </c>
       <c r="M7" t="n">
-        <v>11.47</v>
+        <v>11.51</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.9</v>
+        <v>62.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42.5</v>
+        <v>41.8</v>
       </c>
       <c r="I8" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.62</v>
+        <v>-7.34</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="M8" t="n">
-        <v>18.09</v>
+        <v>18.08</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.4</v>
+        <v>60.4</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>44.7</v>
+        <v>47.5</v>
       </c>
       <c r="I9" t="n">
         <v>64.3</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.74</v>
+        <v>2.82</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.82</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>26.11</v>
+        <v>26.17</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.9</v>
+        <v>58.3</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.1</v>
+        <v>31.3</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-5</v>
+        <v>-6.15</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.57</v>
+        <v>-16.12</v>
       </c>
       <c r="M10" t="n">
-        <v>26.37</v>
+        <v>26.35</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.5</v>
+        <v>52.9</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30.2</v>
+        <v>37.1</v>
       </c>
       <c r="I12" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-15.63</v>
+        <v>-8.92</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.46</v>
+        <v>-3.18</v>
       </c>
       <c r="M12" t="n">
-        <v>28.24</v>
+        <v>28.3</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>45.3</v>
+        <v>45.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>20.3</v>
+        <v>21.8</v>
       </c>
       <c r="I13" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.46</v>
+        <v>-10.38</v>
       </c>
       <c r="L13" t="n">
-        <v>-24.52</v>
+        <v>-22.48</v>
       </c>
       <c r="M13" t="n">
         <v>46.44</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.24</v>
+        <v>-36.39</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.7</v>
+        <v>90.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.13</v>
+        <v>3.83</v>
       </c>
       <c r="L2" t="n">
-        <v>15.9</v>
+        <v>15.57</v>
       </c>
       <c r="M2" t="n">
-        <v>11.75</v>
+        <v>11.73</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>15.32</v>
+        <v>14.93</v>
       </c>
       <c r="L3" t="n">
-        <v>42.37</v>
+        <v>41.89</v>
       </c>
       <c r="M3" t="n">
-        <v>22.83</v>
+        <v>22.79</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.58</v>
+        <v>11.43</v>
       </c>
       <c r="L4" t="n">
-        <v>66</v>
+        <v>65.78</v>
       </c>
       <c r="M4" t="n">
-        <v>39.65</v>
+        <v>39.64</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10.21</v>
+        <v>10.44</v>
       </c>
       <c r="L5" t="n">
-        <v>61.99</v>
+        <v>62.33</v>
       </c>
       <c r="M5" t="n">
         <v>31.54</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="I6" t="n">
         <v>89.8</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="L6" t="n">
-        <v>10.05</v>
+        <v>10.03</v>
       </c>
       <c r="M6" t="n">
-        <v>14.09</v>
+        <v>14.1</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.67</v>
+        <v>-6.53</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.52</v>
+        <v>-3.37</v>
       </c>
       <c r="M7" t="n">
-        <v>11.51</v>
+        <v>11.52</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1200,7 +1200,7 @@
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="I8" t="n">
         <v>77.09999999999999</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.34</v>
+        <v>-7.21</v>
       </c>
       <c r="L8" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>18.08</v>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.4</v>
+        <v>59.5</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>47.5</v>
+        <v>45.1</v>
       </c>
       <c r="I9" t="n">
         <v>64.3</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.82</v>
+        <v>1.52</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.390000000000001</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>26.17</v>
+        <v>26.11</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-6.15</v>
+        <v>-6.14</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.12</v>
+        <v>-16.11</v>
       </c>
       <c r="M10" t="n">
         <v>26.35</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>37.1</v>
+        <v>36</v>
       </c>
       <c r="I12" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.92</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.18</v>
+        <v>-3.76</v>
       </c>
       <c r="M12" t="n">
-        <v>28.3</v>
+        <v>28.27</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>45.7</v>
+        <v>45.2</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>21.8</v>
+        <v>20.4</v>
       </c>
       <c r="I13" t="n">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.38</v>
+        <v>-11.16</v>
       </c>
       <c r="L13" t="n">
-        <v>-22.48</v>
+        <v>-23.16</v>
       </c>
       <c r="M13" t="n">
-        <v>46.44</v>
+        <v>46.46</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.39</v>
+        <v>-36.95</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.5</v>
+        <v>89.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.83</v>
+        <v>2.77</v>
       </c>
       <c r="L2" t="n">
-        <v>15.57</v>
+        <v>14.38</v>
       </c>
       <c r="M2" t="n">
-        <v>11.73</v>
+        <v>11.71</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14.93</v>
+        <v>12.89</v>
       </c>
       <c r="L3" t="n">
-        <v>41.89</v>
+        <v>39.37</v>
       </c>
       <c r="M3" t="n">
-        <v>22.79</v>
+        <v>22.69</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.1</v>
+        <v>45.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.43</v>
+        <v>7.8</v>
       </c>
       <c r="L4" t="n">
-        <v>65.78</v>
+        <v>60.38</v>
       </c>
       <c r="M4" t="n">
-        <v>39.64</v>
+        <v>39.45</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10.44</v>
+        <v>11.42</v>
       </c>
       <c r="L5" t="n">
-        <v>62.33</v>
+        <v>62.63</v>
       </c>
       <c r="M5" t="n">
         <v>31.54</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>75.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>64.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-0.17</v>
+        <v>0.74</v>
       </c>
       <c r="L6" t="n">
-        <v>10.03</v>
+        <v>11.03</v>
       </c>
       <c r="M6" t="n">
-        <v>14.1</v>
+        <v>14.01</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>39.8</v>
+        <v>37.8</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.53</v>
+        <v>-7.57</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.37</v>
+        <v>-4.44</v>
       </c>
       <c r="M7" t="n">
-        <v>11.52</v>
+        <v>11.47</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="I8" t="n">
         <v>77.09999999999999</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.21</v>
+        <v>-6.36</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>-0.35</v>
       </c>
       <c r="M8" t="n">
         <v>18.08</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.5</v>
+        <v>59.9</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>45.1</v>
+        <v>46.1</v>
       </c>
       <c r="I9" t="n">
         <v>64.3</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.550000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="M9" t="n">
-        <v>26.11</v>
+        <v>26.12</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.4</v>
+        <v>59.2</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>31.4</v>
+        <v>33.8</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-6.14</v>
+        <v>-4.42</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.11</v>
+        <v>-15.63</v>
       </c>
       <c r="M10" t="n">
-        <v>26.35</v>
+        <v>26.33</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.5</v>
+        <v>51.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>32.1</v>
       </c>
       <c r="I12" t="n">
         <v>58.4</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.460000000000001</v>
+        <v>-11.48</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.76</v>
+        <v>-5.9</v>
       </c>
       <c r="M12" t="n">
-        <v>28.27</v>
+        <v>28.25</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>45.2</v>
+        <v>47.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>20.4</v>
+        <v>27.8</v>
       </c>
       <c r="I13" t="n">
-        <v>25.9</v>
+        <v>24.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.16</v>
+        <v>-6.26</v>
       </c>
       <c r="L13" t="n">
-        <v>-23.16</v>
+        <v>-20.98</v>
       </c>
       <c r="M13" t="n">
-        <v>46.46</v>
+        <v>46.51</v>
       </c>
       <c r="N13" t="n">
-        <v>-36.95</v>
+        <v>-38.27</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.77</v>
+        <v>4.43</v>
       </c>
       <c r="L2" t="n">
-        <v>14.38</v>
+        <v>16.38</v>
       </c>
       <c r="M2" t="n">
-        <v>11.71</v>
+        <v>11.78</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.89</v>
+        <v>11.87</v>
       </c>
       <c r="L3" t="n">
-        <v>39.37</v>
+        <v>41.75</v>
       </c>
       <c r="M3" t="n">
-        <v>22.69</v>
+        <v>22.76</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.8</v>
+        <v>3.66</v>
       </c>
       <c r="L4" t="n">
-        <v>60.38</v>
+        <v>58.53</v>
       </c>
       <c r="M4" t="n">
-        <v>39.45</v>
+        <v>39.46</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.42</v>
+        <v>14.98</v>
       </c>
       <c r="L5" t="n">
-        <v>62.63</v>
+        <v>60.03</v>
       </c>
       <c r="M5" t="n">
-        <v>31.54</v>
+        <v>31.6</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79</v>
+        <v>79.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>74.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="I6" t="n">
         <v>90</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.74</v>
+        <v>1.94</v>
       </c>
       <c r="L6" t="n">
-        <v>11.03</v>
+        <v>11.71</v>
       </c>
       <c r="M6" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>37.8</v>
+        <v>41.2</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.57</v>
+        <v>-5.33</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.44</v>
+        <v>-3.39</v>
       </c>
       <c r="M7" t="n">
-        <v>11.47</v>
+        <v>11.54</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.8</v>
+        <v>61.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42.1</v>
+        <v>39.1</v>
       </c>
       <c r="I8" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.36</v>
+        <v>-5.27</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.35</v>
+        <v>-6.48</v>
       </c>
       <c r="M8" t="n">
-        <v>18.08</v>
+        <v>18.09</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>46.1</v>
+        <v>36.4</v>
       </c>
       <c r="I9" t="n">
-        <v>64.3</v>
+        <v>62.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.03</v>
+        <v>-1.34</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.1</v>
+        <v>-17.14</v>
       </c>
       <c r="M9" t="n">
-        <v>26.12</v>
+        <v>26.38</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.2</v>
+        <v>59.9</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>33.8</v>
+        <v>46.1</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.42</v>
+        <v>2.22</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.63</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>26.33</v>
+        <v>26.04</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.2</v>
+        <v>55.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>32.1</v>
+        <v>43.9</v>
       </c>
       <c r="I12" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-11.48</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.9</v>
+        <v>-4.47</v>
       </c>
       <c r="M12" t="n">
-        <v>28.25</v>
+        <v>28.34</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>27.8</v>
+        <v>27.1</v>
       </c>
       <c r="I13" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-6.26</v>
+        <v>-4.96</v>
       </c>
       <c r="L13" t="n">
-        <v>-20.98</v>
+        <v>-24.18</v>
       </c>
       <c r="M13" t="n">
-        <v>46.51</v>
+        <v>46.55</v>
       </c>
       <c r="N13" t="n">
         <v>-38.27</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.8</v>
+        <v>82.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.43</v>
+        <v>4.49</v>
       </c>
       <c r="L2" t="n">
-        <v>16.38</v>
+        <v>15.51</v>
       </c>
       <c r="M2" t="n">
-        <v>11.78</v>
+        <v>11.77</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.87</v>
+        <v>14.63</v>
       </c>
       <c r="L3" t="n">
-        <v>41.75</v>
+        <v>42.5</v>
       </c>
       <c r="M3" t="n">
-        <v>22.76</v>
+        <v>22.79</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.66</v>
+        <v>9.56</v>
       </c>
       <c r="L4" t="n">
-        <v>58.53</v>
+        <v>62.57</v>
       </c>
       <c r="M4" t="n">
-        <v>39.46</v>
+        <v>39.54</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.7</v>
+        <v>76</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>76.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.94</v>
+        <v>0.52</v>
       </c>
       <c r="L6" t="n">
-        <v>11.71</v>
+        <v>10.36</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.2</v>
+        <v>65.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>41.2</v>
+        <v>39</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.33</v>
+        <v>-6.36</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.39</v>
+        <v>-4.86</v>
       </c>
       <c r="M7" t="n">
-        <v>11.54</v>
+        <v>11.53</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.1</v>
+        <v>60.6</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>36.4</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>62.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-1.34</v>
+        <v>4.22</v>
       </c>
       <c r="L9" t="n">
-        <v>-17.14</v>
+        <v>-10.11</v>
       </c>
       <c r="M9" t="n">
-        <v>26.38</v>
+        <v>26.09</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>46.1</v>
+        <v>36.4</v>
       </c>
       <c r="I10" t="n">
-        <v>64.40000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2.22</v>
+        <v>-1.34</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.359999999999999</v>
+        <v>-17.14</v>
       </c>
       <c r="M10" t="n">
-        <v>26.04</v>
+        <v>26.38</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.2</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>43.9</v>
+        <v>37.5</v>
       </c>
       <c r="I12" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.109999999999999</v>
+        <v>-7.65</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.47</v>
+        <v>-4.71</v>
       </c>
       <c r="M12" t="n">
-        <v>28.34</v>
+        <v>28.37</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14.98</v>
+        <v>11.42</v>
       </c>
       <c r="L5" t="n">
-        <v>60.03</v>
+        <v>62.63</v>
       </c>
       <c r="M5" t="n">
-        <v>31.6</v>
+        <v>31.66</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.7</v>
+        <v>62.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>39.1</v>
+        <v>42.1</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.27</v>
+        <v>-6.36</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.48</v>
+        <v>-0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>18.09</v>
+        <v>18.12</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.1</v>
+        <v>59.1</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>36.4</v>
+        <v>33.8</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.34</v>
+        <v>-4.42</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.14</v>
+        <v>-15.63</v>
       </c>
       <c r="M10" t="n">
-        <v>26.38</v>
+        <v>26.42</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>27.1</v>
+        <v>27.8</v>
       </c>
       <c r="I13" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-4.96</v>
+        <v>-6.26</v>
       </c>
       <c r="L13" t="n">
-        <v>-24.18</v>
+        <v>-20.98</v>
       </c>
       <c r="M13" t="n">
-        <v>46.55</v>
+        <v>46.64</v>
       </c>
       <c r="N13" t="n">
         <v>-38.27</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.7</v>
+        <v>91.2</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.49</v>
+        <v>4.86</v>
       </c>
       <c r="L2" t="n">
-        <v>15.51</v>
+        <v>16.86</v>
       </c>
       <c r="M2" t="n">
-        <v>11.77</v>
+        <v>11.82</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14.63</v>
+        <v>12.59</v>
       </c>
       <c r="L3" t="n">
-        <v>42.5</v>
+        <v>42.68</v>
       </c>
       <c r="M3" t="n">
         <v>22.79</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.56</v>
+        <v>3.94</v>
       </c>
       <c r="L4" t="n">
-        <v>62.57</v>
+        <v>58.95</v>
       </c>
       <c r="M4" t="n">
-        <v>39.54</v>
+        <v>39.46</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.42</v>
+        <v>18.88</v>
       </c>
       <c r="L5" t="n">
-        <v>62.63</v>
+        <v>65.44</v>
       </c>
       <c r="M5" t="n">
-        <v>31.66</v>
+        <v>31.78</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>80.2</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>65.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.52</v>
+        <v>2.73</v>
       </c>
       <c r="L6" t="n">
-        <v>10.36</v>
+        <v>12.58</v>
       </c>
       <c r="M6" t="n">
-        <v>14.03</v>
+        <v>14.05</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>39</v>
+        <v>40.8</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.36</v>
+        <v>-5.54</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.86</v>
+        <v>-3.59</v>
       </c>
       <c r="M7" t="n">
         <v>11.53</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.7</v>
+        <v>62.2</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42.1</v>
+        <v>40.5</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.36</v>
+        <v>-4.55</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.35</v>
+        <v>-5.77</v>
       </c>
       <c r="M8" t="n">
-        <v>18.12</v>
+        <v>18.08</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.6</v>
+        <v>59.9</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>46.1</v>
       </c>
       <c r="I9" t="n">
         <v>64.40000000000001</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4.22</v>
+        <v>2.21</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.11</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>26.09</v>
+        <v>26.04</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="I10" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.42</v>
+        <v>-2.73</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.63</v>
+        <v>-18.31</v>
       </c>
       <c r="M10" t="n">
-        <v>26.42</v>
+        <v>26.38</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>55.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>37.5</v>
+        <v>45.4</v>
       </c>
       <c r="I12" t="n">
         <v>58.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.65</v>
+        <v>-8.35</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.71</v>
+        <v>-3.68</v>
       </c>
       <c r="M12" t="n">
-        <v>28.37</v>
+        <v>28.39</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.5</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>27.8</v>
+        <v>32.3</v>
       </c>
       <c r="I13" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-6.26</v>
+        <v>-2</v>
       </c>
       <c r="L13" t="n">
-        <v>-20.98</v>
+        <v>-21.83</v>
       </c>
       <c r="M13" t="n">
-        <v>46.64</v>
+        <v>46.69</v>
       </c>
       <c r="N13" t="n">
         <v>-38.27</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="L2" t="n">
-        <v>16.86</v>
+        <v>16.83</v>
       </c>
       <c r="M2" t="n">
         <v>11.82</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.59</v>
+        <v>12.71</v>
       </c>
       <c r="L3" t="n">
-        <v>42.68</v>
+        <v>42.82</v>
       </c>
       <c r="M3" t="n">
-        <v>22.79</v>
+        <v>22.8</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="L4" t="n">
-        <v>58.95</v>
+        <v>58.65</v>
       </c>
       <c r="M4" t="n">
         <v>39.46</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.1</v>
+        <v>58.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>18.88</v>
+        <v>17.39</v>
       </c>
       <c r="L5" t="n">
-        <v>65.44</v>
+        <v>63.37</v>
       </c>
       <c r="M5" t="n">
-        <v>31.78</v>
+        <v>31.67</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.2</v>
+        <v>79.8</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>78.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="L6" t="n">
-        <v>12.58</v>
+        <v>11.94</v>
       </c>
       <c r="M6" t="n">
-        <v>14.05</v>
+        <v>14.01</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>40.8</v>
+        <v>41.2</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.54</v>
+        <v>-5.35</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.59</v>
+        <v>-3.4</v>
       </c>
       <c r="M7" t="n">
-        <v>11.53</v>
+        <v>11.54</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.55</v>
+        <v>-4.43</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.77</v>
+        <v>-5.65</v>
       </c>
       <c r="M8" t="n">
-        <v>18.08</v>
+        <v>18.09</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="I9" t="n">
         <v>64.40000000000001</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.369999999999999</v>
+        <v>-9.18</v>
       </c>
       <c r="M9" t="n">
         <v>26.04</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="I10" t="n">
         <v>62.2</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-2.73</v>
+        <v>-2.94</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.31</v>
+        <v>-18.49</v>
       </c>
       <c r="M10" t="n">
         <v>26.38</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>45.4</v>
+        <v>45.1</v>
       </c>
       <c r="I12" t="n">
         <v>58.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.35</v>
+        <v>-8.48</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.68</v>
+        <v>-3.82</v>
       </c>
       <c r="M12" t="n">
-        <v>28.39</v>
+        <v>28.38</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>49.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>32.3</v>
+        <v>34.8</v>
       </c>
       <c r="I13" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-2</v>
+        <v>-0.58</v>
       </c>
       <c r="L13" t="n">
-        <v>-21.83</v>
+        <v>-20.69</v>
       </c>
       <c r="M13" t="n">
-        <v>46.69</v>
+        <v>46.83</v>
       </c>
       <c r="N13" t="n">
         <v>-38.27</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>83.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.83</v>
+        <v>4.43</v>
       </c>
       <c r="L2" t="n">
-        <v>16.83</v>
+        <v>16.38</v>
       </c>
       <c r="M2" t="n">
-        <v>11.82</v>
+        <v>11.78</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.71</v>
+        <v>11.87</v>
       </c>
       <c r="L3" t="n">
-        <v>42.82</v>
+        <v>41.75</v>
       </c>
       <c r="M3" t="n">
-        <v>22.8</v>
+        <v>22.76</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="L4" t="n">
-        <v>58.65</v>
+        <v>58.53</v>
       </c>
       <c r="M4" t="n">
         <v>39.46</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>17.39</v>
+        <v>14.98</v>
       </c>
       <c r="L5" t="n">
-        <v>63.37</v>
+        <v>60.03</v>
       </c>
       <c r="M5" t="n">
-        <v>31.67</v>
+        <v>31.6</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>76.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="I6" t="n">
         <v>90</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="L6" t="n">
-        <v>11.94</v>
+        <v>11.71</v>
       </c>
       <c r="M6" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.35</v>
+        <v>-5.33</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.4</v>
+        <v>-3.39</v>
       </c>
       <c r="M7" t="n">
         <v>11.54</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.3</v>
+        <v>61.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>40.7</v>
+        <v>39.1</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.43</v>
+        <v>-5.27</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.65</v>
+        <v>-6.48</v>
       </c>
       <c r="M8" t="n">
         <v>18.09</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>46.5</v>
+        <v>36.4</v>
       </c>
       <c r="I9" t="n">
-        <v>64.40000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.42</v>
+        <v>-1.34</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.18</v>
+        <v>-17.14</v>
       </c>
       <c r="M9" t="n">
-        <v>26.04</v>
+        <v>26.38</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.1</v>
+        <v>59.9</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>33.5</v>
+        <v>46.1</v>
       </c>
       <c r="I10" t="n">
-        <v>62.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-2.94</v>
+        <v>2.22</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.49</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>26.38</v>
+        <v>26.04</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.6</v>
+        <v>55.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>45.1</v>
+        <v>43.9</v>
       </c>
       <c r="I12" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.48</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.82</v>
+        <v>-4.47</v>
       </c>
       <c r="M12" t="n">
-        <v>28.38</v>
+        <v>28.34</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.8</v>
+        <v>47.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>34.8</v>
+        <v>27.1</v>
       </c>
       <c r="I13" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-0.58</v>
+        <v>-4.96</v>
       </c>
       <c r="L13" t="n">
-        <v>-20.69</v>
+        <v>-24.18</v>
       </c>
       <c r="M13" t="n">
-        <v>46.83</v>
+        <v>46.55</v>
       </c>
       <c r="N13" t="n">
         <v>-38.27</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.8</v>
+        <v>82.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.43</v>
+        <v>3.97</v>
       </c>
       <c r="L2" t="n">
-        <v>16.38</v>
+        <v>16.34</v>
       </c>
       <c r="M2" t="n">
         <v>11.78</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.87</v>
+        <v>12.35</v>
       </c>
       <c r="L3" t="n">
-        <v>41.75</v>
+        <v>41.55</v>
       </c>
       <c r="M3" t="n">
-        <v>22.76</v>
+        <v>22.74</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.66</v>
+        <v>3.77</v>
       </c>
       <c r="L4" t="n">
-        <v>58.53</v>
+        <v>57.01</v>
       </c>
       <c r="M4" t="n">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14.98</v>
+        <v>11.41</v>
       </c>
       <c r="L5" t="n">
-        <v>60.03</v>
+        <v>67.39</v>
       </c>
       <c r="M5" t="n">
-        <v>31.6</v>
+        <v>31.54</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>76.5</v>
+        <v>81.7</v>
       </c>
       <c r="I6" t="n">
-        <v>90</v>
+        <v>89.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.94</v>
+        <v>4.58</v>
       </c>
       <c r="L6" t="n">
-        <v>11.71</v>
+        <v>14.62</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>14.12</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>41.2</v>
+        <v>43.6</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.33</v>
+        <v>-4.55</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.39</v>
+        <v>-1.39</v>
       </c>
       <c r="M7" t="n">
-        <v>11.54</v>
+        <v>11.53</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.7</v>
+        <v>60.4</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>39.1</v>
+        <v>35.2</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.27</v>
+        <v>-7.62</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.48</v>
+        <v>-8.02</v>
       </c>
       <c r="M8" t="n">
-        <v>18.09</v>
+        <v>18.13</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>36.4</v>
+        <v>46.4</v>
       </c>
       <c r="I9" t="n">
-        <v>62.2</v>
+        <v>64.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-1.34</v>
+        <v>2.19</v>
       </c>
       <c r="L9" t="n">
-        <v>-17.14</v>
+        <v>-8.93</v>
       </c>
       <c r="M9" t="n">
-        <v>26.38</v>
+        <v>26.02</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.29</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.9</v>
+        <v>57.8</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>46.1</v>
+        <v>30.2</v>
       </c>
       <c r="I10" t="n">
-        <v>64.40000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2.22</v>
+        <v>-4.66</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.359999999999999</v>
+        <v>-20.32</v>
       </c>
       <c r="M10" t="n">
-        <v>26.04</v>
+        <v>26.77</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.2</v>
+        <v>55.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>43.9</v>
+        <v>45</v>
       </c>
       <c r="I12" t="n">
         <v>58.3</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.47</v>
+        <v>-4.26</v>
       </c>
       <c r="M12" t="n">
-        <v>28.34</v>
+        <v>28.33</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47.3</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>27.1</v>
+        <v>26.4</v>
       </c>
       <c r="I13" t="n">
         <v>24.8</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-4.96</v>
+        <v>-6.58</v>
       </c>
       <c r="L13" t="n">
-        <v>-24.18</v>
+        <v>-22.48</v>
       </c>
       <c r="M13" t="n">
-        <v>46.55</v>
+        <v>46.58</v>
       </c>
       <c r="N13" t="n">
         <v>-38.27</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.7</v>
+        <v>90.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.97</v>
+        <v>4.08</v>
       </c>
       <c r="L2" t="n">
-        <v>16.34</v>
+        <v>16.46</v>
       </c>
       <c r="M2" t="n">
         <v>11.78</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.35</v>
+        <v>12.37</v>
       </c>
       <c r="L3" t="n">
-        <v>41.55</v>
+        <v>41.57</v>
       </c>
       <c r="M3" t="n">
         <v>22.74</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.77</v>
+        <v>3.97</v>
       </c>
       <c r="L4" t="n">
-        <v>57.01</v>
+        <v>57.31</v>
       </c>
       <c r="M4" t="n">
-        <v>39.42</v>
+        <v>39.41</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.41</v>
+        <v>11.06</v>
       </c>
       <c r="L5" t="n">
-        <v>67.39</v>
+        <v>66.86</v>
       </c>
       <c r="M5" t="n">
         <v>31.54</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>81.7</v>
+        <v>82.8</v>
       </c>
       <c r="I6" t="n">
-        <v>89.8</v>
+        <v>89.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.58</v>
+        <v>5.11</v>
       </c>
       <c r="L6" t="n">
-        <v>14.62</v>
+        <v>15.21</v>
       </c>
       <c r="M6" t="n">
-        <v>14.12</v>
+        <v>14.2</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>43.6</v>
+        <v>42.9</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.55</v>
+        <v>-4.87</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.39</v>
+        <v>-1.72</v>
       </c>
       <c r="M7" t="n">
-        <v>11.53</v>
+        <v>11.52</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60.4</v>
+        <v>60.6</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>35.2</v>
+        <v>35.8</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.62</v>
+        <v>-7.33</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.02</v>
+        <v>-7.73</v>
       </c>
       <c r="M8" t="n">
-        <v>18.13</v>
+        <v>18.11</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
       <c r="I9" t="n">
         <v>64.5</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.93</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>26.02</v>
@@ -1381,102 +1381,90 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Obbligazionario Globale</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="H10" t="n">
-        <v>30.2</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>61.6</v>
+        <v>50</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>-4.66</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-20.32</v>
-      </c>
-      <c r="M10" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-25.29</v>
-      </c>
+          <t>Dati limitati</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETF obbligazionario</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>EUNA.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETF global aggregate bond hedged/unhedged</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>9-35%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Lungo periodo</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Rischio tassi cambio e duration</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Da allineare a orizzonte e consulenza Fineco</t>
         </is>
       </c>
     </row>
@@ -1486,90 +1474,102 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Obbligazionario Globale</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>57.7</v>
+        <v>57.5</v>
       </c>
       <c r="G11" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>29.3</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dati limitati</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Debole o laterale</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-20.74</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26.87</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-25.29</v>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>ETF obbligazionario</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>EUNA.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ETF global aggregate bond hedged/unhedged</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>9-35%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Lungo periodo</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Rischio tassi cambio e duration</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Da allineare a orizzonte e consulenza Fineco</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.6</v>
+        <v>55.4</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>45</v>
+        <v>44.5</v>
       </c>
       <c r="I12" t="n">
         <v>58.3</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.26</v>
+        <v>-4.52</v>
       </c>
       <c r="M12" t="n">
-        <v>28.33</v>
+        <v>28.34</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>46.4</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>26.4</v>
+        <v>24.6</v>
       </c>
       <c r="I13" t="n">
         <v>24.8</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-6.58</v>
+        <v>-7.58</v>
       </c>
       <c r="L13" t="n">
-        <v>-22.48</v>
+        <v>-23.31</v>
       </c>
       <c r="M13" t="n">
-        <v>46.58</v>
+        <v>46.55</v>
       </c>
       <c r="N13" t="n">
         <v>-38.27</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.08</v>
+        <v>4.47</v>
       </c>
       <c r="L2" t="n">
-        <v>16.46</v>
+        <v>16.89</v>
       </c>
       <c r="M2" t="n">
         <v>11.78</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.37</v>
+        <v>12.84</v>
       </c>
       <c r="L3" t="n">
-        <v>41.57</v>
+        <v>42.16</v>
       </c>
       <c r="M3" t="n">
-        <v>22.74</v>
+        <v>22.75</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.97</v>
+        <v>5.19</v>
       </c>
       <c r="L4" t="n">
-        <v>57.31</v>
+        <v>59.15</v>
       </c>
       <c r="M4" t="n">
-        <v>39.41</v>
+        <v>39.39</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.06</v>
+        <v>12.96</v>
       </c>
       <c r="L5" t="n">
-        <v>66.86</v>
+        <v>69.72</v>
       </c>
       <c r="M5" t="n">
-        <v>31.54</v>
+        <v>31.59</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.7</v>
+        <v>80.3</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>82.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>89.7</v>
+        <v>90</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.11</v>
+        <v>2.87</v>
       </c>
       <c r="L6" t="n">
-        <v>15.21</v>
+        <v>12.75</v>
       </c>
       <c r="M6" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.9</v>
+        <v>42.2</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.87</v>
+        <v>-5.26</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.72</v>
+        <v>-2.13</v>
       </c>
       <c r="M7" t="n">
-        <v>11.52</v>
+        <v>11.51</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60.6</v>
+        <v>61.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>35.8</v>
+        <v>39.1</v>
       </c>
       <c r="I8" t="n">
         <v>77</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.33</v>
+        <v>-5.56</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.73</v>
+        <v>-5.97</v>
       </c>
       <c r="M8" t="n">
         <v>18.11</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.1</v>
+        <v>60.6</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>46.7</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
         <v>64.5</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.779999999999999</v>
+        <v>-8.15</v>
       </c>
       <c r="M9" t="n">
-        <v>26.02</v>
+        <v>26.01</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1381,90 +1381,102 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Obbligazionario Globale</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57.7</v>
+        <v>59.8</v>
       </c>
       <c r="G10" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>35.6</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>62.1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dati limitati</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Debole o laterale</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-25.29</v>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF obbligazionario</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>EUNA.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF global aggregate bond hedged/unhedged</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>9-35%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Lungo periodo</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio tassi cambio e duration</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da allineare a orizzonte e consulenza Fineco</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1474,102 +1486,90 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Obbligazionario Globale</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
       <c r="G11" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="H11" t="n">
-        <v>29.3</v>
+        <v>50</v>
       </c>
       <c r="I11" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>-5.17</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-20.74</v>
-      </c>
-      <c r="M11" t="n">
-        <v>26.87</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-25.29</v>
-      </c>
+          <t>Dati limitati</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETF obbligazionario</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>EUNA.MI</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETF global aggregate bond hedged/unhedged</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>9-35%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Lungo periodo</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Rischio tassi cambio e duration</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Da allineare a orizzonte e consulenza Fineco</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.4</v>
+        <v>56.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>44.5</v>
+        <v>46.6</v>
       </c>
       <c r="I12" t="n">
         <v>58.3</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.609999999999999</v>
+        <v>-7.52</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.52</v>
+        <v>-3.37</v>
       </c>
       <c r="M12" t="n">
         <v>28.34</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>46.4</v>
+        <v>48.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>24.6</v>
+        <v>31.5</v>
       </c>
       <c r="I13" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-7.58</v>
+        <v>-3.71</v>
       </c>
       <c r="L13" t="n">
-        <v>-23.31</v>
+        <v>-20.1</v>
       </c>
       <c r="M13" t="n">
-        <v>46.55</v>
+        <v>46.78</v>
       </c>
       <c r="N13" t="n">
         <v>-38.27</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>83.2</v>
+        <v>81</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.47</v>
+        <v>3.96</v>
       </c>
       <c r="L2" t="n">
-        <v>16.89</v>
+        <v>14.68</v>
       </c>
       <c r="M2" t="n">
         <v>11.78</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.84</v>
+        <v>12.73</v>
       </c>
       <c r="L3" t="n">
-        <v>42.16</v>
+        <v>39.48</v>
       </c>
       <c r="M3" t="n">
-        <v>22.75</v>
+        <v>22.71</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.19</v>
+        <v>5.31</v>
       </c>
       <c r="L4" t="n">
-        <v>59.15</v>
+        <v>53.95</v>
       </c>
       <c r="M4" t="n">
-        <v>39.39</v>
+        <v>39.41</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12.96</v>
+        <v>13.01</v>
       </c>
       <c r="L5" t="n">
-        <v>69.72</v>
+        <v>78.89</v>
       </c>
       <c r="M5" t="n">
         <v>31.59</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>80.3</v>
+        <v>79.7</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>78.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="I6" t="n">
         <v>90</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="L6" t="n">
-        <v>12.75</v>
+        <v>10.97</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>13.99</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.2</v>
+        <v>43.1</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.26</v>
+        <v>-5.34</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.13</v>
+        <v>-0.75</v>
       </c>
       <c r="M7" t="n">
-        <v>11.51</v>
+        <v>11.52</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.7</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>39.1</v>
+        <v>49.1</v>
       </c>
       <c r="I8" t="n">
-        <v>77</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,66 +1211,62 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.56</v>
+        <v>4.71</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.97</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>18.11</v>
+        <v>25.94</v>
       </c>
       <c r="N8" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1280,35 +1276,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.6</v>
+        <v>59.5</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>32.6</v>
       </c>
       <c r="I9" t="n">
-        <v>64.5</v>
+        <v>76.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1312,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.05</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.15</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>26.01</v>
+        <v>18.33</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.8</v>
+        <v>58.5</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>35.6</v>
+        <v>32.1</v>
       </c>
       <c r="I10" t="n">
-        <v>62.1</v>
+        <v>61.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.64</v>
+        <v>-4.02</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.8</v>
+        <v>-18.71</v>
       </c>
       <c r="M10" t="n">
-        <v>26.42</v>
+        <v>26.6</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56.1</v>
+        <v>55.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>46.6</v>
+        <v>43.8</v>
       </c>
       <c r="I12" t="n">
         <v>58.3</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.52</v>
+        <v>-7.37</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.37</v>
+        <v>-7.63</v>
       </c>
       <c r="M12" t="n">
-        <v>28.34</v>
+        <v>28.36</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48.7</v>
+        <v>44.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>31.5</v>
+        <v>19.2</v>
       </c>
       <c r="I13" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-3.71</v>
+        <v>-10.41</v>
       </c>
       <c r="L13" t="n">
-        <v>-20.1</v>
+        <v>-26.19</v>
       </c>
       <c r="M13" t="n">
-        <v>46.78</v>
+        <v>47.1</v>
       </c>
       <c r="N13" t="n">
         <v>-38.27</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.96</v>
+        <v>3.69</v>
       </c>
       <c r="L2" t="n">
-        <v>14.68</v>
+        <v>14.39</v>
       </c>
       <c r="M2" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.73</v>
+        <v>12.42</v>
       </c>
       <c r="L3" t="n">
-        <v>39.48</v>
+        <v>39.1</v>
       </c>
       <c r="M3" t="n">
-        <v>22.71</v>
+        <v>22.72</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.31</v>
+        <v>4.88</v>
       </c>
       <c r="L4" t="n">
-        <v>53.95</v>
+        <v>53.32</v>
       </c>
       <c r="M4" t="n">
-        <v>39.41</v>
+        <v>39.43</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13.01</v>
+        <v>12.42</v>
       </c>
       <c r="L5" t="n">
-        <v>78.89</v>
+        <v>77.94</v>
       </c>
       <c r="M5" t="n">
-        <v>31.59</v>
+        <v>31.62</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>76.5</v>
+        <v>68.3</v>
       </c>
       <c r="I6" t="n">
         <v>90</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="L6" t="n">
-        <v>10.97</v>
+        <v>10.85</v>
       </c>
       <c r="M6" t="n">
-        <v>13.99</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>43.1</v>
+        <v>42.3</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.34</v>
+        <v>-5.76</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.75</v>
+        <v>-1.19</v>
       </c>
       <c r="M7" t="n">
-        <v>11.52</v>
+        <v>11.51</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>60.7</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
       <c r="I8" t="n">
         <v>64.59999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.71</v>
+        <v>4.27</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.77</v>
       </c>
       <c r="M8" t="n">
-        <v>25.94</v>
+        <v>25.95</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1295,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.5</v>
+        <v>59.1</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="I9" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>18.33</v>
+        <v>18.42</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.5</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32.1</v>
+        <v>30.7</v>
       </c>
       <c r="I10" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.02</v>
+        <v>-4.81</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.71</v>
+        <v>-19.38</v>
       </c>
       <c r="M10" t="n">
-        <v>26.6</v>
+        <v>26.71</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-25.51</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.1</v>
+        <v>51.9</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>43.8</v>
+        <v>34.4</v>
       </c>
       <c r="I12" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.37</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.63</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>28.36</v>
+        <v>28.4</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44.5</v>
+        <v>43.6</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>19.2</v>
+        <v>16.8</v>
       </c>
       <c r="I13" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.41</v>
+        <v>-11.75</v>
       </c>
       <c r="L13" t="n">
-        <v>-26.19</v>
+        <v>-27.29</v>
       </c>
       <c r="M13" t="n">
-        <v>47.1</v>
+        <v>47.29</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.27</v>
+        <v>-38.31</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.5</v>
+        <v>81.7</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.69</v>
+        <v>4.31</v>
       </c>
       <c r="L2" t="n">
-        <v>14.39</v>
+        <v>15.07</v>
       </c>
       <c r="M2" t="n">
-        <v>11.8</v>
+        <v>11.76</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.42</v>
+        <v>12.84</v>
       </c>
       <c r="L3" t="n">
-        <v>39.1</v>
+        <v>39.62</v>
       </c>
       <c r="M3" t="n">
-        <v>22.72</v>
+        <v>22.7</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.88</v>
+        <v>6.04</v>
       </c>
       <c r="L4" t="n">
-        <v>53.32</v>
+        <v>55.02</v>
       </c>
       <c r="M4" t="n">
-        <v>39.43</v>
+        <v>39.38</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12.42</v>
+        <v>12.8</v>
       </c>
       <c r="L5" t="n">
-        <v>77.94</v>
+        <v>78.56</v>
       </c>
       <c r="M5" t="n">
-        <v>31.62</v>
+        <v>31.6</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>68.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>90</v>
+        <v>89.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.24</v>
+        <v>4.95</v>
       </c>
       <c r="L6" t="n">
-        <v>10.85</v>
+        <v>13.79</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>14.15</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.3</v>
+        <v>42.8</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.76</v>
+        <v>-5.47</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.19</v>
+        <v>-0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>11.51</v>
+        <v>11.52</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1200,7 +1200,7 @@
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I8" t="n">
         <v>64.59999999999999</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.77</v>
+        <v>-9.83</v>
       </c>
       <c r="M8" t="n">
         <v>25.95</v>
@@ -1281,30 +1281,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.1</v>
+        <v>60.1</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>31.6</v>
+        <v>34.4</v>
       </c>
       <c r="I9" t="n">
-        <v>76.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-9.960000000000001</v>
+        <v>-8.48</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.199999999999999</v>
+        <v>-7.72</v>
       </c>
       <c r="M9" t="n">
-        <v>18.42</v>
+        <v>18.19</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>30.7</v>
+        <v>31.5</v>
       </c>
       <c r="I10" t="n">
-        <v>61.5</v>
+        <v>61.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.81</v>
+        <v>-4.34</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.38</v>
+        <v>-18.99</v>
       </c>
       <c r="M10" t="n">
-        <v>26.71</v>
+        <v>26.65</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.51</v>
+        <v>-25.29</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.9</v>
+        <v>55.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>34.4</v>
+        <v>43.6</v>
       </c>
       <c r="I12" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.109999999999999</v>
+        <v>-7.46</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.369999999999999</v>
+        <v>-7.73</v>
       </c>
       <c r="M12" t="n">
-        <v>28.4</v>
+        <v>28.36</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43.6</v>
+        <v>45.4</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>16.8</v>
+        <v>21.7</v>
       </c>
       <c r="I13" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.75</v>
+        <v>-8.98</v>
       </c>
       <c r="L13" t="n">
-        <v>-27.29</v>
+        <v>-25.01</v>
       </c>
       <c r="M13" t="n">
-        <v>47.29</v>
+        <v>46.95</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.31</v>
+        <v>-38.27</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.7</v>
+        <v>81.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="L2" t="n">
-        <v>15.07</v>
+        <v>14.58</v>
       </c>
       <c r="M2" t="n">
-        <v>11.76</v>
+        <v>11.77</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.84</v>
+        <v>11.32</v>
       </c>
       <c r="L3" t="n">
-        <v>39.62</v>
+        <v>35.14</v>
       </c>
       <c r="M3" t="n">
-        <v>22.7</v>
+        <v>22.75</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6.04</v>
+        <v>1.43</v>
       </c>
       <c r="L4" t="n">
-        <v>55.02</v>
+        <v>49.74</v>
       </c>
       <c r="M4" t="n">
-        <v>39.38</v>
+        <v>39.53</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12.8</v>
+        <v>13.47</v>
       </c>
       <c r="L5" t="n">
-        <v>78.56</v>
+        <v>76.95</v>
       </c>
       <c r="M5" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.3</v>
+        <v>82.3</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>81.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="I6" t="n">
         <v>89.8</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.95</v>
+        <v>6.95</v>
       </c>
       <c r="L6" t="n">
-        <v>13.79</v>
+        <v>14.47</v>
       </c>
       <c r="M6" t="n">
         <v>14.15</v>
@@ -1089,30 +1089,30 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.8</v>
+        <v>60.9</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.47</v>
+        <v>-4.76</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>11.52</v>
+        <v>11.55</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60.7</v>
+        <v>61.3</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>48.2</v>
+        <v>50.2</v>
       </c>
       <c r="I8" t="n">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.81</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.83</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>25.95</v>
+        <v>26.01</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.1</v>
+        <v>60.7</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>34.4</v>
+        <v>36.1</v>
       </c>
       <c r="I9" t="n">
         <v>76.90000000000001</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-8.48</v>
+        <v>-7.53</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.72</v>
+        <v>-6.97</v>
       </c>
       <c r="M9" t="n">
         <v>18.19</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.3</v>
+        <v>58.8</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>31.5</v>
+        <v>32.9</v>
       </c>
       <c r="I10" t="n">
         <v>61.8</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.34</v>
+        <v>-2.9</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.99</v>
+        <v>-19.53</v>
       </c>
       <c r="M10" t="n">
-        <v>26.65</v>
+        <v>26.64</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.1</v>
+        <v>54.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>43.6</v>
+        <v>42.6</v>
       </c>
       <c r="I12" t="n">
         <v>58.3</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.46</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.73</v>
+        <v>-7.99</v>
       </c>
       <c r="M12" t="n">
-        <v>28.36</v>
+        <v>28.31</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>45.4</v>
+        <v>44.6</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>21.7</v>
+        <v>19.8</v>
       </c>
       <c r="I13" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-8.98</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-25.01</v>
+        <v>-26.24</v>
       </c>
       <c r="M13" t="n">
-        <v>46.95</v>
+        <v>47.08</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.27</v>
+        <v>-38.6</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.29</v>
+        <v>4.35</v>
       </c>
       <c r="L2" t="n">
-        <v>14.58</v>
+        <v>14.64</v>
       </c>
       <c r="M2" t="n">
-        <v>11.77</v>
+        <v>11.76</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.32</v>
+        <v>11.5</v>
       </c>
       <c r="L3" t="n">
-        <v>35.14</v>
+        <v>35.35</v>
       </c>
       <c r="M3" t="n">
-        <v>22.75</v>
+        <v>22.74</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.43</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>49.74</v>
+        <v>49.03</v>
       </c>
       <c r="M4" t="n">
-        <v>39.53</v>
+        <v>39.57</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13.47</v>
+        <v>14.83</v>
       </c>
       <c r="L5" t="n">
-        <v>76.95</v>
+        <v>79.08</v>
       </c>
       <c r="M5" t="n">
-        <v>31.61</v>
+        <v>31.67</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>84.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.8</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.95</v>
+        <v>6.74</v>
       </c>
       <c r="L6" t="n">
-        <v>14.47</v>
+        <v>14.24</v>
       </c>
       <c r="M6" t="n">
-        <v>14.15</v>
+        <v>14.16</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>60.9</v>
+        <v>61.1</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.76</v>
+        <v>-4.64</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="M7" t="n">
-        <v>11.55</v>
+        <v>11.56</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.029999999999999</v>
+        <v>-7.99</v>
       </c>
       <c r="M8" t="n">
-        <v>26.01</v>
+        <v>26.02</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.7</v>
+        <v>60.5</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>36.1</v>
+        <v>35.6</v>
       </c>
       <c r="I9" t="n">
         <v>76.90000000000001</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.53</v>
+        <v>-7.76</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.97</v>
+        <v>-7.2</v>
       </c>
       <c r="M9" t="n">
         <v>18.19</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.8</v>
+        <v>59.2</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32.9</v>
+        <v>34.2</v>
       </c>
       <c r="I10" t="n">
         <v>61.8</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-2.9</v>
+        <v>-2.14</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.53</v>
+        <v>-18.9</v>
       </c>
       <c r="M10" t="n">
-        <v>26.64</v>
+        <v>26.67</v>
       </c>
       <c r="N10" t="n">
         <v>-25.29</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="I12" t="n">
         <v>58.3</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.140000000000001</v>
+        <v>-8.08</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.99</v>
+        <v>-7.93</v>
       </c>
       <c r="M12" t="n">
         <v>28.31</v>
@@ -1709,7 +1709,7 @@
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="I13" t="n">
         <v>23.9</v>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.880000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="L13" t="n">
-        <v>-26.24</v>
+        <v>-26.25</v>
       </c>
       <c r="M13" t="n">
         <v>47.08</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.6</v>
+        <v>-38.61</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.5</v>
+        <v>80.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.35</v>
+        <v>3.77</v>
       </c>
       <c r="L2" t="n">
-        <v>14.64</v>
+        <v>14.01</v>
       </c>
       <c r="M2" t="n">
-        <v>11.76</v>
+        <v>11.78</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.5</v>
+        <v>12.46</v>
       </c>
       <c r="L3" t="n">
-        <v>35.35</v>
+        <v>36.52</v>
       </c>
       <c r="M3" t="n">
-        <v>22.74</v>
+        <v>22.7</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.2</v>
+        <v>45.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.51</v>
       </c>
       <c r="L4" t="n">
-        <v>49.03</v>
+        <v>52.82</v>
       </c>
       <c r="M4" t="n">
-        <v>39.57</v>
+        <v>39.4</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14.83</v>
+        <v>11.82</v>
       </c>
       <c r="L5" t="n">
-        <v>79.08</v>
+        <v>74.38</v>
       </c>
       <c r="M5" t="n">
-        <v>31.67</v>
+        <v>31.6</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>82.2</v>
+        <v>77.8</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>84.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="I6" t="n">
-        <v>89.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.74</v>
+        <v>4.42</v>
       </c>
       <c r="L6" t="n">
-        <v>14.24</v>
+        <v>11.75</v>
       </c>
       <c r="M6" t="n">
-        <v>14.16</v>
+        <v>14.39</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,30 +1089,30 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>66.7</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>61.1</v>
+        <v>42.5</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.64</v>
+        <v>-5.95</v>
       </c>
       <c r="L7" t="n">
-        <v>0.93</v>
+        <v>-0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>11.56</v>
+        <v>11.52</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.3</v>
+        <v>60.2</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>50.2</v>
+        <v>46.8</v>
       </c>
       <c r="I8" t="n">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4.86</v>
+        <v>2.99</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.99</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>26.02</v>
+        <v>25.95</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1281,30 +1281,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.5</v>
+        <v>59.7</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>35.6</v>
+        <v>33.4</v>
       </c>
       <c r="I9" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.76</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.2</v>
+        <v>-8.41</v>
       </c>
       <c r="M9" t="n">
-        <v>18.19</v>
+        <v>18.25</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.2</v>
+        <v>58.1</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.2</v>
+        <v>31</v>
       </c>
       <c r="I10" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-2.14</v>
+        <v>-3.92</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.9</v>
+        <v>-20.37</v>
       </c>
       <c r="M10" t="n">
-        <v>26.67</v>
+        <v>26.64</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.29</v>
+        <v>-25.51</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>54.8</v>
+        <v>51.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>42.8</v>
+        <v>33.3</v>
       </c>
       <c r="I12" t="n">
         <v>58.3</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.08</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.93</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>28.31</v>
+        <v>28.32</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44.6</v>
+        <v>44.9</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>19.7</v>
+        <v>20.5</v>
       </c>
       <c r="I13" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.9</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-26.25</v>
+        <v>-25.9</v>
       </c>
       <c r="M13" t="n">
-        <v>47.08</v>
+        <v>47.05</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.61</v>
+        <v>-38.31</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.3</v>
+        <v>80.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.77</v>
+        <v>4.85</v>
       </c>
       <c r="L2" t="n">
-        <v>14.01</v>
+        <v>12.9</v>
       </c>
       <c r="M2" t="n">
-        <v>11.78</v>
+        <v>11.55</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>88.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.46</v>
+        <v>12.86</v>
       </c>
       <c r="L3" t="n">
-        <v>36.52</v>
+        <v>30.14</v>
       </c>
       <c r="M3" t="n">
-        <v>22.7</v>
+        <v>22.51</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -780,10 +780,10 @@
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3.51</v>
+        <v>4.18</v>
       </c>
       <c r="L4" t="n">
-        <v>52.82</v>
+        <v>41.29</v>
       </c>
       <c r="M4" t="n">
-        <v>39.4</v>
+        <v>39.22</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.82</v>
+        <v>13.63</v>
       </c>
       <c r="L5" t="n">
-        <v>74.38</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.8</v>
+        <v>81.8</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>71.5</v>
+        <v>83.2</v>
       </c>
       <c r="I6" t="n">
-        <v>89.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.42</v>
+        <v>5.79</v>
       </c>
       <c r="L6" t="n">
-        <v>11.75</v>
+        <v>14.6</v>
       </c>
       <c r="M6" t="n">
-        <v>14.39</v>
+        <v>14.5</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,30 +1089,30 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.7</v>
+        <v>73.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>42.5</v>
+        <v>62.6</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.95</v>
+        <v>-3.62</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.46</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>11.52</v>
+        <v>11.6</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60.2</v>
+        <v>61.6</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>46.8</v>
+        <v>50.9</v>
       </c>
       <c r="I8" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2.99</v>
+        <v>6.29</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.640000000000001</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>25.95</v>
+        <v>25.88</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1281,30 +1281,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.7</v>
+        <v>60.8</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>33.4</v>
+        <v>36.5</v>
       </c>
       <c r="I9" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-8.960000000000001</v>
+        <v>-6.64</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.41</v>
+        <v>-7.86</v>
       </c>
       <c r="M9" t="n">
-        <v>18.25</v>
+        <v>18.33</v>
       </c>
       <c r="N9" t="n">
         <v>-20.62</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.1</v>
+        <v>59.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>34.5</v>
       </c>
       <c r="I10" t="n">
-        <v>61.7</v>
+        <v>61.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-3.92</v>
+        <v>-1.63</v>
       </c>
       <c r="L10" t="n">
-        <v>-20.37</v>
+        <v>-19.36</v>
       </c>
       <c r="M10" t="n">
-        <v>26.64</v>
+        <v>26.45</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.6</v>
+        <v>56.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
       <c r="I12" t="n">
-        <v>58.3</v>
+        <v>58.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.869999999999999</v>
+        <v>-5.68</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.720000000000001</v>
+        <v>-6.36</v>
       </c>
       <c r="M12" t="n">
-        <v>28.32</v>
+        <v>28.07</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44.9</v>
+        <v>43.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>20.5</v>
+        <v>15.9</v>
       </c>
       <c r="I13" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.470000000000001</v>
+        <v>-10.09</v>
       </c>
       <c r="L13" t="n">
-        <v>-25.9</v>
+        <v>-31.36</v>
       </c>
       <c r="M13" t="n">
-        <v>47.05</v>
+        <v>46.97</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.31</v>
+        <v>-38.85</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.2</v>
+        <v>90.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.85</v>
+        <v>4.26</v>
       </c>
       <c r="L2" t="n">
-        <v>12.9</v>
+        <v>13.95</v>
       </c>
       <c r="M2" t="n">
-        <v>11.55</v>
+        <v>11.57</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.86</v>
+        <v>12.47</v>
       </c>
       <c r="L3" t="n">
-        <v>30.14</v>
+        <v>33.22</v>
       </c>
       <c r="M3" t="n">
-        <v>22.51</v>
+        <v>22.54</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="G4" t="n">
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
         <v>45.7</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.18</v>
+        <v>4.77</v>
       </c>
       <c r="L4" t="n">
-        <v>41.29</v>
+        <v>46.36</v>
       </c>
       <c r="M4" t="n">
         <v>39.22</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>83.2</v>
+        <v>83.5</v>
       </c>
       <c r="I6" t="n">
         <v>89.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.79</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>14.6</v>
+        <v>14.68</v>
       </c>
       <c r="M6" t="n">
-        <v>14.5</v>
+        <v>14.49</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>62.6</v>
+        <v>61.3</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.62</v>
+        <v>-4.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>0.73</v>
       </c>
       <c r="M7" t="n">
-        <v>11.6</v>
+        <v>11.59</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1200,10 +1200,10 @@
         <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="I8" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6.29</v>
+        <v>5.74</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.539999999999999</v>
+        <v>-8.27</v>
       </c>
       <c r="M8" t="n">
-        <v>25.88</v>
+        <v>25.93</v>
       </c>
       <c r="N8" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56.2</v>
+        <v>55.4</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>46.7</v>
+        <v>44.3</v>
       </c>
       <c r="I12" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.68</v>
+        <v>-7.72</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.36</v>
+        <v>-6.4</v>
       </c>
       <c r="M12" t="n">
-        <v>28.07</v>
+        <v>28.13</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13.63</v>
+        <v>11.51</v>
       </c>
       <c r="L5" t="n">
-        <v>74.29000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="M5" t="n">
-        <v>31.61</v>
+        <v>31.65</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.8</v>
+        <v>60.2</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>36.5</v>
+        <v>34.9</v>
       </c>
       <c r="I9" t="n">
         <v>76.7</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-6.64</v>
+        <v>-7.54</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.86</v>
+        <v>-8.66</v>
       </c>
       <c r="M9" t="n">
         <v>18.33</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.4</v>
+        <v>59.1</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5</v>
+        <v>33.7</v>
       </c>
       <c r="I10" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.63</v>
+        <v>-2.12</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.36</v>
+        <v>-19.6</v>
       </c>
       <c r="M10" t="n">
-        <v>26.45</v>
+        <v>26.51</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>15.9</v>
+        <v>17.4</v>
       </c>
       <c r="I13" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.09</v>
+        <v>-10.47</v>
       </c>
       <c r="L13" t="n">
-        <v>-31.36</v>
+        <v>-28.65</v>
       </c>
       <c r="M13" t="n">
-        <v>46.97</v>
+        <v>47.06</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.85</v>
+        <v>-38.61</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.3</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.26</v>
+        <v>4.45</v>
       </c>
       <c r="L2" t="n">
-        <v>13.95</v>
+        <v>12.47</v>
       </c>
       <c r="M2" t="n">
-        <v>11.57</v>
+        <v>11.55</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.47</v>
+        <v>12.42</v>
       </c>
       <c r="L3" t="n">
-        <v>33.22</v>
+        <v>29.62</v>
       </c>
       <c r="M3" t="n">
-        <v>22.54</v>
+        <v>22.53</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.7</v>
+        <v>58.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.77</v>
+        <v>12.54</v>
       </c>
       <c r="L4" t="n">
-        <v>46.36</v>
+        <v>72.61</v>
       </c>
       <c r="M4" t="n">
-        <v>39.22</v>
+        <v>31.66</v>
       </c>
       <c r="N4" t="n">
-        <v>-23.17</v>
+        <v>-20.33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>58.3</v>
+        <v>45.4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.51</v>
+        <v>2.08</v>
       </c>
       <c r="L5" t="n">
-        <v>79.41</v>
+        <v>38.44</v>
       </c>
       <c r="M5" t="n">
-        <v>31.65</v>
+        <v>39.4</v>
       </c>
       <c r="N5" t="n">
-        <v>-20.33</v>
+        <v>-23.17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>83.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>4.98</v>
       </c>
       <c r="L6" t="n">
-        <v>14.68</v>
+        <v>13.72</v>
       </c>
       <c r="M6" t="n">
-        <v>14.49</v>
+        <v>14.47</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>61.3</v>
+        <v>62.4</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.35</v>
+        <v>-3.69</v>
       </c>
       <c r="L7" t="n">
-        <v>0.73</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>11.59</v>
+        <v>11.6</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.6</v>
+        <v>62.1</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="I8" t="n">
-        <v>64.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,62 +1211,66 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.74</v>
+        <v>-4.56</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.27</v>
+        <v>-5.81</v>
       </c>
       <c r="M8" t="n">
-        <v>25.93</v>
+        <v>18.59</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1295,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.2</v>
+        <v>61.5</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>34.9</v>
+        <v>50.7</v>
       </c>
       <c r="I9" t="n">
-        <v>76.7</v>
+        <v>64.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.54</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.66</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>18.33</v>
+        <v>25.88</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.1</v>
+        <v>58.5</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.7</v>
+        <v>32.1</v>
       </c>
       <c r="I10" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-2.12</v>
+        <v>-2.98</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.6</v>
+        <v>-20.47</v>
       </c>
       <c r="M10" t="n">
-        <v>26.51</v>
+        <v>26.49</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55.4</v>
+        <v>53.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>44.3</v>
+        <v>37.9</v>
       </c>
       <c r="I12" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.72</v>
+        <v>-6.1</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.4</v>
+        <v>-6.78</v>
       </c>
       <c r="M12" t="n">
-        <v>28.13</v>
+        <v>28.07</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43.8</v>
+        <v>41.6</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>17.4</v>
+        <v>11.7</v>
       </c>
       <c r="I13" t="n">
-        <v>23.9</v>
+        <v>22.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.47</v>
+        <v>-12.55</v>
       </c>
       <c r="L13" t="n">
-        <v>-28.65</v>
+        <v>-33.24</v>
       </c>
       <c r="M13" t="n">
-        <v>47.06</v>
+        <v>47.07</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.61</v>
+        <v>-40.52</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.45</v>
+        <v>4.32</v>
       </c>
       <c r="L2" t="n">
-        <v>12.47</v>
+        <v>12.33</v>
       </c>
       <c r="M2" t="n">
         <v>11.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.42</v>
+        <v>11.8</v>
       </c>
       <c r="L3" t="n">
-        <v>29.62</v>
+        <v>28.92</v>
       </c>
       <c r="M3" t="n">
-        <v>22.53</v>
+        <v>22.56</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12.54</v>
+        <v>12.33</v>
       </c>
       <c r="L4" t="n">
-        <v>72.61</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>31.66</v>
+        <v>31.68</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>95.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="I5" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.08</v>
+        <v>1.08</v>
       </c>
       <c r="L5" t="n">
-        <v>38.44</v>
+        <v>37.09</v>
       </c>
       <c r="M5" t="n">
-        <v>39.4</v>
+        <v>39.52</v>
       </c>
       <c r="N5" t="n">
         <v>-23.17</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>89.3</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>13.72</v>
+        <v>13.63</v>
       </c>
       <c r="M6" t="n">
         <v>14.47</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>62.4</v>
+        <v>62.7</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.69</v>
+        <v>-3.58</v>
       </c>
       <c r="L7" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>11.6</v>
+        <v>11.61</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.56</v>
+        <v>-4.54</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.81</v>
+        <v>-5.78</v>
       </c>
       <c r="M8" t="n">
-        <v>18.59</v>
+        <v>18.6</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>5.97</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.619999999999999</v>
+        <v>-9.82</v>
       </c>
       <c r="M9" t="n">
-        <v>25.88</v>
+        <v>25.89</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="I10" t="n">
         <v>61.9</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-2.98</v>
+        <v>-3.12</v>
       </c>
       <c r="L10" t="n">
-        <v>-20.47</v>
+        <v>-20.59</v>
       </c>
       <c r="M10" t="n">
         <v>26.49</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>53.2</v>
+        <v>52.9</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>37.9</v>
+        <v>37</v>
       </c>
       <c r="I12" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-6.1</v>
+        <v>-6.6</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.78</v>
+        <v>-7.28</v>
       </c>
       <c r="M12" t="n">
-        <v>28.07</v>
+        <v>28.09</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>11.7</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.55</v>
+        <v>-12.97</v>
       </c>
       <c r="L13" t="n">
-        <v>-33.24</v>
+        <v>-33.56</v>
       </c>
       <c r="M13" t="n">
-        <v>47.07</v>
+        <v>47.1</v>
       </c>
       <c r="N13" t="n">
-        <v>-40.52</v>
+        <v>-40.81</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.8</v>
+        <v>80.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.32</v>
+        <v>4.85</v>
       </c>
       <c r="L2" t="n">
-        <v>12.33</v>
+        <v>12.9</v>
       </c>
       <c r="M2" t="n">
         <v>11.55</v>
@@ -678,7 +678,7 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.8</v>
+        <v>12.86</v>
       </c>
       <c r="L3" t="n">
-        <v>28.92</v>
+        <v>30.14</v>
       </c>
       <c r="M3" t="n">
-        <v>22.56</v>
+        <v>22.51</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>58.2</v>
+        <v>45.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12.33</v>
+        <v>4.18</v>
       </c>
       <c r="L4" t="n">
-        <v>72.29000000000001</v>
+        <v>41.29</v>
       </c>
       <c r="M4" t="n">
-        <v>31.68</v>
+        <v>39.22</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.33</v>
+        <v>-23.17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>45.3</v>
+        <v>58.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.08</v>
+        <v>13.63</v>
       </c>
       <c r="L5" t="n">
-        <v>37.09</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>39.52</v>
+        <v>31.61</v>
       </c>
       <c r="N5" t="n">
-        <v>-23.17</v>
+        <v>-20.33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>81.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I6" t="n">
         <v>89.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>5.79</v>
       </c>
       <c r="L6" t="n">
-        <v>13.63</v>
+        <v>14.6</v>
       </c>
       <c r="M6" t="n">
-        <v>14.47</v>
+        <v>14.5</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>62.7</v>
+        <v>62.6</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.58</v>
+        <v>-3.62</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>11.61</v>
+        <v>11.6</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.1</v>
+        <v>61.6</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>40.5</v>
+        <v>50.9</v>
       </c>
       <c r="I8" t="n">
-        <v>76.3</v>
+        <v>64.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,66 +1211,62 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.54</v>
+        <v>6.29</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.78</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>18.6</v>
+        <v>25.88</v>
       </c>
       <c r="N8" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1276,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1299,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.4</v>
+        <v>60.8</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>50.3</v>
+        <v>36.5</v>
       </c>
       <c r="I9" t="n">
-        <v>64.7</v>
+        <v>76.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1312,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5.97</v>
+        <v>-6.64</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.82</v>
+        <v>-7.86</v>
       </c>
       <c r="M9" t="n">
-        <v>25.89</v>
+        <v>18.33</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.4</v>
+        <v>59.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>31.8</v>
+        <v>34.5</v>
       </c>
       <c r="I10" t="n">
         <v>61.9</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-3.12</v>
+        <v>-1.63</v>
       </c>
       <c r="L10" t="n">
-        <v>-20.59</v>
+        <v>-19.36</v>
       </c>
       <c r="M10" t="n">
-        <v>26.49</v>
+        <v>26.45</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.9</v>
+        <v>56.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>37</v>
+        <v>46.7</v>
       </c>
       <c r="I12" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-6.6</v>
+        <v>-5.68</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.28</v>
+        <v>-6.36</v>
       </c>
       <c r="M12" t="n">
-        <v>28.09</v>
+        <v>28.07</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.4</v>
+        <v>43.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>15.9</v>
       </c>
       <c r="I13" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.97</v>
+        <v>-10.09</v>
       </c>
       <c r="L13" t="n">
-        <v>-33.56</v>
+        <v>-31.36</v>
       </c>
       <c r="M13" t="n">
-        <v>47.1</v>
+        <v>46.97</v>
       </c>
       <c r="N13" t="n">
-        <v>-40.81</v>
+        <v>-38.85</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.2</v>
+        <v>90.7</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.8</v>
+        <v>82.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.85</v>
+        <v>5.81</v>
       </c>
       <c r="L2" t="n">
-        <v>12.9</v>
+        <v>13.16</v>
       </c>
       <c r="M2" t="n">
         <v>11.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.86</v>
+        <v>14.36</v>
       </c>
       <c r="L3" t="n">
-        <v>30.14</v>
+        <v>30.44</v>
       </c>
       <c r="M3" t="n">
-        <v>22.51</v>
+        <v>22.47</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -780,10 +780,10 @@
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.18</v>
+        <v>5.71</v>
       </c>
       <c r="L4" t="n">
-        <v>41.29</v>
+        <v>39.08</v>
       </c>
       <c r="M4" t="n">
-        <v>39.22</v>
+        <v>39.28</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13.63</v>
+        <v>12.25</v>
       </c>
       <c r="L5" t="n">
-        <v>74.29000000000001</v>
+        <v>63.62</v>
       </c>
       <c r="M5" t="n">
-        <v>31.61</v>
+        <v>31.71</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>83.2</v>
+        <v>82.2</v>
       </c>
       <c r="I6" t="n">
         <v>89.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.79</v>
+        <v>5.03</v>
       </c>
       <c r="L6" t="n">
-        <v>14.6</v>
+        <v>14.55</v>
       </c>
       <c r="M6" t="n">
-        <v>14.5</v>
+        <v>14.45</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>62.6</v>
+        <v>62.8</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.62</v>
+        <v>-3.73</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>11.6</v>
+        <v>11.63</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1197,13 +1197,13 @@
         <v>61.6</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>50.9</v>
+        <v>39</v>
       </c>
       <c r="I8" t="n">
-        <v>64.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,62 +1211,66 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6.29</v>
+        <v>-5.18</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.539999999999999</v>
+        <v>-6.82</v>
       </c>
       <c r="M8" t="n">
-        <v>25.88</v>
+        <v>18.38</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1295,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.8</v>
+        <v>61.2</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>36.5</v>
+        <v>49.8</v>
       </c>
       <c r="I9" t="n">
-        <v>76.7</v>
+        <v>64.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-6.64</v>
+        <v>5.32</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.86</v>
+        <v>-9.48</v>
       </c>
       <c r="M9" t="n">
-        <v>18.33</v>
+        <v>25.89</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.63</v>
+        <v>-1.4</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.36</v>
+        <v>-19.77</v>
       </c>
       <c r="M10" t="n">
         <v>26.45</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56.2</v>
+        <v>53.8</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>46.7</v>
+        <v>39.6</v>
       </c>
       <c r="I12" t="n">
         <v>58.7</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.68</v>
+        <v>-4.19</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.36</v>
+        <v>-7.63</v>
       </c>
       <c r="M12" t="n">
-        <v>28.07</v>
+        <v>28.06</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43.3</v>
+        <v>41.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>15.9</v>
+        <v>12.2</v>
       </c>
       <c r="I13" t="n">
-        <v>23.8</v>
+        <v>22</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.09</v>
+        <v>-11.38</v>
       </c>
       <c r="L13" t="n">
-        <v>-31.36</v>
+        <v>-34.5</v>
       </c>
       <c r="M13" t="n">
-        <v>46.97</v>
+        <v>47.08</v>
       </c>
       <c r="N13" t="n">
-        <v>-38.85</v>
+        <v>-41.24</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.81</v>
+        <v>5.59</v>
       </c>
       <c r="L2" t="n">
-        <v>13.16</v>
+        <v>12.93</v>
       </c>
       <c r="M2" t="n">
-        <v>11.55</v>
+        <v>11.56</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14.36</v>
+        <v>13.66</v>
       </c>
       <c r="L3" t="n">
-        <v>30.44</v>
+        <v>29.63</v>
       </c>
       <c r="M3" t="n">
-        <v>22.47</v>
+        <v>22.49</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="G4" t="n">
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="I4" t="n">
         <v>45.6</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.71</v>
+        <v>5.36</v>
       </c>
       <c r="L4" t="n">
-        <v>39.08</v>
+        <v>38.62</v>
       </c>
       <c r="M4" t="n">
-        <v>39.28</v>
+        <v>39.3</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12.25</v>
+        <v>11.89</v>
       </c>
       <c r="L5" t="n">
-        <v>63.62</v>
+        <v>63.1</v>
       </c>
       <c r="M5" t="n">
-        <v>31.71</v>
+        <v>31.74</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>82.2</v>
+        <v>85</v>
       </c>
       <c r="I6" t="n">
         <v>89.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.03</v>
+        <v>6.43</v>
       </c>
       <c r="L6" t="n">
-        <v>14.55</v>
+        <v>16.08</v>
       </c>
       <c r="M6" t="n">
-        <v>14.45</v>
+        <v>14.48</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>62.8</v>
+        <v>62</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.73</v>
+        <v>-4.14</v>
       </c>
       <c r="L7" t="n">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>11.63</v>
+        <v>11.61</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.6</v>
+        <v>61.5</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>39</v>
+        <v>38.7</v>
       </c>
       <c r="I8" t="n">
-        <v>76.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.18</v>
+        <v>-5.35</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.82</v>
+        <v>-6.98</v>
       </c>
       <c r="M8" t="n">
-        <v>18.38</v>
+        <v>18.36</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.2</v>
+        <v>60.9</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>49.8</v>
+        <v>48.9</v>
       </c>
       <c r="I9" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5.32</v>
+        <v>4.86</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.48</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>25.89</v>
+        <v>25.91</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="I10" t="n">
         <v>61.9</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.77</v>
+        <v>-19.85</v>
       </c>
       <c r="M10" t="n">
         <v>26.45</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>39.6</v>
+        <v>37.8</v>
       </c>
       <c r="I12" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.19</v>
+        <v>-5.18</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.63</v>
+        <v>-8.59</v>
       </c>
       <c r="M12" t="n">
-        <v>28.06</v>
+        <v>28.1</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.7</v>
+        <v>40.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>12.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.38</v>
+        <v>-13.09</v>
       </c>
       <c r="L13" t="n">
-        <v>-34.5</v>
+        <v>-35.77</v>
       </c>
       <c r="M13" t="n">
-        <v>47.08</v>
+        <v>47.27</v>
       </c>
       <c r="N13" t="n">
-        <v>-41.24</v>
+        <v>-42.38</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.59</v>
+        <v>5.49</v>
       </c>
       <c r="L2" t="n">
-        <v>12.93</v>
+        <v>12.82</v>
       </c>
       <c r="M2" t="n">
         <v>11.56</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13.66</v>
+        <v>13.39</v>
       </c>
       <c r="L3" t="n">
-        <v>29.63</v>
+        <v>29.33</v>
       </c>
       <c r="M3" t="n">
-        <v>22.49</v>
+        <v>22.5</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.3</v>
+        <v>83.8</v>
       </c>
       <c r="G4" t="n">
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>99.5</v>
+        <v>98</v>
       </c>
       <c r="I4" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.36</v>
+        <v>4.65</v>
       </c>
       <c r="L4" t="n">
-        <v>38.62</v>
+        <v>37.68</v>
       </c>
       <c r="M4" t="n">
-        <v>39.3</v>
+        <v>39.35</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.1</v>
+        <v>57.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.89</v>
+        <v>10.49</v>
       </c>
       <c r="L5" t="n">
-        <v>63.1</v>
+        <v>61.05</v>
       </c>
       <c r="M5" t="n">
-        <v>31.74</v>
+        <v>31.88</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>85</v>
+        <v>85.5</v>
       </c>
       <c r="I6" t="n">
         <v>89.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.43</v>
+        <v>6.68</v>
       </c>
       <c r="L6" t="n">
-        <v>16.08</v>
+        <v>16.35</v>
       </c>
       <c r="M6" t="n">
-        <v>14.48</v>
+        <v>14.5</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.3</v>
+        <v>73.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>62</v>
+        <v>62.4</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.14</v>
+        <v>-3.97</v>
       </c>
       <c r="L7" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>38.7</v>
+        <v>39.2</v>
       </c>
       <c r="I8" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.35</v>
+        <v>-5.09</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.98</v>
+        <v>-6.73</v>
       </c>
       <c r="M8" t="n">
-        <v>18.36</v>
+        <v>18.38</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1305,7 +1305,7 @@
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
         <v>64.59999999999999</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4.86</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.869999999999999</v>
+        <v>-9.84</v>
       </c>
       <c r="M9" t="n">
         <v>25.91</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.3</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.3</v>
+        <v>33.6</v>
       </c>
       <c r="I10" t="n">
         <v>61.9</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.5</v>
+        <v>-1.9</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.85</v>
+        <v>-20.18</v>
       </c>
       <c r="M10" t="n">
-        <v>26.45</v>
+        <v>26.46</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>53.2</v>
+        <v>52.8</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>37.8</v>
+        <v>36.7</v>
       </c>
       <c r="I12" t="n">
         <v>58.6</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.18</v>
+        <v>-5.74</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.59</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>28.1</v>
+        <v>28.14</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40.5</v>
+        <v>39.9</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-13.09</v>
+        <v>-13.97</v>
       </c>
       <c r="L13" t="n">
-        <v>-35.77</v>
+        <v>-36.41</v>
       </c>
       <c r="M13" t="n">
-        <v>47.27</v>
+        <v>47.39</v>
       </c>
       <c r="N13" t="n">
-        <v>-42.38</v>
+        <v>-42.95</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.49</v>
+        <v>5.57</v>
       </c>
       <c r="L2" t="n">
-        <v>12.82</v>
+        <v>12.9</v>
       </c>
       <c r="M2" t="n">
         <v>11.56</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13.39</v>
+        <v>13.72</v>
       </c>
       <c r="L3" t="n">
-        <v>29.33</v>
+        <v>29.71</v>
       </c>
       <c r="M3" t="n">
-        <v>22.5</v>
+        <v>22.49</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -780,7 +780,7 @@
         <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="I4" t="n">
         <v>45.5</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="L4" t="n">
-        <v>37.68</v>
+        <v>37.81</v>
       </c>
       <c r="M4" t="n">
-        <v>39.35</v>
+        <v>39.34</v>
       </c>
       <c r="N4" t="n">
         <v>-23.17</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.9</v>
+        <v>58.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10.49</v>
+        <v>11.66</v>
       </c>
       <c r="L5" t="n">
-        <v>61.05</v>
+        <v>58.93</v>
       </c>
       <c r="M5" t="n">
-        <v>31.88</v>
+        <v>31.71</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>82.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>89.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.68</v>
+        <v>4.44</v>
       </c>
       <c r="L6" t="n">
-        <v>16.35</v>
+        <v>13.91</v>
       </c>
       <c r="M6" t="n">
-        <v>14.5</v>
+        <v>14.48</v>
       </c>
       <c r="N6" t="n">
         <v>-10.32</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>62.4</v>
+        <v>61.4</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.97</v>
+        <v>-4.48</v>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>1.08</v>
       </c>
       <c r="M7" t="n">
-        <v>11.62</v>
+        <v>11.6</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1197,13 +1197,13 @@
         <v>61.7</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>39.2</v>
+        <v>51.1</v>
       </c>
       <c r="I8" t="n">
-        <v>76.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,66 +1211,62 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-5.09</v>
+        <v>6.09</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.73</v>
+        <v>-8.82</v>
       </c>
       <c r="M8" t="n">
-        <v>18.38</v>
+        <v>25.87</v>
       </c>
       <c r="N8" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1276,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1299,16 +1295,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.9</v>
+        <v>60.7</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>36.3</v>
       </c>
       <c r="I9" t="n">
-        <v>64.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1312,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>-5.51</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.84</v>
+        <v>-10.1</v>
       </c>
       <c r="M9" t="n">
-        <v>25.91</v>
+        <v>18.44</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.6</v>
+        <v>33.3</v>
       </c>
       <c r="I10" t="n">
         <v>61.9</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.9</v>
+        <v>-1.97</v>
       </c>
       <c r="L10" t="n">
-        <v>-20.18</v>
+        <v>-20.47</v>
       </c>
       <c r="M10" t="n">
-        <v>26.46</v>
+        <v>26.44</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.8</v>
+        <v>53.5</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>36.7</v>
+        <v>38.7</v>
       </c>
       <c r="I12" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.74</v>
+        <v>-4.68</v>
       </c>
       <c r="L12" t="n">
-        <v>-9.119999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="M12" t="n">
-        <v>28.14</v>
+        <v>28.07</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39.9</v>
+        <v>40.9</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="I13" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-13.97</v>
+        <v>-11</v>
       </c>
       <c r="L13" t="n">
-        <v>-36.41</v>
+        <v>-37.37</v>
       </c>
       <c r="M13" t="n">
-        <v>47.39</v>
+        <v>47.07</v>
       </c>
       <c r="N13" t="n">
         <v>-42.95</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.5</v>
+        <v>89.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.7</v>
+        <v>78.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.57</v>
+        <v>3.68</v>
       </c>
       <c r="L2" t="n">
-        <v>12.9</v>
+        <v>11.58</v>
       </c>
       <c r="M2" t="n">
-        <v>11.56</v>
+        <v>11.64</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>88.7</v>
+        <v>86.2</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>74.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13.72</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>29.71</v>
+        <v>23.99</v>
       </c>
       <c r="M3" t="n">
-        <v>22.49</v>
+        <v>22.77</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.8</v>
+        <v>84.2</v>
       </c>
       <c r="G4" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>98.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>45.5</v>
+        <v>88.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.75</v>
+        <v>9.08</v>
       </c>
       <c r="L4" t="n">
-        <v>37.81</v>
+        <v>19.52</v>
       </c>
       <c r="M4" t="n">
-        <v>39.34</v>
+        <v>14.85</v>
       </c>
       <c r="N4" t="n">
-        <v>-23.17</v>
+        <v>-10.32</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58.2</v>
+        <v>57.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.66</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>58.93</v>
+        <v>54.23</v>
       </c>
       <c r="M5" t="n">
-        <v>31.71</v>
+        <v>32.19</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -965,102 +965,102 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>81.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>81.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="I6" t="n">
-        <v>89.3</v>
+        <v>45.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.44</v>
+        <v>-2.75</v>
       </c>
       <c r="L6" t="n">
-        <v>13.91</v>
+        <v>30.2</v>
       </c>
       <c r="M6" t="n">
-        <v>14.48</v>
+        <v>39.65</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.32</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>61.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.48</v>
+        <v>-2.72</v>
       </c>
       <c r="L7" t="n">
-        <v>1.08</v>
+        <v>3.79</v>
       </c>
       <c r="M7" t="n">
-        <v>11.6</v>
+        <v>11.64</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>51.1</v>
+        <v>38.8</v>
       </c>
       <c r="I8" t="n">
-        <v>64.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,62 +1211,66 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6.09</v>
+        <v>-4.16</v>
       </c>
       <c r="L8" t="n">
         <v>-8.82</v>
       </c>
       <c r="M8" t="n">
-        <v>25.87</v>
+        <v>18.4</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.72</v>
+        <v>-20.62</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1295,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.7</v>
+        <v>61.5</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>36.3</v>
+        <v>50.6</v>
       </c>
       <c r="I9" t="n">
-        <v>76.5</v>
+        <v>64.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-5.51</v>
+        <v>5.34</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.1</v>
+        <v>-8.27</v>
       </c>
       <c r="M9" t="n">
-        <v>18.44</v>
+        <v>25.86</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.62</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58.9</v>
+        <v>59.1</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.3</v>
+        <v>33.9</v>
       </c>
       <c r="I10" t="n">
         <v>61.9</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.97</v>
+        <v>-1.61</v>
       </c>
       <c r="L10" t="n">
-        <v>-20.47</v>
+        <v>-20.18</v>
       </c>
       <c r="M10" t="n">
-        <v>26.44</v>
+        <v>26.48</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>53.5</v>
+        <v>50.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>38.7</v>
+        <v>30.8</v>
       </c>
       <c r="I12" t="n">
-        <v>58.7</v>
+        <v>57.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.68</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.1</v>
+        <v>-12.55</v>
       </c>
       <c r="M12" t="n">
-        <v>28.07</v>
+        <v>28.25</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.91</v>
+        <v>-27.65</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40.9</v>
+        <v>40.1</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>10.6</v>
+        <v>8.5</v>
       </c>
       <c r="I13" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11</v>
+        <v>-12.25</v>
       </c>
       <c r="L13" t="n">
-        <v>-37.37</v>
+        <v>-38.24</v>
       </c>
       <c r="M13" t="n">
-        <v>47.07</v>
+        <v>47.19</v>
       </c>
       <c r="N13" t="n">
-        <v>-42.95</v>
+        <v>-43.75</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.68</v>
+        <v>3.86</v>
       </c>
       <c r="L2" t="n">
-        <v>11.58</v>
+        <v>11.77</v>
       </c>
       <c r="M2" t="n">
-        <v>11.64</v>
+        <v>11.62</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -675,7 +675,7 @@
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="I3" t="n">
         <v>74</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.470000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>23.99</v>
+        <v>23.87</v>
       </c>
       <c r="M3" t="n">
-        <v>22.77</v>
+        <v>22.79</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.2</v>
+        <v>84.8</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>90.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>88.8</v>
+        <v>88.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.08</v>
+        <v>10.02</v>
       </c>
       <c r="L4" t="n">
-        <v>19.52</v>
+        <v>20.54</v>
       </c>
       <c r="M4" t="n">
-        <v>14.85</v>
+        <v>15.07</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.359999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="L5" t="n">
-        <v>54.23</v>
+        <v>53.7</v>
       </c>
       <c r="M5" t="n">
-        <v>32.19</v>
+        <v>32.25</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>75.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-2.75</v>
+        <v>-3.11</v>
       </c>
       <c r="L6" t="n">
-        <v>30.2</v>
+        <v>29.73</v>
       </c>
       <c r="M6" t="n">
-        <v>39.65</v>
+        <v>39.69</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74.5</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>65.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.72</v>
+        <v>-3.51</v>
       </c>
       <c r="L7" t="n">
-        <v>3.79</v>
+        <v>2.95</v>
       </c>
       <c r="M7" t="n">
-        <v>11.64</v>
+        <v>11.59</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>38.8</v>
+        <v>39.4</v>
       </c>
       <c r="I8" t="n">
         <v>76.59999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.16</v>
+        <v>-3.83</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.82</v>
+        <v>-8.51</v>
       </c>
       <c r="M8" t="n">
-        <v>18.4</v>
+        <v>18.42</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5.34</v>
+        <v>5.43</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.27</v>
+        <v>-8.19</v>
       </c>
       <c r="M9" t="n">
         <v>25.86</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.1</v>
+        <v>59.5</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.9</v>
+        <v>34.9</v>
       </c>
       <c r="I10" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.61</v>
+        <v>-1.07</v>
       </c>
       <c r="L10" t="n">
-        <v>-20.18</v>
+        <v>-19.74</v>
       </c>
       <c r="M10" t="n">
-        <v>26.48</v>
+        <v>26.51</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.7</v>
+        <v>51.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30.8</v>
+        <v>32</v>
       </c>
       <c r="I12" t="n">
-        <v>57.9</v>
+        <v>58.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-12.55</v>
+        <v>-11.92</v>
       </c>
       <c r="M12" t="n">
-        <v>28.25</v>
+        <v>28.16</v>
       </c>
       <c r="N12" t="n">
-        <v>-27.65</v>
+        <v>-27.12</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40.1</v>
+        <v>41.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="I13" t="n">
-        <v>20.1</v>
+        <v>21.1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.25</v>
+        <v>-10.52</v>
       </c>
       <c r="L13" t="n">
-        <v>-38.24</v>
+        <v>-37.03</v>
       </c>
       <c r="M13" t="n">
-        <v>47.19</v>
+        <v>47.04</v>
       </c>
       <c r="N13" t="n">
-        <v>-43.75</v>
+        <v>-42.65</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="L2" t="n">
-        <v>11.77</v>
+        <v>12.05</v>
       </c>
       <c r="M2" t="n">
-        <v>11.62</v>
+        <v>11.59</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>92.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>74</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.369999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="L3" t="n">
-        <v>23.87</v>
+        <v>24.22</v>
       </c>
       <c r="M3" t="n">
-        <v>22.79</v>
+        <v>22.75</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>92.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="I4" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.02</v>
+        <v>10.44</v>
       </c>
       <c r="L4" t="n">
-        <v>20.54</v>
+        <v>21.01</v>
       </c>
       <c r="M4" t="n">
-        <v>15.07</v>
+        <v>15.18</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7.98</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>53.7</v>
+        <v>54.49</v>
       </c>
       <c r="M5" t="n">
-        <v>32.25</v>
+        <v>32.16</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>75.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>75.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-3.11</v>
+        <v>-2.27</v>
       </c>
       <c r="L6" t="n">
-        <v>29.73</v>
+        <v>30.85</v>
       </c>
       <c r="M6" t="n">
-        <v>39.69</v>
+        <v>39.59</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.51</v>
+        <v>-3.62</v>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="M7" t="n">
-        <v>11.59</v>
+        <v>11.58</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.7</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="I8" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.83</v>
+        <v>-3.46</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.51</v>
+        <v>-8.15</v>
       </c>
       <c r="M8" t="n">
-        <v>18.42</v>
+        <v>18.45</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.6</v>
+        <v>61.5</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.19</v>
+        <v>-8.23</v>
       </c>
       <c r="M9" t="n">
         <v>25.86</v>
@@ -1406,7 +1406,7 @@
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="I10" t="n">
         <v>61.8</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.07</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.74</v>
+        <v>-19.64</v>
       </c>
       <c r="M10" t="n">
         <v>26.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="I12" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.029999999999999</v>
+        <v>-7.89</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.92</v>
+        <v>-11.78</v>
       </c>
       <c r="M12" t="n">
-        <v>28.16</v>
+        <v>28.14</v>
       </c>
       <c r="N12" t="n">
-        <v>-27.12</v>
+        <v>-27.01</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>11.5</v>
+        <v>13.7</v>
       </c>
       <c r="I13" t="n">
-        <v>21.1</v>
+        <v>21.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.52</v>
+        <v>-9.18</v>
       </c>
       <c r="L13" t="n">
-        <v>-37.03</v>
+        <v>-36.08</v>
       </c>
       <c r="M13" t="n">
-        <v>47.04</v>
+        <v>46.96</v>
       </c>
       <c r="N13" t="n">
-        <v>-42.65</v>
+        <v>-41.79</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.12</v>
+        <v>5.06</v>
       </c>
       <c r="L2" t="n">
-        <v>12.05</v>
+        <v>13.06</v>
       </c>
       <c r="M2" t="n">
-        <v>11.59</v>
+        <v>11.55</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>93.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.67</v>
+        <v>12.07</v>
       </c>
       <c r="L3" t="n">
-        <v>24.22</v>
+        <v>28.1</v>
       </c>
       <c r="M3" t="n">
-        <v>22.75</v>
+        <v>22.49</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>93.2</v>
+        <v>88</v>
       </c>
       <c r="I4" t="n">
-        <v>88.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.44</v>
+        <v>7.8</v>
       </c>
       <c r="L4" t="n">
-        <v>21.01</v>
+        <v>18.12</v>
       </c>
       <c r="M4" t="n">
-        <v>15.18</v>
+        <v>14.62</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.539999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="L5" t="n">
-        <v>54.49</v>
+        <v>53.04</v>
       </c>
       <c r="M5" t="n">
-        <v>32.16</v>
+        <v>31.85</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>76.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-2.27</v>
+        <v>2.05</v>
       </c>
       <c r="L6" t="n">
-        <v>30.85</v>
+        <v>36.63</v>
       </c>
       <c r="M6" t="n">
-        <v>39.59</v>
+        <v>39.32</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>63.6</v>
+        <v>64.2</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.62</v>
+        <v>-3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="M7" t="n">
-        <v>11.58</v>
+        <v>11.59</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>62.6</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>40.1</v>
+        <v>42.1</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.46</v>
+        <v>-3.03</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.15</v>
+        <v>-6.02</v>
       </c>
       <c r="M8" t="n">
-        <v>18.45</v>
+        <v>18.5</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.5</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>50.7</v>
+        <v>49.2</v>
       </c>
       <c r="I9" t="n">
         <v>64.7</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5.39</v>
+        <v>4.55</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.23</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>25.86</v>
+        <v>25.88</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.5</v>
+        <v>59.7</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>35.1</v>
+        <v>35.5</v>
       </c>
       <c r="I10" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.2</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.64</v>
+        <v>-18.72</v>
       </c>
       <c r="M10" t="n">
-        <v>26.51</v>
+        <v>26.44</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.3</v>
+        <v>52.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>32.3</v>
+        <v>36</v>
       </c>
       <c r="I12" t="n">
-        <v>58.5</v>
+        <v>58.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.89</v>
+        <v>-5.89</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.78</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>28.14</v>
+        <v>27.98</v>
       </c>
       <c r="N12" t="n">
-        <v>-27.01</v>
+        <v>-26.91</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>42.2</v>
+        <v>41.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>13.7</v>
+        <v>12.8</v>
       </c>
       <c r="I13" t="n">
-        <v>21.8</v>
+        <v>20.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.18</v>
+        <v>-10.14</v>
       </c>
       <c r="L13" t="n">
-        <v>-36.08</v>
+        <v>-35.81</v>
       </c>
       <c r="M13" t="n">
-        <v>46.96</v>
+        <v>47.03</v>
       </c>
       <c r="N13" t="n">
-        <v>-41.79</v>
+        <v>-42.95</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>81.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.06</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>13.06</v>
+        <v>11.54</v>
       </c>
       <c r="M2" t="n">
-        <v>11.55</v>
+        <v>11.58</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>88.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>74.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.07</v>
+        <v>7.26</v>
       </c>
       <c r="L3" t="n">
-        <v>28.1</v>
+        <v>22.72</v>
       </c>
       <c r="M3" t="n">
-        <v>22.49</v>
+        <v>22.67</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>88</v>
+        <v>91.5</v>
       </c>
       <c r="I4" t="n">
-        <v>89.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.8</v>
+        <v>9.69</v>
       </c>
       <c r="L4" t="n">
-        <v>18.12</v>
+        <v>19.83</v>
       </c>
       <c r="M4" t="n">
-        <v>14.62</v>
+        <v>14.69</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7.63</v>
+        <v>9.4</v>
       </c>
       <c r="L5" t="n">
-        <v>53.04</v>
+        <v>55.56</v>
       </c>
       <c r="M5" t="n">
-        <v>31.85</v>
+        <v>31.76</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -970,44 +970,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>82.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>94.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.05</v>
+        <v>-5.94</v>
       </c>
       <c r="L6" t="n">
-        <v>36.63</v>
+        <v>27.2</v>
       </c>
       <c r="M6" t="n">
-        <v>39.32</v>
+        <v>39.59</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>64.2</v>
+        <v>63.9</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.35</v>
+        <v>-2.5</v>
       </c>
       <c r="L7" t="n">
-        <v>3.12</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>11.59</v>
+        <v>11.6</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1200,7 +1200,7 @@
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.03</v>
+        <v>-3.14</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.02</v>
+        <v>-6.14</v>
       </c>
       <c r="M8" t="n">
-        <v>18.5</v>
+        <v>18.48</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>61.2</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>49.2</v>
+        <v>40.1</v>
       </c>
       <c r="I9" t="n">
-        <v>64.7</v>
+        <v>61.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4.55</v>
+        <v>1.39</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.949999999999999</v>
+        <v>-16.58</v>
       </c>
       <c r="M9" t="n">
-        <v>25.88</v>
+        <v>26.73</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-25.51</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.7</v>
+        <v>60.8</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>35.5</v>
+        <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>61.9</v>
+        <v>64.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.2</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.72</v>
+        <v>-8.18</v>
       </c>
       <c r="M10" t="n">
-        <v>26.44</v>
+        <v>25.84</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.51</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.6</v>
+        <v>50.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>30.2</v>
       </c>
       <c r="I12" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.89</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-9.869999999999999</v>
+        <v>-12.6</v>
       </c>
       <c r="M12" t="n">
-        <v>27.98</v>
+        <v>28.03</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.7</v>
+        <v>42.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>12.8</v>
+        <v>15.1</v>
       </c>
       <c r="I13" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.14</v>
+        <v>-8.77</v>
       </c>
       <c r="L13" t="n">
-        <v>-35.81</v>
+        <v>-34.83</v>
       </c>
       <c r="M13" t="n">
-        <v>47.03</v>
+        <v>47.2</v>
       </c>
       <c r="N13" t="n">
         <v>-42.95</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>11.54</v>
+        <v>11.38</v>
       </c>
       <c r="M2" t="n">
-        <v>11.58</v>
+        <v>11.59</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>90.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.26</v>
+        <v>6.34</v>
       </c>
       <c r="L3" t="n">
-        <v>22.72</v>
+        <v>21.67</v>
       </c>
       <c r="M3" t="n">
-        <v>22.67</v>
+        <v>22.8</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>91.5</v>
+        <v>91.2</v>
       </c>
       <c r="I4" t="n">
         <v>89</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.69</v>
+        <v>9.56</v>
       </c>
       <c r="L4" t="n">
-        <v>19.83</v>
+        <v>19.68</v>
       </c>
       <c r="M4" t="n">
-        <v>14.69</v>
+        <v>14.68</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -879,30 +879,30 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="I5" t="n">
-        <v>58.1</v>
+        <v>57.6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.4</v>
+        <v>5.34</v>
       </c>
       <c r="L5" t="n">
-        <v>55.56</v>
+        <v>49.8</v>
       </c>
       <c r="M5" t="n">
-        <v>31.76</v>
+        <v>32.13</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>69.90000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>45.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-5.94</v>
+        <v>-1.99</v>
       </c>
       <c r="L6" t="n">
-        <v>27.2</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>39.59</v>
+        <v>11.59</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>63.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.5</v>
+        <v>-6.34</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>26.67</v>
       </c>
       <c r="M7" t="n">
-        <v>11.6</v>
+        <v>39.64</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.14</v>
+        <v>-3.19</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.14</v>
+        <v>-6.18</v>
       </c>
       <c r="M8" t="n">
-        <v>18.48</v>
+        <v>18.47</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.2</v>
+        <v>61.1</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="I9" t="n">
         <v>61.5</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="L9" t="n">
-        <v>-16.58</v>
+        <v>-16.6</v>
       </c>
       <c r="M9" t="n">
         <v>26.73</v>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.8</v>
+        <v>61.1</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>48.7</v>
+        <v>49.5</v>
       </c>
       <c r="I10" t="n">
         <v>64.7</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.18</v>
+        <v>-7.78</v>
       </c>
       <c r="M10" t="n">
-        <v>25.84</v>
+        <v>25.86</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30.2</v>
+        <v>30.6</v>
       </c>
       <c r="I12" t="n">
         <v>58.7</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.130000000000001</v>
+        <v>-8.93</v>
       </c>
       <c r="L12" t="n">
-        <v>-12.6</v>
+        <v>-12.41</v>
       </c>
       <c r="M12" t="n">
-        <v>28.03</v>
+        <v>28.02</v>
       </c>
       <c r="N12" t="n">
         <v>-26.91</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="I13" t="n">
         <v>20.7</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-8.77</v>
+        <v>-8.93</v>
       </c>
       <c r="L13" t="n">
-        <v>-34.83</v>
+        <v>-34.95</v>
       </c>
       <c r="M13" t="n">
-        <v>47.2</v>
+        <v>47.19</v>
       </c>
       <c r="N13" t="n">
         <v>-42.95</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.3</v>
+        <v>89.2</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="L2" t="n">
-        <v>11.38</v>
+        <v>11.12</v>
       </c>
       <c r="M2" t="n">
-        <v>11.59</v>
+        <v>11.62</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>88.8</v>
+        <v>91.8</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.34</v>
+        <v>9.83</v>
       </c>
       <c r="L3" t="n">
-        <v>21.67</v>
+        <v>19.97</v>
       </c>
       <c r="M3" t="n">
-        <v>22.8</v>
+        <v>14.71</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>91.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>89</v>
+        <v>73.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.56</v>
+        <v>5.75</v>
       </c>
       <c r="L4" t="n">
-        <v>19.68</v>
+        <v>20.99</v>
       </c>
       <c r="M4" t="n">
-        <v>14.68</v>
+        <v>22.89</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>99.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.34</v>
+        <v>3.33</v>
       </c>
       <c r="L5" t="n">
-        <v>49.8</v>
+        <v>46.94</v>
       </c>
       <c r="M5" t="n">
-        <v>32.13</v>
+        <v>32.47</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74.3</v>
+        <v>74.5</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>64.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-1.99</v>
+        <v>-1.72</v>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="M6" t="n">
-        <v>11.59</v>
+        <v>11.6</v>
       </c>
       <c r="N6" t="n">
         <v>-10.18</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>69.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.34</v>
+        <v>-7.03</v>
       </c>
       <c r="L7" t="n">
-        <v>26.67</v>
+        <v>25.73</v>
       </c>
       <c r="M7" t="n">
-        <v>39.64</v>
+        <v>39.74</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>41.8</v>
+        <v>42.1</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.19</v>
+        <v>-3.04</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.18</v>
+        <v>-6.04</v>
       </c>
       <c r="M8" t="n">
-        <v>18.47</v>
+        <v>18.49</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.1</v>
+        <v>60.9</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
-        <v>61.5</v>
+        <v>64.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.38</v>
+        <v>3.84</v>
       </c>
       <c r="L9" t="n">
-        <v>-16.6</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>26.73</v>
+        <v>25.85</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.51</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>61.1</v>
+        <v>60.8</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>49.5</v>
+        <v>39</v>
       </c>
       <c r="I10" t="n">
-        <v>64.7</v>
+        <v>61.6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4.15</v>
+        <v>0.77</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.78</v>
+        <v>-17.1</v>
       </c>
       <c r="M10" t="n">
-        <v>25.86</v>
+        <v>26.65</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.51</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30.6</v>
+        <v>30.1</v>
       </c>
       <c r="I12" t="n">
         <v>58.7</v>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.93</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-12.41</v>
+        <v>-12.67</v>
       </c>
       <c r="M12" t="n">
-        <v>28.02</v>
+        <v>28.04</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.91</v>
+        <v>-26.96</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>42.4</v>
+        <v>41.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>14.8</v>
+        <v>13.2</v>
       </c>
       <c r="I13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-8.93</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-34.95</v>
+        <v>-35.61</v>
       </c>
       <c r="M13" t="n">
-        <v>47.19</v>
+        <v>47.12</v>
       </c>
       <c r="N13" t="n">
         <v>-42.95</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.21</v>
+        <v>3.51</v>
       </c>
       <c r="L2" t="n">
-        <v>11.12</v>
+        <v>11.45</v>
       </c>
       <c r="M2" t="n">
-        <v>11.62</v>
+        <v>11.59</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.7</v>
+        <v>85.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>91.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>89</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.83</v>
+        <v>6.98</v>
       </c>
       <c r="L3" t="n">
-        <v>19.97</v>
+        <v>22.4</v>
       </c>
       <c r="M3" t="n">
-        <v>14.71</v>
+        <v>22.71</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.3</v>
+        <v>85.2</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>87.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="I4" t="n">
-        <v>73.8</v>
+        <v>88.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.75</v>
+        <v>10.69</v>
       </c>
       <c r="L4" t="n">
-        <v>20.99</v>
+        <v>20.92</v>
       </c>
       <c r="M4" t="n">
-        <v>22.89</v>
+        <v>14.81</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -885,10 +885,10 @@
         <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>94.90000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="I5" t="n">
-        <v>57.1</v>
+        <v>57.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3.33</v>
+        <v>5.55</v>
       </c>
       <c r="L5" t="n">
-        <v>46.94</v>
+        <v>42.58</v>
       </c>
       <c r="M5" t="n">
-        <v>32.47</v>
+        <v>32.08</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74.5</v>
+        <v>74.3</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>65.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90000000000001</v>
+        <v>45.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-1.72</v>
+        <v>-5.74</v>
       </c>
       <c r="L6" t="n">
-        <v>2.14</v>
+        <v>27.48</v>
       </c>
       <c r="M6" t="n">
-        <v>11.6</v>
+        <v>39.57</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I7" t="n">
-        <v>44.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.03</v>
+        <v>-2.36</v>
       </c>
       <c r="L7" t="n">
-        <v>25.73</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>39.74</v>
+        <v>11.6</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.6</v>
+        <v>62.8</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42.1</v>
+        <v>42.6</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.04</v>
+        <v>-3.24</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.04</v>
+        <v>-5.09</v>
       </c>
       <c r="M8" t="n">
-        <v>18.49</v>
+        <v>18.46</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>60.9</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>39.2</v>
       </c>
       <c r="I9" t="n">
-        <v>64.7</v>
+        <v>61.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.84</v>
+        <v>-0.16</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.050000000000001</v>
+        <v>-15.13</v>
       </c>
       <c r="M9" t="n">
-        <v>25.85</v>
+        <v>26.52</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-25.51</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>60.8</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>39</v>
+        <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>61.6</v>
+        <v>64.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.77</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>-17.1</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>26.65</v>
+        <v>25.84</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.51</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.27</v>
       </c>
       <c r="L12" t="n">
-        <v>-12.67</v>
+        <v>-12.74</v>
       </c>
       <c r="M12" t="n">
         <v>28.04</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.96</v>
+        <v>-27.01</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="I13" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.859999999999999</v>
+        <v>-12.14</v>
       </c>
       <c r="L13" t="n">
-        <v>-35.61</v>
+        <v>-33.72</v>
       </c>
       <c r="M13" t="n">
-        <v>47.12</v>
+        <v>47.01</v>
       </c>
       <c r="N13" t="n">
         <v>-42.95</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.2</v>
+        <v>79</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.51</v>
+        <v>4.38</v>
       </c>
       <c r="L2" t="n">
-        <v>11.45</v>
+        <v>11.02</v>
       </c>
       <c r="M2" t="n">
-        <v>11.59</v>
+        <v>11.39</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>90.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>74.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.98</v>
+        <v>7.91</v>
       </c>
       <c r="L3" t="n">
-        <v>22.4</v>
+        <v>20.53</v>
       </c>
       <c r="M3" t="n">
-        <v>22.71</v>
+        <v>22.5</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85.2</v>
+        <v>84.5</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>93.5</v>
+        <v>91.2</v>
       </c>
       <c r="I4" t="n">
-        <v>88.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.69</v>
+        <v>8.33</v>
       </c>
       <c r="L4" t="n">
-        <v>20.92</v>
+        <v>21.68</v>
       </c>
       <c r="M4" t="n">
-        <v>14.81</v>
+        <v>14.78</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>80.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>94.5</v>
+        <v>97.8</v>
       </c>
       <c r="I5" t="n">
         <v>57.7</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.55</v>
+        <v>7.58</v>
       </c>
       <c r="L5" t="n">
-        <v>42.58</v>
+        <v>43.91</v>
       </c>
       <c r="M5" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74.3</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>70.40000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="I6" t="n">
-        <v>45.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-5.74</v>
+        <v>-4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>27.48</v>
+        <v>1.08</v>
       </c>
       <c r="M6" t="n">
-        <v>39.57</v>
+        <v>11.57</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>64.2</v>
+        <v>64.7</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>45.4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.36</v>
+        <v>-5.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>19.24</v>
       </c>
       <c r="M7" t="n">
-        <v>11.6</v>
+        <v>39.43</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.8</v>
+        <v>62.4</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="I8" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.24</v>
+        <v>-3.48</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.09</v>
+        <v>-6.12</v>
       </c>
       <c r="M8" t="n">
-        <v>18.46</v>
+        <v>18.52</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>39.2</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-0.16</v>
+        <v>3.96</v>
       </c>
       <c r="L9" t="n">
-        <v>-15.13</v>
+        <v>-8.26</v>
       </c>
       <c r="M9" t="n">
-        <v>26.52</v>
+        <v>25.74</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.51</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.8</v>
+        <v>60.6</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>48.6</v>
+        <v>37.8</v>
       </c>
       <c r="I10" t="n">
-        <v>64.7</v>
+        <v>62.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>-1.33</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.220000000000001</v>
+        <v>-15.11</v>
       </c>
       <c r="M10" t="n">
-        <v>25.84</v>
+        <v>26.05</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.51</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.5</v>
+        <v>49.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>27.7</v>
       </c>
       <c r="I12" t="n">
-        <v>58.6</v>
+        <v>58.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.27</v>
+        <v>-9.93</v>
       </c>
       <c r="L12" t="n">
-        <v>-12.74</v>
+        <v>-14.8</v>
       </c>
       <c r="M12" t="n">
-        <v>28.04</v>
+        <v>27.92</v>
       </c>
       <c r="N12" t="n">
-        <v>-27.01</v>
+        <v>-27.92</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.4</v>
+        <v>39.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>11.8</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>20.9</v>
+        <v>22.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.14</v>
+        <v>-16.6</v>
       </c>
       <c r="L13" t="n">
-        <v>-33.72</v>
+        <v>-36.15</v>
       </c>
       <c r="M13" t="n">
-        <v>47.01</v>
+        <v>45.83</v>
       </c>
       <c r="N13" t="n">
         <v>-42.95</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.38</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>11.02</v>
+        <v>11.25</v>
       </c>
       <c r="M2" t="n">
         <v>11.39</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.2</v>
+        <v>85.5</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>89.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>74.40000000000001</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.91</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>20.53</v>
+        <v>20.98</v>
       </c>
       <c r="M3" t="n">
-        <v>22.5</v>
+        <v>22.52</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.5</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>91.2</v>
+        <v>90</v>
       </c>
       <c r="I4" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8.33</v>
+        <v>7.75</v>
       </c>
       <c r="L4" t="n">
-        <v>21.68</v>
+        <v>21.02</v>
       </c>
       <c r="M4" t="n">
-        <v>14.78</v>
+        <v>14.81</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82</v>
+        <v>82.8</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7.58</v>
+        <v>8.57</v>
       </c>
       <c r="L5" t="n">
-        <v>43.91</v>
+        <v>45.24</v>
       </c>
       <c r="M5" t="n">
-        <v>32.07</v>
+        <v>32.09</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -987,49 +987,49 @@
         <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>61.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-4.7</v>
+        <v>-4.84</v>
       </c>
       <c r="L6" t="n">
-        <v>1.08</v>
+        <v>20.25</v>
       </c>
       <c r="M6" t="n">
-        <v>11.57</v>
+        <v>39.46</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>64.7</v>
+        <v>60.7</v>
       </c>
       <c r="I7" t="n">
-        <v>45.4</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.64</v>
+        <v>-4.93</v>
       </c>
       <c r="L7" t="n">
-        <v>19.24</v>
+        <v>0.84</v>
       </c>
       <c r="M7" t="n">
-        <v>39.43</v>
+        <v>11.58</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="I8" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.48</v>
+        <v>-3.27</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.12</v>
+        <v>-5.92</v>
       </c>
       <c r="M8" t="n">
-        <v>18.52</v>
+        <v>18.5</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I9" t="n">
-        <v>64.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.96</v>
+        <v>-0.67</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.26</v>
+        <v>-14.54</v>
       </c>
       <c r="M9" t="n">
-        <v>25.74</v>
+        <v>26.05</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-25.51</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.6</v>
+        <v>60.9</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>37.8</v>
+        <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>62.5</v>
+        <v>64.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-1.33</v>
+        <v>3.82</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.11</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>26.05</v>
+        <v>25.75</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.51</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="I12" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.93</v>
+        <v>-10.03</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.8</v>
+        <v>-14.89</v>
       </c>
       <c r="M12" t="n">
-        <v>27.92</v>
+        <v>27.93</v>
       </c>
       <c r="N12" t="n">
-        <v>-27.92</v>
+        <v>-28</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-16.6</v>
+        <v>-16.56</v>
       </c>
       <c r="L13" t="n">
-        <v>-36.15</v>
+        <v>-36.12</v>
       </c>
       <c r="M13" t="n">
         <v>45.83</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="L2" t="n">
-        <v>11.25</v>
+        <v>10.83</v>
       </c>
       <c r="M2" t="n">
-        <v>11.39</v>
+        <v>11.42</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>90.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="I3" t="n">
-        <v>74.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.300000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="L3" t="n">
-        <v>20.98</v>
+        <v>20.21</v>
       </c>
       <c r="M3" t="n">
-        <v>22.52</v>
+        <v>14.81</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84</v>
+        <v>84.2</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>90</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>88.8</v>
+        <v>74.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.75</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>21.02</v>
+        <v>20.61</v>
       </c>
       <c r="M4" t="n">
-        <v>14.81</v>
+        <v>22.53</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>66.40000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="I6" t="n">
-        <v>45.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-4.84</v>
+        <v>-2.69</v>
       </c>
       <c r="L6" t="n">
-        <v>20.25</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>39.46</v>
+        <v>11.59</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>60.7</v>
+        <v>63.8</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.93</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.84</v>
+        <v>22.33</v>
       </c>
       <c r="M7" t="n">
-        <v>11.58</v>
+        <v>39.49</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.9</v>
+        <v>60.1</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>48.7</v>
+        <v>46.6</v>
       </c>
       <c r="I10" t="n">
         <v>64.8</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.82</v>
+        <v>1.94</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.380000000000001</v>
+        <v>-8.15</v>
       </c>
       <c r="M10" t="n">
-        <v>25.75</v>
+        <v>25.79</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.6</v>
+        <v>49.9</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="I12" t="n">
-        <v>58.1</v>
+        <v>58.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.03</v>
+        <v>-10.01</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.89</v>
+        <v>-14.3</v>
       </c>
       <c r="M12" t="n">
-        <v>27.93</v>
+        <v>27.95</v>
       </c>
       <c r="N12" t="n">
-        <v>-28</v>
+        <v>-27.01</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.2</v>
+        <v>76.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="L2" t="n">
-        <v>10.83</v>
+        <v>10.23</v>
       </c>
       <c r="M2" t="n">
         <v>11.42</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>91.8</v>
+        <v>91.5</v>
       </c>
       <c r="I3" t="n">
         <v>88.8</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.68</v>
+        <v>8.16</v>
       </c>
       <c r="L3" t="n">
-        <v>20.21</v>
+        <v>22.48</v>
       </c>
       <c r="M3" t="n">
         <v>14.81</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,83 +774,83 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.2</v>
+        <v>82.8</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>86.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>74.3</v>
+        <v>57.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="L4" t="n">
-        <v>20.61</v>
+        <v>46.3</v>
       </c>
       <c r="M4" t="n">
-        <v>22.53</v>
+        <v>32.07</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.59</v>
+        <v>-20.33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.8</v>
+        <v>81.3</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>78.5</v>
       </c>
       <c r="I5" t="n">
-        <v>57.6</v>
+        <v>74.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.57</v>
+        <v>5.99</v>
       </c>
       <c r="L5" t="n">
-        <v>45.24</v>
+        <v>19.01</v>
       </c>
       <c r="M5" t="n">
-        <v>32.09</v>
+        <v>22.57</v>
       </c>
       <c r="N5" t="n">
-        <v>-20.33</v>
+        <v>-15.59</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>63.7</v>
+        <v>61</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-2.69</v>
+        <v>-4.79</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="M6" t="n">
-        <v>11.59</v>
+        <v>11.55</v>
       </c>
       <c r="N6" t="n">
         <v>-10.18</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>63.8</v>
+        <v>61.8</v>
       </c>
       <c r="I7" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-8.210000000000001</v>
+        <v>-6.68</v>
       </c>
       <c r="L7" t="n">
-        <v>22.33</v>
+        <v>16.83</v>
       </c>
       <c r="M7" t="n">
-        <v>39.49</v>
+        <v>39.61</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.6</v>
+        <v>63.4</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>41.9</v>
+        <v>44.2</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.27</v>
+        <v>-1.62</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.92</v>
+        <v>-5.44</v>
       </c>
       <c r="M8" t="n">
-        <v>18.5</v>
+        <v>18.47</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>60.5</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>39</v>
+        <v>47.6</v>
       </c>
       <c r="I9" t="n">
-        <v>62.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-0.67</v>
+        <v>2.63</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.54</v>
+        <v>-7.93</v>
       </c>
       <c r="M9" t="n">
-        <v>26.05</v>
+        <v>25.7</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.51</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,35 +1381,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.1</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>46.6</v>
+        <v>33.1</v>
       </c>
       <c r="I10" t="n">
-        <v>64.8</v>
+        <v>62.4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.94</v>
+        <v>-4.82</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.15</v>
+        <v>-15.91</v>
       </c>
       <c r="M10" t="n">
-        <v>25.79</v>
+        <v>26.08</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-25.51</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
@@ -1607,7 +1607,7 @@
         <v>28</v>
       </c>
       <c r="I12" t="n">
-        <v>58.8</v>
+        <v>57.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.01</v>
+        <v>-9.35</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.3</v>
+        <v>-15.45</v>
       </c>
       <c r="M12" t="n">
-        <v>27.95</v>
+        <v>27.89</v>
       </c>
       <c r="N12" t="n">
-        <v>-27.01</v>
+        <v>-28.77</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39.3</v>
+        <v>39.1</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
         <v>22.6</v>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-16.56</v>
+        <v>-15.85</v>
       </c>
       <c r="L13" t="n">
-        <v>-36.12</v>
+        <v>-38.29</v>
       </c>
       <c r="M13" t="n">
-        <v>45.83</v>
+        <v>45.74</v>
       </c>
       <c r="N13" t="n">
-        <v>-42.95</v>
+        <v>-43.14</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>76.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.99</v>
+        <v>3.96</v>
       </c>
       <c r="L2" t="n">
-        <v>10.23</v>
+        <v>11.26</v>
       </c>
       <c r="M2" t="n">
-        <v>11.42</v>
+        <v>11.37</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.5</v>
+        <v>85.3</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>91.5</v>
+        <v>93.8</v>
       </c>
       <c r="I3" t="n">
-        <v>88.8</v>
+        <v>88.7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.16</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>22.48</v>
+        <v>23.76</v>
       </c>
       <c r="M3" t="n">
-        <v>14.81</v>
+        <v>14.92</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,83 +774,83 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>57.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.6</v>
+        <v>7.22</v>
       </c>
       <c r="L4" t="n">
-        <v>46.3</v>
+        <v>20.39</v>
       </c>
       <c r="M4" t="n">
-        <v>32.07</v>
+        <v>22.49</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.33</v>
+        <v>-15.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81.3</v>
+        <v>82.8</v>
       </c>
       <c r="G5" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>78.5</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>74.3</v>
+        <v>57.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.99</v>
+        <v>10.12</v>
       </c>
       <c r="L5" t="n">
-        <v>19.01</v>
+        <v>47</v>
       </c>
       <c r="M5" t="n">
-        <v>22.57</v>
+        <v>32.05</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.59</v>
+        <v>-20.33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>61</v>
+        <v>62.2</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-4.79</v>
+        <v>-4.18</v>
       </c>
       <c r="L6" t="n">
-        <v>1.08</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>11.55</v>
+        <v>11.57</v>
       </c>
       <c r="N6" t="n">
         <v>-10.18</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>61.8</v>
+        <v>66.5</v>
       </c>
       <c r="I7" t="n">
-        <v>45.1</v>
+        <v>45.4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-6.68</v>
+        <v>-4.39</v>
       </c>
       <c r="L7" t="n">
-        <v>16.83</v>
+        <v>19.69</v>
       </c>
       <c r="M7" t="n">
-        <v>39.61</v>
+        <v>39.43</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.4</v>
+        <v>63.9</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>44.2</v>
+        <v>45.9</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.62</v>
+        <v>-0.75</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.44</v>
+        <v>-4.61</v>
       </c>
       <c r="M8" t="n">
-        <v>18.47</v>
+        <v>18.49</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>47.6</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
         <v>64.90000000000001</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.93</v>
+        <v>-7.74</v>
       </c>
       <c r="M9" t="n">
         <v>25.7</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>59.6</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.1</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.82</v>
+        <v>-3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.91</v>
+        <v>-14.96</v>
       </c>
       <c r="M10" t="n">
-        <v>26.08</v>
+        <v>26.01</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.6</v>
+        <v>50.8</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I12" t="n">
-        <v>57.6</v>
+        <v>58.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.35</v>
+        <v>-7.73</v>
       </c>
       <c r="L12" t="n">
-        <v>-15.45</v>
+        <v>-13.93</v>
       </c>
       <c r="M12" t="n">
-        <v>27.89</v>
+        <v>27.88</v>
       </c>
       <c r="N12" t="n">
-        <v>-28.77</v>
+        <v>-28</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39.1</v>
+        <v>39.9</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="I13" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-15.85</v>
+        <v>-14.53</v>
       </c>
       <c r="L13" t="n">
-        <v>-38.29</v>
+        <v>-37.32</v>
       </c>
       <c r="M13" t="n">
         <v>45.74</v>
       </c>
       <c r="N13" t="n">
-        <v>-43.14</v>
+        <v>-42.95</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.5</v>
+        <v>89.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>11.26</v>
+        <v>10.98</v>
       </c>
       <c r="M2" t="n">
-        <v>11.37</v>
+        <v>11.38</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>93.8</v>
+        <v>94</v>
       </c>
       <c r="I3" t="n">
         <v>88.7</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.289999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>23.76</v>
+        <v>23.86</v>
       </c>
       <c r="M3" t="n">
-        <v>14.92</v>
+        <v>14.93</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="G4" t="n">
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>88.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="I4" t="n">
         <v>74.40000000000001</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.22</v>
+        <v>6.87</v>
       </c>
       <c r="L4" t="n">
-        <v>20.39</v>
+        <v>20</v>
       </c>
       <c r="M4" t="n">
-        <v>22.49</v>
+        <v>22.51</v>
       </c>
       <c r="N4" t="n">
         <v>-15.59</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10.12</v>
+        <v>10.2</v>
       </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="M5" t="n">
-        <v>32.05</v>
+        <v>32.04</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-4.18</v>
+        <v>-4.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="M6" t="n">
         <v>11.57</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>66.5</v>
+        <v>65.2</v>
       </c>
       <c r="I7" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.39</v>
+        <v>-5.02</v>
       </c>
       <c r="L7" t="n">
-        <v>19.69</v>
+        <v>18.91</v>
       </c>
       <c r="M7" t="n">
-        <v>39.43</v>
+        <v>39.46</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>45.9</v>
+        <v>44.8</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-0.75</v>
+        <v>-1.31</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.61</v>
+        <v>-5.15</v>
       </c>
       <c r="M8" t="n">
-        <v>18.49</v>
+        <v>18.47</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1305,7 +1305,7 @@
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="I9" t="n">
         <v>64.90000000000001</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.74</v>
+        <v>-7.77</v>
       </c>
       <c r="M9" t="n">
         <v>25.7</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.6</v>
+        <v>59.1</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>35</v>
+        <v>33.5</v>
       </c>
       <c r="I10" t="n">
         <v>62.5</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-3.75</v>
+        <v>-4.57</v>
       </c>
       <c r="L10" t="n">
-        <v>-14.96</v>
+        <v>-15.69</v>
       </c>
       <c r="M10" t="n">
-        <v>26.01</v>
+        <v>26.06</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
         <v>58.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.73</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-13.93</v>
+        <v>-14.44</v>
       </c>
       <c r="M12" t="n">
-        <v>27.88</v>
+        <v>27.87</v>
       </c>
       <c r="N12" t="n">
         <v>-28</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
         <v>22.7</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-14.53</v>
+        <v>-14.76</v>
       </c>
       <c r="L13" t="n">
-        <v>-37.32</v>
+        <v>-37.49</v>
       </c>
       <c r="M13" t="n">
         <v>45.74</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.3</v>
+        <v>89.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>10.98</v>
+        <v>11.25</v>
       </c>
       <c r="M2" t="n">
-        <v>11.38</v>
+        <v>11.39</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>94</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>88.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.380000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>23.86</v>
+        <v>20.98</v>
       </c>
       <c r="M3" t="n">
-        <v>14.93</v>
+        <v>22.52</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.7</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>88.2</v>
+        <v>90</v>
       </c>
       <c r="I4" t="n">
-        <v>74.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6.87</v>
+        <v>7.75</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>21.02</v>
       </c>
       <c r="M4" t="n">
-        <v>22.51</v>
+        <v>14.81</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>62.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-4.15</v>
+        <v>-4.84</v>
       </c>
       <c r="L6" t="n">
-        <v>1.76</v>
+        <v>20.25</v>
       </c>
       <c r="M6" t="n">
-        <v>11.57</v>
+        <v>39.46</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>65.2</v>
+        <v>60.7</v>
       </c>
       <c r="I7" t="n">
-        <v>45.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.02</v>
+        <v>-4.93</v>
       </c>
       <c r="L7" t="n">
-        <v>18.91</v>
+        <v>0.84</v>
       </c>
       <c r="M7" t="n">
-        <v>39.46</v>
+        <v>11.58</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.6</v>
+        <v>60.9</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>47.9</v>
+        <v>48.7</v>
       </c>
       <c r="I9" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.77</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>25.7</v>
+        <v>25.75</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.4</v>
+        <v>49.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>27.5</v>
       </c>
       <c r="I12" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.279999999999999</v>
+        <v>-10.03</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.44</v>
+        <v>-14.89</v>
       </c>
       <c r="M12" t="n">
-        <v>27.87</v>
+        <v>27.93</v>
       </c>
       <c r="N12" t="n">
         <v>-28</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.71</v>
       </c>
       <c r="L2" t="n">
-        <v>11.25</v>
+        <v>11.89</v>
       </c>
       <c r="M2" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>90.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="I3" t="n">
         <v>74.40000000000001</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.300000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="L3" t="n">
-        <v>20.98</v>
+        <v>22.47</v>
       </c>
       <c r="M3" t="n">
         <v>22.52</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84</v>
+        <v>84.5</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>90</v>
+        <v>91.5</v>
       </c>
       <c r="I4" t="n">
-        <v>88.8</v>
+        <v>88.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.75</v>
+        <v>7.81</v>
       </c>
       <c r="L4" t="n">
-        <v>21.02</v>
+        <v>23.01</v>
       </c>
       <c r="M4" t="n">
-        <v>14.81</v>
+        <v>14.93</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10.2</v>
+        <v>9.93</v>
       </c>
       <c r="L5" t="n">
-        <v>47.1</v>
+        <v>50.79</v>
       </c>
       <c r="M5" t="n">
-        <v>32.04</v>
+        <v>32</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>77.2</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>66.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="I6" t="n">
         <v>45.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-4.84</v>
+        <v>2.74</v>
       </c>
       <c r="L6" t="n">
-        <v>20.25</v>
+        <v>25.02</v>
       </c>
       <c r="M6" t="n">
-        <v>39.46</v>
+        <v>39.47</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>60.7</v>
+        <v>63.3</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-4.93</v>
+        <v>-2.85</v>
       </c>
       <c r="L7" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="M7" t="n">
-        <v>11.58</v>
+        <v>11.57</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63.6</v>
+        <v>62.6</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>44.8</v>
+        <v>42</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.31</v>
+        <v>-3.69</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.15</v>
+        <v>-5.14</v>
       </c>
       <c r="M8" t="n">
-        <v>18.47</v>
+        <v>18.49</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.9</v>
+        <v>61.1</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
-        <v>64.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.82</v>
+        <v>2.63</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.380000000000001</v>
+        <v>-5.9</v>
       </c>
       <c r="M9" t="n">
-        <v>25.75</v>
+        <v>25.24</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.1</v>
+        <v>59.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.5</v>
+        <v>34.3</v>
       </c>
       <c r="I10" t="n">
         <v>62.5</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.57</v>
+        <v>-5.32</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.69</v>
+        <v>-13.39</v>
       </c>
       <c r="M10" t="n">
-        <v>26.06</v>
+        <v>26.04</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.6</v>
+        <v>51.9</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>27.5</v>
+        <v>34.2</v>
       </c>
       <c r="I12" t="n">
-        <v>58.1</v>
+        <v>58.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.03</v>
+        <v>-5.43</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.89</v>
+        <v>-13.32</v>
       </c>
       <c r="M12" t="n">
-        <v>27.93</v>
+        <v>27.83</v>
       </c>
       <c r="N12" t="n">
         <v>-28</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39.7</v>
+        <v>41.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="I13" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-14.76</v>
+        <v>-13.25</v>
       </c>
       <c r="L13" t="n">
-        <v>-37.49</v>
+        <v>-33.79</v>
       </c>
       <c r="M13" t="n">
-        <v>45.74</v>
+        <v>45.63</v>
       </c>
       <c r="N13" t="n">
         <v>-42.95</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.71</v>
+        <v>4.69</v>
       </c>
       <c r="L2" t="n">
-        <v>11.89</v>
+        <v>11.87</v>
       </c>
       <c r="M2" t="n">
         <v>11.38</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>94</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>74.40000000000001</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10.23</v>
+        <v>10.44</v>
       </c>
       <c r="L3" t="n">
-        <v>22.47</v>
+        <v>22.7</v>
       </c>
       <c r="M3" t="n">
         <v>22.52</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>91.5</v>
+        <v>91.7</v>
       </c>
       <c r="I4" t="n">
         <v>88.7</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.81</v>
+        <v>7.92</v>
       </c>
       <c r="L4" t="n">
-        <v>23.01</v>
+        <v>23.14</v>
       </c>
       <c r="M4" t="n">
-        <v>14.93</v>
+        <v>14.92</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -888,21 +888,21 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.93</v>
+        <v>11.78</v>
       </c>
       <c r="L5" t="n">
-        <v>50.79</v>
+        <v>53.33</v>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>32.08</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.2</v>
+        <v>76.8</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>78.8</v>
+        <v>77.8</v>
       </c>
       <c r="I6" t="n">
         <v>45.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.74</v>
+        <v>2.27</v>
       </c>
       <c r="L6" t="n">
-        <v>25.02</v>
+        <v>24.44</v>
       </c>
       <c r="M6" t="n">
-        <v>39.47</v>
+        <v>39.46</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1095,7 +1095,7 @@
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.85</v>
+        <v>-2.79</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="M7" t="n">
         <v>11.57</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.69</v>
+        <v>-3.79</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.14</v>
+        <v>-5.23</v>
       </c>
       <c r="M8" t="n">
         <v>18.49</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.1</v>
+        <v>61.2</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="I9" t="n">
         <v>65.59999999999999</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="M9" t="n">
         <v>25.24</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.3</v>
+        <v>33.7</v>
       </c>
       <c r="I10" t="n">
         <v>62.5</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-5.32</v>
+        <v>-5.63</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.39</v>
+        <v>-13.67</v>
       </c>
       <c r="M10" t="n">
         <v>26.04</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="I12" t="n">
         <v>58.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.43</v>
+        <v>-5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>-13.32</v>
+        <v>-13.1</v>
       </c>
       <c r="M12" t="n">
-        <v>27.83</v>
+        <v>27.84</v>
       </c>
       <c r="N12" t="n">
         <v>-28</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="I13" t="n">
         <v>22.9</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-13.25</v>
+        <v>-13.45</v>
       </c>
       <c r="L13" t="n">
-        <v>-33.79</v>
+        <v>-33.94</v>
       </c>
       <c r="M13" t="n">
-        <v>45.63</v>
+        <v>45.62</v>
       </c>
       <c r="N13" t="n">
         <v>-42.95</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.69</v>
+        <v>4.87</v>
       </c>
       <c r="L2" t="n">
-        <v>11.87</v>
+        <v>12.06</v>
       </c>
       <c r="M2" t="n">
-        <v>11.38</v>
+        <v>11.39</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>94.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="I3" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10.44</v>
+        <v>10.89</v>
       </c>
       <c r="L3" t="n">
-        <v>22.7</v>
+        <v>23.21</v>
       </c>
       <c r="M3" t="n">
-        <v>22.52</v>
+        <v>22.54</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -780,7 +780,7 @@
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>91.7</v>
+        <v>91.8</v>
       </c>
       <c r="I4" t="n">
         <v>88.7</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.92</v>
+        <v>7.95</v>
       </c>
       <c r="L4" t="n">
-        <v>23.14</v>
+        <v>23.18</v>
       </c>
       <c r="M4" t="n">
         <v>14.92</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.8</v>
+        <v>77.2</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="I6" t="n">
         <v>45.3</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.27</v>
+        <v>2.71</v>
       </c>
       <c r="L6" t="n">
-        <v>24.44</v>
+        <v>24.98</v>
       </c>
       <c r="M6" t="n">
-        <v>39.46</v>
+        <v>39.47</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1095,7 +1095,7 @@
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.79</v>
+        <v>-2.82</v>
       </c>
       <c r="L7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="M7" t="n">
         <v>11.57</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>41.8</v>
+        <v>42.9</v>
       </c>
       <c r="I8" t="n">
         <v>76.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.79</v>
+        <v>-3.22</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.23</v>
+        <v>-4.67</v>
       </c>
       <c r="M8" t="n">
-        <v>18.49</v>
+        <v>18.47</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>49.2</v>
+        <v>49.5</v>
       </c>
       <c r="I9" t="n">
         <v>65.59999999999999</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.8</v>
+        <v>-5.66</v>
       </c>
       <c r="M9" t="n">
         <v>25.24</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>33.7</v>
+        <v>34.3</v>
       </c>
       <c r="I10" t="n">
         <v>62.5</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-5.63</v>
+        <v>-5.3</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.67</v>
+        <v>-13.37</v>
       </c>
       <c r="M10" t="n">
         <v>26.04</v>
@@ -1604,7 +1604,7 @@
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="I12" t="n">
         <v>58.2</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.2</v>
+        <v>-5.14</v>
       </c>
       <c r="L12" t="n">
-        <v>-13.1</v>
+        <v>-13.05</v>
       </c>
       <c r="M12" t="n">
         <v>27.84</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-13.45</v>
+        <v>-13.47</v>
       </c>
       <c r="L13" t="n">
-        <v>-33.94</v>
+        <v>-33.95</v>
       </c>
       <c r="M13" t="n">
         <v>45.62</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.87</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>12.06</v>
+        <v>10.98</v>
       </c>
       <c r="M2" t="n">
-        <v>11.39</v>
+        <v>11.4</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>95.3</v>
+        <v>94</v>
       </c>
       <c r="I3" t="n">
-        <v>74.3</v>
+        <v>88.7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10.89</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>23.21</v>
+        <v>23.86</v>
       </c>
       <c r="M3" t="n">
-        <v>22.54</v>
+        <v>14.95</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -777,13 +777,13 @@
         <v>84.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>91.8</v>
+        <v>88.2</v>
       </c>
       <c r="I4" t="n">
-        <v>88.7</v>
+        <v>74.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.95</v>
+        <v>6.87</v>
       </c>
       <c r="L4" t="n">
-        <v>23.18</v>
+        <v>20</v>
       </c>
       <c r="M4" t="n">
-        <v>14.92</v>
+        <v>22.55</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>78.7</v>
+        <v>62.2</v>
       </c>
       <c r="I6" t="n">
-        <v>45.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.71</v>
+        <v>-4.15</v>
       </c>
       <c r="L6" t="n">
-        <v>24.98</v>
+        <v>1.76</v>
       </c>
       <c r="M6" t="n">
-        <v>39.47</v>
+        <v>11.59</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.8</v>
+        <v>72.5</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>63.4</v>
+        <v>65.2</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>45.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.82</v>
+        <v>-5.02</v>
       </c>
       <c r="L7" t="n">
-        <v>1.13</v>
+        <v>18.91</v>
       </c>
       <c r="M7" t="n">
-        <v>11.57</v>
+        <v>39.53</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.3</v>
+        <v>60.7</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>49.5</v>
+        <v>47.9</v>
       </c>
       <c r="I9" t="n">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.66</v>
+        <v>-7.77</v>
       </c>
       <c r="M9" t="n">
-        <v>25.24</v>
+        <v>25.29</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>50.4</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>34.7</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
         <v>58.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.14</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-13.05</v>
+        <v>-14.44</v>
       </c>
       <c r="M12" t="n">
-        <v>27.84</v>
+        <v>27.89</v>
       </c>
       <c r="N12" t="n">
         <v>-28</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="L2" t="n">
-        <v>10.98</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>11.4</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I3" t="n">
-        <v>88.7</v>
+        <v>74.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>23.86</v>
+        <v>20.14</v>
       </c>
       <c r="M3" t="n">
-        <v>14.95</v>
+        <v>22.54</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>88.2</v>
+        <v>93.3</v>
       </c>
       <c r="I4" t="n">
-        <v>74.3</v>
+        <v>88.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6.87</v>
+        <v>7.63</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>25.88</v>
       </c>
       <c r="M4" t="n">
-        <v>22.55</v>
+        <v>14.95</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.78</v>
+        <v>12.04</v>
       </c>
       <c r="L5" t="n">
-        <v>53.33</v>
+        <v>51.99</v>
       </c>
       <c r="M5" t="n">
         <v>32.08</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>73.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>62.2</v>
+        <v>71.7</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-4.15</v>
+        <v>1.32</v>
       </c>
       <c r="L6" t="n">
-        <v>1.76</v>
+        <v>17.3</v>
       </c>
       <c r="M6" t="n">
-        <v>11.59</v>
+        <v>39.51</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.5</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>65.2</v>
+        <v>64</v>
       </c>
       <c r="I7" t="n">
-        <v>45.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.02</v>
+        <v>-3.01</v>
       </c>
       <c r="L7" t="n">
-        <v>18.91</v>
+        <v>2.31</v>
       </c>
       <c r="M7" t="n">
-        <v>39.53</v>
+        <v>11.57</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.9</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>42.9</v>
+        <v>40.3</v>
       </c>
       <c r="I8" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-3.22</v>
+        <v>-4.85</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.67</v>
+        <v>-5.57</v>
       </c>
       <c r="M8" t="n">
-        <v>18.47</v>
+        <v>18.43</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.7</v>
+        <v>61.1</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>47.9</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
-        <v>65.5</v>
+        <v>65.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="L9" t="n">
-        <v>-7.77</v>
+        <v>-6.31</v>
       </c>
       <c r="M9" t="n">
-        <v>25.29</v>
+        <v>25.17</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.4</v>
+        <v>59.9</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.3</v>
+        <v>35.9</v>
       </c>
       <c r="I10" t="n">
         <v>62.5</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-5.3</v>
+        <v>-4.41</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.37</v>
+        <v>-12.53</v>
       </c>
       <c r="M10" t="n">
         <v>26.04</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.4</v>
+        <v>51.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>33.7</v>
       </c>
       <c r="I12" t="n">
         <v>58.2</v>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.279999999999999</v>
+        <v>-4.34</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.44</v>
+        <v>-15.84</v>
       </c>
       <c r="M12" t="n">
-        <v>27.89</v>
+        <v>27.75</v>
       </c>
       <c r="N12" t="n">
-        <v>-28</v>
+        <v>-28.16</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.2</v>
+        <v>40.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>10.1</v>
+        <v>7.8</v>
       </c>
       <c r="I13" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-13.47</v>
+        <v>-14.55</v>
       </c>
       <c r="L13" t="n">
-        <v>-33.95</v>
+        <v>-35.29</v>
       </c>
       <c r="M13" t="n">
-        <v>45.62</v>
+        <v>45.68</v>
       </c>
       <c r="N13" t="n">
-        <v>-42.95</v>
+        <v>-43.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.2</v>
+        <v>77.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.77</v>
+        <v>3.32</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>10.51</v>
       </c>
       <c r="M2" t="n">
-        <v>11.4</v>
+        <v>11.44</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>92</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>74.3</v>
+        <v>88.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.890000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="L3" t="n">
-        <v>20.14</v>
+        <v>27.08</v>
       </c>
       <c r="M3" t="n">
-        <v>22.54</v>
+        <v>15.04</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>88.7</v>
+        <v>57.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.63</v>
+        <v>11.83</v>
       </c>
       <c r="L4" t="n">
-        <v>25.88</v>
+        <v>51.7</v>
       </c>
       <c r="M4" t="n">
-        <v>14.95</v>
+        <v>32.08</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.32</v>
+        <v>-20.33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,83 +879,83 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="I5" t="n">
-        <v>57.7</v>
+        <v>74.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12.04</v>
+        <v>8.77</v>
       </c>
       <c r="L5" t="n">
-        <v>51.99</v>
+        <v>18.91</v>
       </c>
       <c r="M5" t="n">
-        <v>32.08</v>
+        <v>22.63</v>
       </c>
       <c r="N5" t="n">
-        <v>-20.33</v>
+        <v>-15.59</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>71.7</v>
+        <v>65.8</v>
       </c>
       <c r="I6" t="n">
-        <v>45.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.32</v>
+        <v>-2.09</v>
       </c>
       <c r="L6" t="n">
-        <v>17.3</v>
+        <v>3.27</v>
       </c>
       <c r="M6" t="n">
-        <v>39.51</v>
+        <v>11.63</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>73.5</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>64</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>45</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-3.01</v>
+        <v>-0.47</v>
       </c>
       <c r="L7" t="n">
-        <v>2.31</v>
+        <v>15.22</v>
       </c>
       <c r="M7" t="n">
-        <v>11.57</v>
+        <v>39.7</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>62.2</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
       <c r="I8" t="n">
         <v>76.59999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.85</v>
+        <v>-4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.57</v>
+        <v>-5.42</v>
       </c>
       <c r="M8" t="n">
-        <v>18.43</v>
+        <v>18.42</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.1</v>
+        <v>60.8</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>48.2</v>
       </c>
       <c r="I9" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.31</v>
+        <v>-6.75</v>
       </c>
       <c r="M9" t="n">
-        <v>25.17</v>
+        <v>25.19</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.9</v>
+        <v>59.6</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>35.9</v>
+        <v>34.9</v>
       </c>
       <c r="I10" t="n">
         <v>62.5</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.41</v>
+        <v>-4.97</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.53</v>
+        <v>-13.05</v>
       </c>
       <c r="M10" t="n">
         <v>26.04</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.7</v>
+        <v>51.3</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>33.7</v>
+        <v>32.8</v>
       </c>
       <c r="I12" t="n">
-        <v>58.2</v>
+        <v>57.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.34</v>
+        <v>-4.84</v>
       </c>
       <c r="L12" t="n">
-        <v>-15.84</v>
+        <v>-16.28</v>
       </c>
       <c r="M12" t="n">
-        <v>27.75</v>
+        <v>27.77</v>
       </c>
       <c r="N12" t="n">
-        <v>-28.16</v>
+        <v>-28.54</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-14.55</v>
+        <v>-16.52</v>
       </c>
       <c r="L13" t="n">
-        <v>-35.29</v>
+        <v>-36.79</v>
       </c>
       <c r="M13" t="n">
-        <v>45.68</v>
+        <v>45.84</v>
       </c>
       <c r="N13" t="n">
-        <v>-43.07</v>
+        <v>-44.39</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="L2" t="n">
-        <v>10.51</v>
+        <v>10.55</v>
       </c>
       <c r="M2" t="n">
         <v>11.44</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>88.5</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.66</v>
+        <v>8.77</v>
       </c>
       <c r="L3" t="n">
-        <v>27.08</v>
+        <v>27.21</v>
       </c>
       <c r="M3" t="n">
-        <v>15.04</v>
+        <v>15.05</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.83</v>
+        <v>11.92</v>
       </c>
       <c r="L4" t="n">
-        <v>51.7</v>
+        <v>51.83</v>
       </c>
       <c r="M4" t="n">
         <v>32.08</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="G5" t="n">
         <v>86</v>
       </c>
       <c r="H5" t="n">
-        <v>81.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>74.2</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.77</v>
+        <v>8.56</v>
       </c>
       <c r="L5" t="n">
-        <v>18.91</v>
+        <v>18.69</v>
       </c>
       <c r="M5" t="n">
-        <v>22.63</v>
+        <v>22.65</v>
       </c>
       <c r="N5" t="n">
         <v>-15.59</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>65.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-2.09</v>
+        <v>-2.42</v>
       </c>
       <c r="L6" t="n">
-        <v>3.27</v>
+        <v>2.93</v>
       </c>
       <c r="M6" t="n">
-        <v>11.63</v>
+        <v>11.6</v>
       </c>
       <c r="N6" t="n">
         <v>-10.18</v>
@@ -1095,7 +1095,7 @@
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>68.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="I7" t="n">
         <v>45</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.47</v>
+        <v>-0.52</v>
       </c>
       <c r="L7" t="n">
-        <v>15.22</v>
+        <v>15.17</v>
       </c>
       <c r="M7" t="n">
         <v>39.7</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>40.6</v>
+        <v>40.9</v>
       </c>
       <c r="I8" t="n">
         <v>76.59999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.7</v>
+        <v>-4.54</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.42</v>
+        <v>-5.26</v>
       </c>
       <c r="M8" t="n">
-        <v>18.42</v>
+        <v>18.41</v>
       </c>
       <c r="N8" t="n">
         <v>-20.62</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>48.2</v>
+        <v>47.8</v>
       </c>
       <c r="I9" t="n">
         <v>65.59999999999999</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.75</v>
+        <v>-6.94</v>
       </c>
       <c r="M9" t="n">
-        <v>25.19</v>
+        <v>25.21</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1406,7 +1406,7 @@
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
         <v>62.5</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.97</v>
+        <v>-4.94</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.05</v>
+        <v>-13.02</v>
       </c>
       <c r="M10" t="n">
         <v>26.04</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>32.8</v>
+        <v>32.4</v>
       </c>
       <c r="I12" t="n">
-        <v>57.9</v>
+        <v>57.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.84</v>
+        <v>-5.08</v>
       </c>
       <c r="L12" t="n">
-        <v>-16.28</v>
+        <v>-16.49</v>
       </c>
       <c r="M12" t="n">
-        <v>27.77</v>
+        <v>27.79</v>
       </c>
       <c r="N12" t="n">
-        <v>-28.54</v>
+        <v>-28.72</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-16.52</v>
+        <v>-16.68</v>
       </c>
       <c r="L13" t="n">
-        <v>-36.79</v>
+        <v>-36.91</v>
       </c>
       <c r="M13" t="n">
-        <v>45.84</v>
+        <v>45.86</v>
       </c>
       <c r="N13" t="n">
-        <v>-44.39</v>
+        <v>-44.49</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.36</v>
+        <v>4.87</v>
       </c>
       <c r="L2" t="n">
-        <v>10.55</v>
+        <v>12.06</v>
       </c>
       <c r="M2" t="n">
-        <v>11.44</v>
+        <v>11.39</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>95.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="I3" t="n">
-        <v>88.5</v>
+        <v>74.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.77</v>
+        <v>10.89</v>
       </c>
       <c r="L3" t="n">
-        <v>27.21</v>
+        <v>23.21</v>
       </c>
       <c r="M3" t="n">
-        <v>15.05</v>
+        <v>22.53</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="I4" t="n">
-        <v>57.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.92</v>
+        <v>7.95</v>
       </c>
       <c r="L4" t="n">
-        <v>51.83</v>
+        <v>23.18</v>
       </c>
       <c r="M4" t="n">
-        <v>32.08</v>
+        <v>14.95</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.33</v>
+        <v>-10.32</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,83 +879,83 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.3</v>
+        <v>82.8</v>
       </c>
       <c r="G5" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>81.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>74.2</v>
+        <v>57.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.56</v>
+        <v>11.92</v>
       </c>
       <c r="L5" t="n">
-        <v>18.69</v>
+        <v>51.83</v>
       </c>
       <c r="M5" t="n">
-        <v>22.65</v>
+        <v>32.08</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.59</v>
+        <v>-20.33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>65.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90000000000001</v>
+        <v>45.4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-2.42</v>
+        <v>2.71</v>
       </c>
       <c r="L6" t="n">
-        <v>2.93</v>
+        <v>24.98</v>
       </c>
       <c r="M6" t="n">
-        <v>11.6</v>
+        <v>39.44</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.5</v>
+        <v>73.8</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>68</v>
+        <v>63.4</v>
       </c>
       <c r="I7" t="n">
-        <v>45</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.52</v>
+        <v>-2.82</v>
       </c>
       <c r="L7" t="n">
-        <v>15.17</v>
+        <v>1.13</v>
       </c>
       <c r="M7" t="n">
-        <v>39.7</v>
+        <v>11.59</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.7</v>
+        <v>61.3</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>47.8</v>
+        <v>49.5</v>
       </c>
       <c r="I9" t="n">
         <v>65.59999999999999</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.19</v>
+        <v>2.89</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.94</v>
+        <v>-5.66</v>
       </c>
       <c r="M9" t="n">
-        <v>25.21</v>
+        <v>25.19</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.2</v>
+        <v>52.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>32.4</v>
+        <v>34.7</v>
       </c>
       <c r="I12" t="n">
-        <v>57.8</v>
+        <v>58.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.08</v>
+        <v>-5.14</v>
       </c>
       <c r="L12" t="n">
-        <v>-16.49</v>
+        <v>-13.05</v>
       </c>
       <c r="M12" t="n">
-        <v>27.79</v>
+        <v>27.78</v>
       </c>
       <c r="N12" t="n">
-        <v>-28.72</v>
+        <v>-28</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,30 +568,30 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>90.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>80.3</v>
+        <v>69.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.87</v>
+        <v>3.97</v>
       </c>
       <c r="L2" t="n">
-        <v>12.06</v>
+        <v>9.66</v>
       </c>
       <c r="M2" t="n">
-        <v>11.39</v>
+        <v>11.44</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>95.3</v>
+        <v>92.3</v>
       </c>
       <c r="I3" t="n">
-        <v>74.3</v>
+        <v>88.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10.89</v>
+        <v>7.65</v>
       </c>
       <c r="L3" t="n">
-        <v>23.21</v>
+        <v>24.44</v>
       </c>
       <c r="M3" t="n">
-        <v>22.53</v>
+        <v>15.04</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,33 +774,33 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>91.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>88.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7.95</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>23.18</v>
+        <v>19.49</v>
       </c>
       <c r="M4" t="n">
-        <v>14.95</v>
+        <v>22.62</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.92</v>
+        <v>11.72</v>
       </c>
       <c r="L5" t="n">
-        <v>51.83</v>
+        <v>51.74</v>
       </c>
       <c r="M5" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.2</v>
+        <v>75.3</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>78.7</v>
+        <v>67.7</v>
       </c>
       <c r="I6" t="n">
-        <v>45.4</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.71</v>
+        <v>-0.24</v>
       </c>
       <c r="L6" t="n">
-        <v>24.98</v>
+        <v>2.88</v>
       </c>
       <c r="M6" t="n">
-        <v>39.44</v>
+        <v>11.65</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>63.4</v>
+        <v>70.8</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-2.82</v>
+        <v>2.99</v>
       </c>
       <c r="L7" t="n">
-        <v>1.13</v>
+        <v>13.11</v>
       </c>
       <c r="M7" t="n">
-        <v>11.59</v>
+        <v>39.66</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62.3</v>
+        <v>60.8</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>40.9</v>
+        <v>36.3</v>
       </c>
       <c r="I8" t="n">
-        <v>76.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,16 +1211,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-4.54</v>
+        <v>-7.99</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.26</v>
+        <v>-5.93</v>
       </c>
       <c r="M8" t="n">
-        <v>18.41</v>
+        <v>18.44</v>
       </c>
       <c r="N8" t="n">
-        <v>-20.62</v>
+        <v>-19.76</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.3</v>
+        <v>60.2</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>49.5</v>
+        <v>46.2</v>
       </c>
       <c r="I9" t="n">
-        <v>65.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.89</v>
+        <v>1.97</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.66</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>25.19</v>
+        <v>25.07</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.6</v>
+        <v>59.3</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I10" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-4.94</v>
+        <v>-6.02</v>
       </c>
       <c r="L10" t="n">
-        <v>-13.02</v>
+        <v>-12.51</v>
       </c>
       <c r="M10" t="n">
-        <v>26.04</v>
+        <v>25.95</v>
       </c>
       <c r="N10" t="n">
         <v>-25.51</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>52.1</v>
+        <v>51.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>34.7</v>
+        <v>32.4</v>
       </c>
       <c r="I12" t="n">
-        <v>58.3</v>
+        <v>57.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.14</v>
+        <v>-4.17</v>
       </c>
       <c r="L12" t="n">
-        <v>-13.05</v>
+        <v>-17.96</v>
       </c>
       <c r="M12" t="n">
-        <v>27.78</v>
+        <v>27.74</v>
       </c>
       <c r="N12" t="n">
-        <v>-28</v>
+        <v>-29.07</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>38.8</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>7.3</v>
       </c>
       <c r="I13" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-16.68</v>
+        <v>-14.91</v>
       </c>
       <c r="L13" t="n">
-        <v>-36.91</v>
+        <v>-35.48</v>
       </c>
       <c r="M13" t="n">
-        <v>45.86</v>
+        <v>45.75</v>
       </c>
       <c r="N13" t="n">
-        <v>-44.49</v>
+        <v>-44.64</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,27 +568,27 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>86.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>69.5</v>
+        <v>77.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.97</v>
+        <v>4.11</v>
       </c>
       <c r="L2" t="n">
-        <v>9.66</v>
+        <v>9.82</v>
       </c>
       <c r="M2" t="n">
         <v>11.44</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.8</v>
+        <v>84.3</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>92.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>88.5</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.65</v>
+        <v>7.05</v>
       </c>
       <c r="L3" t="n">
-        <v>24.44</v>
+        <v>23.74</v>
       </c>
       <c r="M3" t="n">
-        <v>15.04</v>
+        <v>15.07</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="G4" t="n">
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>83.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="I4" t="n">
         <v>74.2</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.949999999999999</v>
+        <v>11.01</v>
       </c>
       <c r="L4" t="n">
-        <v>19.49</v>
+        <v>20.64</v>
       </c>
       <c r="M4" t="n">
-        <v>22.62</v>
+        <v>22.63</v>
       </c>
       <c r="N4" t="n">
         <v>-15.59</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.7</v>
+        <v>57.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11.72</v>
+        <v>14.68</v>
       </c>
       <c r="L5" t="n">
-        <v>51.74</v>
+        <v>55.77</v>
       </c>
       <c r="M5" t="n">
-        <v>32.07</v>
+        <v>32.16</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -987,49 +987,49 @@
         <v>75.3</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>67.7</v>
+        <v>73.3</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-0.24</v>
+        <v>4.28</v>
       </c>
       <c r="L6" t="n">
-        <v>2.88</v>
+        <v>14.52</v>
       </c>
       <c r="M6" t="n">
-        <v>11.65</v>
+        <v>39.67</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>70.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>45.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.99</v>
+        <v>-0.67</v>
       </c>
       <c r="L7" t="n">
-        <v>13.11</v>
+        <v>2.43</v>
       </c>
       <c r="M7" t="n">
-        <v>39.66</v>
+        <v>11.61</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="I8" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.99</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.93</v>
+        <v>-6</v>
       </c>
       <c r="M8" t="n">
-        <v>18.44</v>
+        <v>18.45</v>
       </c>
       <c r="N8" t="n">
         <v>-19.76</v>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>46.2</v>
+        <v>45.1</v>
       </c>
       <c r="I9" t="n">
         <v>65.8</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.97</v>
+        <v>1.38</v>
       </c>
       <c r="L9" t="n">
-        <v>-8.859999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="M9" t="n">
-        <v>25.07</v>
+        <v>25.09</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-6.02</v>
+        <v>-6.04</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.51</v>
+        <v>-12.53</v>
       </c>
       <c r="M10" t="n">
         <v>25.95</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>32.4</v>
+        <v>30.9</v>
       </c>
       <c r="I12" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.17</v>
+        <v>-5</v>
       </c>
       <c r="L12" t="n">
-        <v>-17.96</v>
+        <v>-18.68</v>
       </c>
       <c r="M12" t="n">
-        <v>27.74</v>
+        <v>27.77</v>
       </c>
       <c r="N12" t="n">
-        <v>-29.07</v>
+        <v>-29.69</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="I13" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-14.91</v>
+        <v>-15.57</v>
       </c>
       <c r="L13" t="n">
-        <v>-35.48</v>
+        <v>-35.98</v>
       </c>
       <c r="M13" t="n">
-        <v>45.75</v>
+        <v>45.76</v>
       </c>
       <c r="N13" t="n">
-        <v>-44.64</v>
+        <v>-45.07</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.11</v>
+        <v>4.25</v>
       </c>
       <c r="L2" t="n">
-        <v>9.82</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>11.44</v>
+        <v>11.43</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>91.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="I3" t="n">
         <v>88.5</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.05</v>
+        <v>7.14</v>
       </c>
       <c r="L3" t="n">
-        <v>23.74</v>
+        <v>23.85</v>
       </c>
       <c r="M3" t="n">
-        <v>15.07</v>
+        <v>15.06</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="G4" t="n">
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>85.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>74.2</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.01</v>
+        <v>10.85</v>
       </c>
       <c r="L4" t="n">
-        <v>20.64</v>
+        <v>20.47</v>
       </c>
       <c r="M4" t="n">
         <v>22.63</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14.68</v>
+        <v>15.88</v>
       </c>
       <c r="L5" t="n">
-        <v>55.77</v>
+        <v>57.4</v>
       </c>
       <c r="M5" t="n">
-        <v>32.16</v>
+        <v>32.26</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>73.3</v>
+        <v>72.7</v>
       </c>
       <c r="I6" t="n">
         <v>45.1</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4.28</v>
+        <v>3.99</v>
       </c>
       <c r="L6" t="n">
-        <v>14.52</v>
+        <v>14.21</v>
       </c>
       <c r="M6" t="n">
-        <v>39.67</v>
+        <v>39.66</v>
       </c>
       <c r="N6" t="n">
         <v>-23.17</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>66.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.67</v>
+        <v>-0.47</v>
       </c>
       <c r="L7" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="M7" t="n">
-        <v>11.61</v>
+        <v>11.63</v>
       </c>
       <c r="N7" t="n">
         <v>-10.18</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-8.050000000000001</v>
+        <v>-8.08</v>
       </c>
       <c r="L8" t="n">
-        <v>-6</v>
+        <v>-6.03</v>
       </c>
       <c r="M8" t="n">
         <v>18.45</v>
@@ -1305,7 +1305,7 @@
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="I9" t="n">
         <v>65.8</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.4</v>
+        <v>-9.49</v>
       </c>
       <c r="M9" t="n">
-        <v>25.09</v>
+        <v>25.1</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G10" t="n">
         <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="I10" t="n">
         <v>62.6</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-6.04</v>
+        <v>-5.82</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.53</v>
+        <v>-12.32</v>
       </c>
       <c r="M10" t="n">
         <v>25.95</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>30.9</v>
+        <v>31.5</v>
       </c>
       <c r="I12" t="n">
-        <v>57.1</v>
+        <v>57.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5</v>
+        <v>-4.67</v>
       </c>
       <c r="L12" t="n">
-        <v>-18.68</v>
+        <v>-18.39</v>
       </c>
       <c r="M12" t="n">
-        <v>27.77</v>
+        <v>27.76</v>
       </c>
       <c r="N12" t="n">
-        <v>-29.69</v>
+        <v>-29.44</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-15.57</v>
+        <v>-15.24</v>
       </c>
       <c r="L13" t="n">
-        <v>-35.98</v>
+        <v>-35.72</v>
       </c>
       <c r="M13" t="n">
-        <v>45.76</v>
+        <v>45.75</v>
       </c>
       <c r="N13" t="n">
-        <v>-45.07</v>
+        <v>-44.85</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.25</v>
+        <v>3.36</v>
       </c>
       <c r="L2" t="n">
-        <v>9.960000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="M2" t="n">
-        <v>11.43</v>
+        <v>11.46</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>91.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>88.5</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.14</v>
+        <v>8.77</v>
       </c>
       <c r="L3" t="n">
-        <v>23.85</v>
+        <v>27.21</v>
       </c>
       <c r="M3" t="n">
-        <v>15.06</v>
+        <v>15.07</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,83 +774,83 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.7</v>
+        <v>82.7</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>85.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>74.2</v>
+        <v>57.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.85</v>
+        <v>15.88</v>
       </c>
       <c r="L4" t="n">
-        <v>20.47</v>
+        <v>57.4</v>
       </c>
       <c r="M4" t="n">
-        <v>22.63</v>
+        <v>32.26</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.59</v>
+        <v>-20.33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,83 +879,83 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>57.4</v>
+        <v>74.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15.88</v>
+        <v>8.56</v>
       </c>
       <c r="L5" t="n">
-        <v>57.4</v>
+        <v>18.69</v>
       </c>
       <c r="M5" t="n">
-        <v>32.26</v>
+        <v>22.67</v>
       </c>
       <c r="N5" t="n">
-        <v>-20.33</v>
+        <v>-15.59</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>75.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>72.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>45.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.99</v>
+        <v>-2.42</v>
       </c>
       <c r="L6" t="n">
-        <v>14.21</v>
+        <v>2.93</v>
       </c>
       <c r="M6" t="n">
-        <v>39.66</v>
+        <v>11.61</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>67.3</v>
+        <v>68</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.47</v>
+        <v>-0.52</v>
       </c>
       <c r="L7" t="n">
-        <v>2.64</v>
+        <v>15.17</v>
       </c>
       <c r="M7" t="n">
-        <v>11.63</v>
+        <v>39.74</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1285,30 +1285,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59.8</v>
+        <v>60.7</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>44.9</v>
+        <v>47.8</v>
       </c>
       <c r="I9" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.27</v>
+        <v>2.19</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.49</v>
+        <v>-6.94</v>
       </c>
       <c r="M9" t="n">
-        <v>25.1</v>
+        <v>25.11</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>31.5</v>
+        <v>32.4</v>
       </c>
       <c r="I12" t="n">
-        <v>57.3</v>
+        <v>57.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.67</v>
+        <v>-5.08</v>
       </c>
       <c r="L12" t="n">
-        <v>-18.39</v>
+        <v>-16.49</v>
       </c>
       <c r="M12" t="n">
-        <v>27.76</v>
+        <v>27.79</v>
       </c>
       <c r="N12" t="n">
-        <v>-29.44</v>
+        <v>-28.72</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.36</v>
+        <v>4.59</v>
       </c>
       <c r="L2" t="n">
-        <v>10.55</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>11.46</v>
+        <v>11.35</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>95.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="I3" t="n">
         <v>88.5</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.77</v>
+        <v>12.26</v>
       </c>
       <c r="L3" t="n">
-        <v>27.21</v>
+        <v>25.37</v>
       </c>
       <c r="M3" t="n">
-        <v>15.07</v>
+        <v>15.08</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>15.88</v>
+        <v>19.02</v>
       </c>
       <c r="L4" t="n">
-        <v>57.4</v>
+        <v>59.75</v>
       </c>
       <c r="M4" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="G5" t="n">
         <v>86</v>
       </c>
       <c r="H5" t="n">
-        <v>81.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="I5" t="n">
-        <v>74.2</v>
+        <v>74.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.56</v>
+        <v>8.75</v>
       </c>
       <c r="L5" t="n">
-        <v>18.69</v>
+        <v>18.86</v>
       </c>
       <c r="M5" t="n">
-        <v>22.67</v>
+        <v>22.44</v>
       </c>
       <c r="N5" t="n">
         <v>-15.59</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>74.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>65.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-2.42</v>
+        <v>2.51</v>
       </c>
       <c r="L6" t="n">
-        <v>2.93</v>
+        <v>2.68</v>
       </c>
       <c r="M6" t="n">
-        <v>11.61</v>
+        <v>11.6</v>
       </c>
       <c r="N6" t="n">
         <v>-10.18</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>68</v>
+        <v>66.5</v>
       </c>
       <c r="I7" t="n">
-        <v>44.9</v>
+        <v>45.4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.52</v>
+        <v>-0.76</v>
       </c>
       <c r="L7" t="n">
-        <v>15.17</v>
+        <v>13.42</v>
       </c>
       <c r="M7" t="n">
-        <v>39.74</v>
+        <v>39.45</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60.7</v>
+        <v>61.4</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>36.1</v>
+        <v>38</v>
       </c>
       <c r="I8" t="n">
         <v>77.09999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-8.08</v>
+        <v>-6.64</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.03</v>
+        <v>-5.82</v>
       </c>
       <c r="M8" t="n">
-        <v>18.45</v>
+        <v>18.48</v>
       </c>
       <c r="N8" t="n">
         <v>-19.76</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.7</v>
+        <v>61.1</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>47.8</v>
+        <v>39.2</v>
       </c>
       <c r="I9" t="n">
-        <v>65.7</v>
+        <v>62.6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2.19</v>
+        <v>-2.45</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.94</v>
+        <v>-11.21</v>
       </c>
       <c r="M9" t="n">
-        <v>25.11</v>
+        <v>25.96</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-25.51</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.4</v>
+        <v>59.9</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>34.4</v>
+        <v>45.1</v>
       </c>
       <c r="I10" t="n">
-        <v>62.6</v>
+        <v>66.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-5.82</v>
+        <v>0.45</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.32</v>
+        <v>-7.73</v>
       </c>
       <c r="M10" t="n">
-        <v>25.95</v>
+        <v>24.78</v>
       </c>
       <c r="N10" t="n">
-        <v>-25.51</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>51.2</v>
+        <v>47.4</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>32.4</v>
+        <v>22.6</v>
       </c>
       <c r="I12" t="n">
-        <v>57.8</v>
+        <v>55.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-5.08</v>
+        <v>-10.18</v>
       </c>
       <c r="L12" t="n">
-        <v>-16.49</v>
+        <v>-21.67</v>
       </c>
       <c r="M12" t="n">
-        <v>27.79</v>
+        <v>27.91</v>
       </c>
       <c r="N12" t="n">
-        <v>-28.72</v>
+        <v>-31.89</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39.7</v>
+        <v>40.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-15.24</v>
+        <v>-13.5</v>
       </c>
       <c r="L13" t="n">
-        <v>-35.72</v>
+        <v>-34.36</v>
       </c>
       <c r="M13" t="n">
-        <v>45.75</v>
+        <v>45.83</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.3</v>
+        <v>79</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.59</v>
+        <v>4.97</v>
       </c>
       <c r="L2" t="n">
-        <v>9.640000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="M2" t="n">
-        <v>11.35</v>
+        <v>11.36</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>98.5</v>
+        <v>96.7</v>
       </c>
       <c r="I3" t="n">
         <v>88.5</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.26</v>
+        <v>11.37</v>
       </c>
       <c r="L3" t="n">
-        <v>25.37</v>
+        <v>24.37</v>
       </c>
       <c r="M3" t="n">
-        <v>15.08</v>
+        <v>15.06</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.7</v>
+        <v>85.8</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="I4" t="n">
-        <v>57.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19.02</v>
+        <v>9.75</v>
       </c>
       <c r="L4" t="n">
-        <v>59.75</v>
+        <v>19.96</v>
       </c>
       <c r="M4" t="n">
-        <v>32.27</v>
+        <v>22.47</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.33</v>
+        <v>-15.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,83 +879,83 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="G5" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>81.7</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>74.5</v>
+        <v>57.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.75</v>
+        <v>20.81</v>
       </c>
       <c r="L5" t="n">
-        <v>18.86</v>
+        <v>62.15</v>
       </c>
       <c r="M5" t="n">
-        <v>22.44</v>
+        <v>32.38</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.59</v>
+        <v>-20.33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>70.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.51</v>
+        <v>2.39</v>
       </c>
       <c r="L6" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="M6" t="n">
         <v>11.6</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>66.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.76</v>
+        <v>1.32</v>
       </c>
       <c r="L7" t="n">
-        <v>13.42</v>
+        <v>15.79</v>
       </c>
       <c r="M7" t="n">
-        <v>39.45</v>
+        <v>39.51</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1175,35 +1175,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.4</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>38</v>
+        <v>41.9</v>
       </c>
       <c r="I8" t="n">
-        <v>77.09999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,35 +1211,35 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-6.64</v>
+        <v>-0.97</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.82</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>18.48</v>
+        <v>26.06</v>
       </c>
       <c r="N8" t="n">
-        <v>-19.76</v>
+        <v>-25.51</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
+          <t>ETF difesa/sicurezza UCITS</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
+          <t>LMT|RTX|BA.L</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>39.2</v>
+        <v>37.7</v>
       </c>
       <c r="I9" t="n">
-        <v>62.6</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,35 +1316,35 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-2.45</v>
+        <v>-6.8</v>
       </c>
       <c r="L9" t="n">
-        <v>-11.21</v>
+        <v>-5.98</v>
       </c>
       <c r="M9" t="n">
-        <v>25.96</v>
+        <v>18.47</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.51</v>
+        <v>-19.76</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
+          <t>ETF India UCITS / fondo Asia consumer</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>LMT|RTX|BA.L</t>
+          <t>INFY|HDB|RELIANCE.NS</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1360,22 +1360,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1390,27 +1390,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.9</v>
+        <v>60.2</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>45.1</v>
+        <v>46.1</v>
       </c>
       <c r="I10" t="n">
         <v>66.2</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.73</v>
+        <v>-7.23</v>
       </c>
       <c r="M10" t="n">
-        <v>24.78</v>
+        <v>24.79</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>22.6</v>
+        <v>24</v>
       </c>
       <c r="I12" t="n">
-        <v>55.4</v>
+        <v>55.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.18</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-21.67</v>
+        <v>-20.98</v>
       </c>
       <c r="M12" t="n">
-        <v>27.91</v>
+        <v>27.82</v>
       </c>
       <c r="N12" t="n">
-        <v>-31.89</v>
+        <v>-31.3</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40.7</v>
+        <v>41.8</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>9.699999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="I13" t="n">
         <v>21.2</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-13.5</v>
+        <v>-11.75</v>
       </c>
       <c r="L13" t="n">
-        <v>-34.36</v>
+        <v>-33.04</v>
       </c>
       <c r="M13" t="n">
-        <v>45.83</v>
+        <v>45.89</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.97</v>
+        <v>4.93</v>
       </c>
       <c r="L2" t="n">
-        <v>10.04</v>
+        <v>9.99</v>
       </c>
       <c r="M2" t="n">
         <v>11.36</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>96.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>88.5</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.37</v>
+        <v>11.22</v>
       </c>
       <c r="L3" t="n">
-        <v>24.37</v>
+        <v>24.21</v>
       </c>
       <c r="M3" t="n">
         <v>15.06</v>
@@ -780,7 +780,7 @@
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>91.7</v>
+        <v>91.5</v>
       </c>
       <c r="I4" t="n">
         <v>74.40000000000001</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.75</v>
+        <v>9.68</v>
       </c>
       <c r="L4" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="M4" t="n">
-        <v>22.47</v>
+        <v>22.46</v>
       </c>
       <c r="N4" t="n">
         <v>-15.59</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20.81</v>
+        <v>21.19</v>
       </c>
       <c r="L5" t="n">
-        <v>62.15</v>
+        <v>62.66</v>
       </c>
       <c r="M5" t="n">
-        <v>32.38</v>
+        <v>32.41</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="L6" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
         <v>11.6</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>70.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="I7" t="n">
         <v>45.3</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="L7" t="n">
-        <v>15.79</v>
+        <v>15.62</v>
       </c>
       <c r="M7" t="n">
-        <v>39.51</v>
+        <v>39.5</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="G8" t="n">
         <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="I8" t="n">
         <v>62.5</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-0.97</v>
+        <v>-1.04</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.859999999999999</v>
+        <v>-9.92</v>
       </c>
       <c r="M8" t="n">
         <v>26.06</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.3</v>
+        <v>61.1</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>37.7</v>
+        <v>37.2</v>
       </c>
       <c r="I9" t="n">
         <v>77.09999999999999</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-6.8</v>
+        <v>-7.05</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.98</v>
+        <v>-6.23</v>
       </c>
       <c r="M9" t="n">
         <v>18.47</v>
@@ -1410,7 +1410,7 @@
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="I10" t="n">
         <v>66.2</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.23</v>
+        <v>-7.27</v>
       </c>
       <c r="M10" t="n">
         <v>24.79</v>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.42</v>
       </c>
       <c r="L12" t="n">
-        <v>-20.98</v>
+        <v>-21</v>
       </c>
       <c r="M12" t="n">
         <v>27.82</v>
       </c>
       <c r="N12" t="n">
-        <v>-31.3</v>
+        <v>-31.32</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="I13" t="n">
         <v>21.2</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-11.75</v>
+        <v>-12.15</v>
       </c>
       <c r="L13" t="n">
-        <v>-33.04</v>
+        <v>-33.34</v>
       </c>
       <c r="M13" t="n">
-        <v>45.89</v>
+        <v>45.86</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.93</v>
+        <v>4.25</v>
       </c>
       <c r="L2" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>11.36</v>
+        <v>11.38</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>96.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="I3" t="n">
-        <v>88.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.22</v>
+        <v>7.14</v>
       </c>
       <c r="L3" t="n">
-        <v>24.21</v>
+        <v>23.85</v>
       </c>
       <c r="M3" t="n">
-        <v>15.06</v>
+        <v>15.09</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -774,30 +774,30 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85.8</v>
+        <v>83.7</v>
       </c>
       <c r="G4" t="n">
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>91.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.68</v>
+        <v>10.85</v>
       </c>
       <c r="L4" t="n">
-        <v>19.88</v>
+        <v>20.47</v>
       </c>
       <c r="M4" t="n">
-        <v>22.46</v>
+        <v>22.49</v>
       </c>
       <c r="N4" t="n">
         <v>-15.59</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>70.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90000000000001</v>
+        <v>45.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.37</v>
+        <v>3.99</v>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>14.21</v>
       </c>
       <c r="M6" t="n">
-        <v>11.6</v>
+        <v>39.53</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>70.3</v>
+        <v>67.3</v>
       </c>
       <c r="I7" t="n">
-        <v>45.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.17</v>
+        <v>-0.47</v>
       </c>
       <c r="L7" t="n">
-        <v>15.62</v>
+        <v>2.64</v>
       </c>
       <c r="M7" t="n">
-        <v>39.5</v>
+        <v>11.62</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1390,30 +1390,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>46</v>
+        <v>44.9</v>
       </c>
       <c r="I10" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.27</v>
+        <v>-9.49</v>
       </c>
       <c r="M10" t="n">
-        <v>24.79</v>
+        <v>24.83</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>50.8</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>31.5</v>
       </c>
       <c r="I12" t="n">
-        <v>55.9</v>
+        <v>57.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-9.42</v>
+        <v>-4.67</v>
       </c>
       <c r="L12" t="n">
-        <v>-21</v>
+        <v>-18.39</v>
       </c>
       <c r="M12" t="n">
-        <v>27.82</v>
+        <v>27.74</v>
       </c>
       <c r="N12" t="n">
-        <v>-31.32</v>
+        <v>-29.44</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.3</v>
+        <v>89.5</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.25</v>
+        <v>4.97</v>
       </c>
       <c r="L2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="M2" t="n">
-        <v>11.38</v>
+        <v>11.35</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>91.3</v>
+        <v>93.5</v>
       </c>
       <c r="I3" t="n">
-        <v>88.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.14</v>
+        <v>11.75</v>
       </c>
       <c r="L3" t="n">
-        <v>23.85</v>
+        <v>19.21</v>
       </c>
       <c r="M3" t="n">
-        <v>15.09</v>
+        <v>22.44</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,33 +774,33 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>85.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>74.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.85</v>
+        <v>11.75</v>
       </c>
       <c r="L4" t="n">
-        <v>20.47</v>
+        <v>24.26</v>
       </c>
       <c r="M4" t="n">
-        <v>22.49</v>
+        <v>15.03</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>21.19</v>
+        <v>22.04</v>
       </c>
       <c r="L5" t="n">
-        <v>62.66</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>32.41</v>
+        <v>32.34</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,52 +984,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>75.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>72.7</v>
+        <v>70.2</v>
       </c>
       <c r="I6" t="n">
-        <v>45.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.99</v>
+        <v>2.01</v>
       </c>
       <c r="L6" t="n">
-        <v>14.21</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>39.53</v>
+        <v>11.58</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>67.3</v>
+        <v>70.2</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-0.47</v>
+        <v>2.56</v>
       </c>
       <c r="L7" t="n">
-        <v>2.64</v>
+        <v>13.01</v>
       </c>
       <c r="M7" t="n">
-        <v>11.62</v>
+        <v>39.46</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="I8" t="n">
         <v>62.5</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.04</v>
+        <v>-0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.92</v>
+        <v>-11.17</v>
       </c>
       <c r="M8" t="n">
-        <v>26.06</v>
+        <v>26.01</v>
       </c>
       <c r="N8" t="n">
         <v>-25.51</v>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="I9" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.05</v>
+        <v>-7.59</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.23</v>
+        <v>-5.68</v>
       </c>
       <c r="M9" t="n">
-        <v>18.47</v>
+        <v>18.44</v>
       </c>
       <c r="N9" t="n">
         <v>-19.76</v>
@@ -1390,30 +1390,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.8</v>
+        <v>60.8</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>44.9</v>
+        <v>47.8</v>
       </c>
       <c r="I10" t="n">
-        <v>66.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.27</v>
+        <v>2.74</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.49</v>
+        <v>-7.81</v>
       </c>
       <c r="M10" t="n">
-        <v>24.83</v>
+        <v>24.74</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.8</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>31.5</v>
+        <v>24</v>
       </c>
       <c r="I12" t="n">
-        <v>57.4</v>
+        <v>56</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-4.67</v>
+        <v>-8.5</v>
       </c>
       <c r="L12" t="n">
-        <v>-18.39</v>
+        <v>-22.63</v>
       </c>
       <c r="M12" t="n">
-        <v>27.74</v>
+        <v>27.78</v>
       </c>
       <c r="N12" t="n">
-        <v>-29.44</v>
+        <v>-31.32</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="I13" t="n">
         <v>21.2</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.15</v>
+        <v>-12.02</v>
       </c>
       <c r="L13" t="n">
-        <v>-33.34</v>
+        <v>-32.85</v>
       </c>
       <c r="M13" t="n">
-        <v>45.86</v>
+        <v>45.87</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.5</v>
+        <v>89.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>78.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.97</v>
+        <v>5.31</v>
       </c>
       <c r="L2" t="n">
-        <v>9.67</v>
+        <v>10.03</v>
       </c>
       <c r="M2" t="n">
-        <v>11.35</v>
+        <v>11.37</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>93.5</v>
+        <v>95.3</v>
       </c>
       <c r="I3" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.75</v>
+        <v>12.65</v>
       </c>
       <c r="L3" t="n">
-        <v>19.21</v>
+        <v>20.17</v>
       </c>
       <c r="M3" t="n">
-        <v>22.44</v>
+        <v>22.49</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>86.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>97.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>88.5</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.75</v>
+        <v>12.24</v>
       </c>
       <c r="L4" t="n">
-        <v>24.26</v>
+        <v>24.81</v>
       </c>
       <c r="M4" t="n">
-        <v>15.03</v>
+        <v>15.04</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>22.04</v>
+        <v>23.31</v>
       </c>
       <c r="L5" t="n">
-        <v>64.06999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="M5" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="M6" t="n">
         <v>11.58</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74.3</v>
+        <v>74.8</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>70.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>45.3</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.56</v>
+        <v>3.41</v>
       </c>
       <c r="L7" t="n">
-        <v>13.01</v>
+        <v>13.95</v>
       </c>
       <c r="M7" t="n">
-        <v>39.46</v>
+        <v>39.51</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1200,7 +1200,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="I8" t="n">
         <v>62.5</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-0.5</v>
+        <v>-0.38</v>
       </c>
       <c r="L8" t="n">
-        <v>-11.17</v>
+        <v>-11.06</v>
       </c>
       <c r="M8" t="n">
         <v>26.01</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>61.4</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>36.9</v>
+        <v>49.6</v>
       </c>
       <c r="I9" t="n">
-        <v>77.2</v>
+        <v>66.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.59</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.68</v>
+        <v>-6.95</v>
       </c>
       <c r="M9" t="n">
-        <v>18.44</v>
+        <v>24.77</v>
       </c>
       <c r="N9" t="n">
-        <v>-19.76</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1381,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1404,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H10" t="n">
-        <v>47.8</v>
+        <v>36.7</v>
       </c>
       <c r="I10" t="n">
-        <v>66.3</v>
+        <v>77.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2.74</v>
+        <v>-7.68</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.81</v>
+        <v>-5.77</v>
       </c>
       <c r="M10" t="n">
-        <v>24.74</v>
+        <v>18.44</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-19.76</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="I12" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-8.5</v>
+        <v>-7.45</v>
       </c>
       <c r="L12" t="n">
-        <v>-22.63</v>
+        <v>-21.74</v>
       </c>
       <c r="M12" t="n">
-        <v>27.78</v>
+        <v>27.85</v>
       </c>
       <c r="N12" t="n">
         <v>-31.32</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41.7</v>
+        <v>43.2</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>12.6</v>
+        <v>17.2</v>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>20.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-12.02</v>
+        <v>-9.35</v>
       </c>
       <c r="L13" t="n">
-        <v>-32.85</v>
+        <v>-30.81</v>
       </c>
       <c r="M13" t="n">
-        <v>45.87</v>
+        <v>46.18</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="L2" t="n">
-        <v>10.03</v>
+        <v>10.07</v>
       </c>
       <c r="M2" t="n">
         <v>11.37</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>95.3</v>
+        <v>95.7</v>
       </c>
       <c r="I3" t="n">
         <v>74.40000000000001</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.65</v>
+        <v>12.88</v>
       </c>
       <c r="L3" t="n">
-        <v>20.17</v>
+        <v>20.41</v>
       </c>
       <c r="M3" t="n">
-        <v>22.49</v>
+        <v>22.51</v>
       </c>
       <c r="N3" t="n">
         <v>-15.59</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
       <c r="G4" t="n">
         <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>98.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="I4" t="n">
         <v>88.5</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12.24</v>
+        <v>11.94</v>
       </c>
       <c r="L4" t="n">
-        <v>24.81</v>
+        <v>24.47</v>
       </c>
       <c r="M4" t="n">
-        <v>15.04</v>
+        <v>15.03</v>
       </c>
       <c r="N4" t="n">
         <v>-10.32</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>23.31</v>
+        <v>24.7</v>
       </c>
       <c r="L5" t="n">
-        <v>65.77</v>
+        <v>67.64</v>
       </c>
       <c r="M5" t="n">
-        <v>32.35</v>
+        <v>32.41</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="L6" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="M6" t="n">
         <v>11.58</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74.8</v>
+        <v>75.2</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>71.90000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3.41</v>
+        <v>3.94</v>
       </c>
       <c r="L7" t="n">
-        <v>13.95</v>
+        <v>14.53</v>
       </c>
       <c r="M7" t="n">
-        <v>39.51</v>
+        <v>39.55</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="L8" t="n">
-        <v>-11.06</v>
+        <v>-11.05</v>
       </c>
       <c r="M8" t="n">
         <v>26.01</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.95</v>
+        <v>-6.93</v>
       </c>
       <c r="M9" t="n">
         <v>24.77</v>
@@ -1406,7 +1406,7 @@
         <v>72</v>
       </c>
       <c r="H10" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="I10" t="n">
         <v>77.2</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-7.68</v>
+        <v>-7.79</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.77</v>
+        <v>-5.89</v>
       </c>
       <c r="M10" t="n">
         <v>18.44</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="I12" t="n">
         <v>55.9</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.45</v>
+        <v>-7.33</v>
       </c>
       <c r="L12" t="n">
-        <v>-21.74</v>
+        <v>-21.64</v>
       </c>
       <c r="M12" t="n">
-        <v>27.85</v>
+        <v>27.86</v>
       </c>
       <c r="N12" t="n">
         <v>-31.32</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>17.2</v>
+        <v>16.4</v>
       </c>
       <c r="I13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.35</v>
+        <v>-9.81</v>
       </c>
       <c r="L13" t="n">
-        <v>-30.81</v>
+        <v>-31.17</v>
       </c>
       <c r="M13" t="n">
-        <v>46.18</v>
+        <v>46.11</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.5</v>
+        <v>76.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.35</v>
+        <v>3.96</v>
       </c>
       <c r="L2" t="n">
-        <v>10.07</v>
+        <v>8.59</v>
       </c>
       <c r="M2" t="n">
         <v>11.37</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87.2</v>
+        <v>86.8</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>95.7</v>
+        <v>98.2</v>
       </c>
       <c r="I3" t="n">
-        <v>74.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.88</v>
+        <v>12.82</v>
       </c>
       <c r="L3" t="n">
-        <v>20.41</v>
+        <v>24.04</v>
       </c>
       <c r="M3" t="n">
-        <v>22.51</v>
+        <v>15.02</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>86.5</v>
+        <v>85.8</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>97.5</v>
+        <v>91.5</v>
       </c>
       <c r="I4" t="n">
-        <v>88.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.94</v>
+        <v>10.53</v>
       </c>
       <c r="L4" t="n">
-        <v>24.47</v>
+        <v>18.43</v>
       </c>
       <c r="M4" t="n">
-        <v>15.03</v>
+        <v>22.49</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>24.7</v>
+        <v>23.13</v>
       </c>
       <c r="L5" t="n">
-        <v>67.64</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>32.41</v>
+        <v>32.39</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>70.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="L6" t="n">
-        <v>2.59</v>
+        <v>4.37</v>
       </c>
       <c r="M6" t="n">
-        <v>11.58</v>
+        <v>11.54</v>
       </c>
       <c r="N6" t="n">
         <v>-10.18</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I7" t="n">
         <v>45.2</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3.94</v>
+        <v>6.13</v>
       </c>
       <c r="L7" t="n">
-        <v>14.53</v>
+        <v>11.14</v>
       </c>
       <c r="M7" t="n">
-        <v>39.55</v>
+        <v>39.57</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.9</v>
+        <v>61.3</v>
       </c>
       <c r="G8" t="n">
         <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>41.8</v>
+        <v>39.9</v>
       </c>
       <c r="I8" t="n">
         <v>62.5</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-0.36</v>
+        <v>-1.32</v>
       </c>
       <c r="L8" t="n">
-        <v>-11.05</v>
+        <v>-12.15</v>
       </c>
       <c r="M8" t="n">
         <v>26.01</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.4</v>
+        <v>60.9</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>49.6</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
         <v>66.2</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.72</v>
+        <v>3.59</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.93</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>24.77</v>
+        <v>24.76</v>
       </c>
       <c r="N9" t="n">
         <v>-22.72</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.9</v>
+        <v>60.7</v>
       </c>
       <c r="G10" t="n">
         <v>72</v>
       </c>
       <c r="H10" t="n">
-        <v>36.5</v>
+        <v>36.1</v>
       </c>
       <c r="I10" t="n">
         <v>77.2</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-7.79</v>
+        <v>-7.84</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.89</v>
+        <v>-6.43</v>
       </c>
       <c r="M10" t="n">
         <v>18.44</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48.7</v>
+        <v>47.1</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>21.3</v>
       </c>
       <c r="I12" t="n">
         <v>55.9</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.33</v>
+        <v>-10.95</v>
       </c>
       <c r="L12" t="n">
-        <v>-21.64</v>
+        <v>-22.19</v>
       </c>
       <c r="M12" t="n">
-        <v>27.86</v>
+        <v>27.84</v>
       </c>
       <c r="N12" t="n">
         <v>-31.32</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>42.9</v>
+        <v>44.1</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>16.4</v>
+        <v>19.2</v>
       </c>
       <c r="I13" t="n">
-        <v>20.8</v>
+        <v>22.1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-9.81</v>
+        <v>-8.15</v>
       </c>
       <c r="L13" t="n">
-        <v>-31.17</v>
+        <v>-30.08</v>
       </c>
       <c r="M13" t="n">
-        <v>46.11</v>
+        <v>45.24</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>76.8</v>
+        <v>77</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.96</v>
+        <v>4.11</v>
       </c>
       <c r="L2" t="n">
-        <v>8.59</v>
+        <v>8.74</v>
       </c>
       <c r="M2" t="n">
         <v>11.37</v>
@@ -675,7 +675,7 @@
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>88.59999999999999</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.82</v>
+        <v>12.91</v>
       </c>
       <c r="L3" t="n">
-        <v>24.04</v>
+        <v>24.15</v>
       </c>
       <c r="M3" t="n">
         <v>15.02</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>91.5</v>
+        <v>91.8</v>
       </c>
       <c r="I4" t="n">
         <v>74.40000000000001</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.53</v>
+        <v>10.64</v>
       </c>
       <c r="L4" t="n">
-        <v>18.43</v>
+        <v>18.56</v>
       </c>
       <c r="M4" t="n">
         <v>22.49</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>23.13</v>
+        <v>21.89</v>
       </c>
       <c r="L5" t="n">
-        <v>65.01000000000001</v>
+        <v>63.34</v>
       </c>
       <c r="M5" t="n">
-        <v>32.39</v>
+        <v>32.43</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -965,35 +965,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.7</v>
+        <v>78.5</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>71.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,35 +1001,35 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.38</v>
+        <v>6.99</v>
       </c>
       <c r="L6" t="n">
-        <v>4.37</v>
+        <v>12.05</v>
       </c>
       <c r="M6" t="n">
-        <v>11.54</v>
+        <v>39.6</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75.3</v>
+        <v>76.7</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>73.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>45.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6.13</v>
+        <v>2.35</v>
       </c>
       <c r="L7" t="n">
-        <v>11.14</v>
+        <v>4.34</v>
       </c>
       <c r="M7" t="n">
-        <v>39.57</v>
+        <v>11.53</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.32</v>
+        <v>-1.31</v>
       </c>
       <c r="L8" t="n">
-        <v>-12.15</v>
+        <v>-12.13</v>
       </c>
       <c r="M8" t="n">
         <v>26.01</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.9</v>
+        <v>60.7</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>35.9</v>
       </c>
       <c r="I9" t="n">
-        <v>66.2</v>
+        <v>77.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,62 +1316,66 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.59</v>
+        <v>-7.93</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.050000000000001</v>
+        <v>-6.52</v>
       </c>
       <c r="M9" t="n">
-        <v>24.76</v>
+        <v>18.44</v>
       </c>
       <c r="N9" t="n">
-        <v>-22.72</v>
+        <v>-19.76</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1385,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1403,13 +1407,13 @@
         <v>60.7</v>
       </c>
       <c r="G10" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>36.1</v>
+        <v>47.6</v>
       </c>
       <c r="I10" t="n">
-        <v>77.2</v>
+        <v>66.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-7.84</v>
+        <v>3.37</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.43</v>
+        <v>-9.24</v>
       </c>
       <c r="M10" t="n">
-        <v>18.44</v>
+        <v>24.76</v>
       </c>
       <c r="N10" t="n">
-        <v>-19.76</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="I12" t="n">
         <v>55.9</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.95</v>
+        <v>-10.78</v>
       </c>
       <c r="L12" t="n">
-        <v>-22.19</v>
+        <v>-22.04</v>
       </c>
       <c r="M12" t="n">
-        <v>27.84</v>
+        <v>27.83</v>
       </c>
       <c r="N12" t="n">
         <v>-31.32</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44.1</v>
+        <v>44.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>19.2</v>
+        <v>19.7</v>
       </c>
       <c r="I13" t="n">
         <v>22.1</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-8.15</v>
+        <v>-7.81</v>
       </c>
       <c r="L13" t="n">
-        <v>-30.08</v>
+        <v>-29.82</v>
       </c>
       <c r="M13" t="n">
-        <v>45.24</v>
+        <v>45.25</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -574,7 +574,7 @@
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="L2" t="n">
-        <v>8.74</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>11.37</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>88.59999999999999</v>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.91</v>
+        <v>13.03</v>
       </c>
       <c r="L3" t="n">
-        <v>24.15</v>
+        <v>24.28</v>
       </c>
       <c r="M3" t="n">
         <v>15.02</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.64</v>
+        <v>10.68</v>
       </c>
       <c r="L4" t="n">
-        <v>18.56</v>
+        <v>18.59</v>
       </c>
       <c r="M4" t="n">
         <v>22.49</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>21.89</v>
+        <v>21.88</v>
       </c>
       <c r="L5" t="n">
-        <v>63.34</v>
+        <v>63.33</v>
       </c>
       <c r="M5" t="n">
         <v>32.43</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>82.8</v>
+        <v>83</v>
       </c>
       <c r="I6" t="n">
         <v>45.1</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.99</v>
+        <v>7.06</v>
       </c>
       <c r="L6" t="n">
-        <v>12.05</v>
+        <v>12.12</v>
       </c>
       <c r="M6" t="n">
         <v>39.6</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>71.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="I7" t="n">
         <v>92.90000000000001</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="L7" t="n">
-        <v>4.34</v>
+        <v>4.26</v>
       </c>
       <c r="M7" t="n">
         <v>11.53</v>
@@ -1200,7 +1200,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="I8" t="n">
         <v>62.5</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.31</v>
+        <v>-1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>-12.13</v>
+        <v>-12.09</v>
       </c>
       <c r="M8" t="n">
         <v>26.01</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>35.9</v>
+        <v>36.4</v>
       </c>
       <c r="I9" t="n">
         <v>77.2</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.93</v>
+        <v>-7.7</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.52</v>
+        <v>-6.29</v>
       </c>
       <c r="M9" t="n">
         <v>18.44</v>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="L10" t="n">
         <v>-9.24</v>
@@ -1604,7 +1604,7 @@
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="I12" t="n">
         <v>55.9</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.78</v>
+        <v>-10.72</v>
       </c>
       <c r="L12" t="n">
-        <v>-22.04</v>
+        <v>-21.98</v>
       </c>
       <c r="M12" t="n">
         <v>27.83</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>19.7</v>
+        <v>20.5</v>
       </c>
       <c r="I13" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-7.81</v>
+        <v>-7.39</v>
       </c>
       <c r="L13" t="n">
-        <v>-29.82</v>
+        <v>-29.5</v>
       </c>
       <c r="M13" t="n">
-        <v>45.25</v>
+        <v>45.27</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>89.8</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.14</v>
+        <v>5.35</v>
       </c>
       <c r="L2" t="n">
-        <v>8.779999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="M2" t="n">
-        <v>11.37</v>
+        <v>11.4</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>98.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="I3" t="n">
-        <v>88.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13.03</v>
+        <v>12.88</v>
       </c>
       <c r="L3" t="n">
-        <v>24.28</v>
+        <v>20.41</v>
       </c>
       <c r="M3" t="n">
-        <v>15.02</v>
+        <v>22.53</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>91.8</v>
+        <v>97.5</v>
       </c>
       <c r="I4" t="n">
-        <v>74.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.68</v>
+        <v>11.94</v>
       </c>
       <c r="L4" t="n">
-        <v>18.59</v>
+        <v>24.47</v>
       </c>
       <c r="M4" t="n">
-        <v>22.49</v>
+        <v>15.05</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -965,35 +965,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>78.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>83</v>
+        <v>70.2</v>
       </c>
       <c r="I6" t="n">
-        <v>45.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,35 +1001,35 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7.06</v>
+        <v>1.99</v>
       </c>
       <c r="L6" t="n">
-        <v>12.12</v>
+        <v>2.59</v>
       </c>
       <c r="M6" t="n">
-        <v>39.6</v>
+        <v>11.56</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>76.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>71.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.27</v>
+        <v>3.94</v>
       </c>
       <c r="L7" t="n">
-        <v>4.26</v>
+        <v>14.53</v>
       </c>
       <c r="M7" t="n">
-        <v>11.53</v>
+        <v>39.63</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1175,35 +1175,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.3</v>
+        <v>61.4</v>
       </c>
       <c r="G8" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>40</v>
+        <v>49.6</v>
       </c>
       <c r="I8" t="n">
-        <v>62.5</v>
+        <v>66.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,66 +1211,62 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.25</v>
+        <v>3.72</v>
       </c>
       <c r="L8" t="n">
-        <v>-12.09</v>
+        <v>-6.93</v>
       </c>
       <c r="M8" t="n">
-        <v>26.01</v>
+        <v>24.8</v>
       </c>
       <c r="N8" t="n">
-        <v>-25.51</v>
+        <v>-22.72</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1280,35 +1276,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>60.8</v>
+        <v>61.3</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>36.4</v>
+        <v>40</v>
       </c>
       <c r="I9" t="n">
-        <v>77.2</v>
+        <v>62.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,35 +1312,35 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.7</v>
+        <v>-1.25</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.29</v>
+        <v>-12.09</v>
       </c>
       <c r="M9" t="n">
-        <v>18.44</v>
+        <v>26.01</v>
       </c>
       <c r="N9" t="n">
-        <v>-19.76</v>
+        <v>-25.51</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
+          <t>ETF difesa/sicurezza UCITS</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
+          <t>LMT|RTX|BA.L</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1360,22 +1356,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1381,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1404,16 +1400,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H10" t="n">
-        <v>47.6</v>
+        <v>36.4</v>
       </c>
       <c r="I10" t="n">
-        <v>66.2</v>
+        <v>77.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,62 +1417,66 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.38</v>
+        <v>-7.7</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.24</v>
+        <v>-6.29</v>
       </c>
       <c r="M10" t="n">
-        <v>24.76</v>
+        <v>18.44</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.72</v>
+        <v>-19.76</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF India UCITS / fondo Asia consumer</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>INFY|HDB|RELIANCE.NS</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47.2</v>
+        <v>48.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>21.8</v>
+        <v>26</v>
       </c>
       <c r="I12" t="n">
         <v>55.9</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.72</v>
+        <v>-7.33</v>
       </c>
       <c r="L12" t="n">
-        <v>-21.98</v>
+        <v>-21.64</v>
       </c>
       <c r="M12" t="n">
-        <v>27.83</v>
+        <v>27.85</v>
       </c>
       <c r="N12" t="n">
         <v>-31.32</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>79.5</v>
+        <v>75.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5.35</v>
+        <v>2.61</v>
       </c>
       <c r="L2" t="n">
-        <v>10.07</v>
+        <v>8.82</v>
       </c>
       <c r="M2" t="n">
-        <v>11.4</v>
+        <v>11.37</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>74.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12.88</v>
+        <v>15.16</v>
       </c>
       <c r="L3" t="n">
-        <v>20.41</v>
+        <v>28.26</v>
       </c>
       <c r="M3" t="n">
-        <v>22.53</v>
+        <v>15.12</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.59</v>
+        <v>-10.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -704,17 +704,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF healthcare globale / fondo sanitario</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NOVO-B.CO|LLY|JNJ</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -730,22 +730,22 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>86.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>97.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>88.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.94</v>
+        <v>5.96</v>
       </c>
       <c r="L4" t="n">
-        <v>24.47</v>
+        <v>16.07</v>
       </c>
       <c r="M4" t="n">
-        <v>15.05</v>
+        <v>22.46</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.32</v>
+        <v>-15.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -809,17 +809,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -835,22 +835,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>21.88</v>
+        <v>16.36</v>
       </c>
       <c r="L5" t="n">
-        <v>63.33</v>
+        <v>54.29</v>
       </c>
       <c r="M5" t="n">
-        <v>32.43</v>
+        <v>32.42</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>70.2</v>
+        <v>74.7</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.99</v>
+        <v>3.71</v>
       </c>
       <c r="L6" t="n">
-        <v>2.59</v>
+        <v>6.1</v>
       </c>
       <c r="M6" t="n">
-        <v>11.56</v>
+        <v>11.55</v>
       </c>
       <c r="N6" t="n">
         <v>-10.18</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>72.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3.94</v>
+        <v>0.05</v>
       </c>
       <c r="L7" t="n">
-        <v>14.53</v>
+        <v>11.45</v>
       </c>
       <c r="M7" t="n">
-        <v>39.63</v>
+        <v>39.59</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1175,35 +1175,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61.4</v>
+        <v>64.2</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>49.6</v>
+        <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>66.2</v>
+        <v>62.4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,62 +1211,66 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3.72</v>
+        <v>-2.08</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.93</v>
+        <v>-9.99</v>
       </c>
       <c r="M8" t="n">
-        <v>24.8</v>
+        <v>26.09</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.72</v>
+        <v>-25.51</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1276,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.3</v>
+        <v>61.4</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
-        <v>62.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1312,35 +1316,35 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-1.25</v>
+        <v>-7.35</v>
       </c>
       <c r="L9" t="n">
-        <v>-12.09</v>
+        <v>-4.51</v>
       </c>
       <c r="M9" t="n">
-        <v>26.01</v>
+        <v>18.49</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.51</v>
+        <v>-19.76</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
+          <t>ETF India UCITS / fondo Asia consumer</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>LMT|RTX|BA.L</t>
+          <t>INFY|HDB|RELIANCE.NS</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1356,22 +1360,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1385,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.8</v>
+        <v>59.9</v>
       </c>
       <c r="G10" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>36.4</v>
+        <v>45</v>
       </c>
       <c r="I10" t="n">
-        <v>77.2</v>
+        <v>66.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1417,66 +1421,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-7.7</v>
+        <v>1.96</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.29</v>
+        <v>-10.47</v>
       </c>
       <c r="M10" t="n">
-        <v>18.44</v>
+        <v>24.75</v>
       </c>
       <c r="N10" t="n">
-        <v>-19.76</v>
+        <v>-22.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48.7</v>
+        <v>46.7</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>20.1</v>
       </c>
       <c r="I12" t="n">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-7.33</v>
+        <v>-12.41</v>
       </c>
       <c r="L12" t="n">
-        <v>-21.64</v>
+        <v>-21.46</v>
       </c>
       <c r="M12" t="n">
-        <v>27.85</v>
+        <v>27.65</v>
       </c>
       <c r="N12" t="n">
         <v>-31.32</v>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44.5</v>
+        <v>43.3</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>20.5</v>
+        <v>16.8</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-7.39</v>
+        <v>-10.15</v>
       </c>
       <c r="L13" t="n">
-        <v>-29.5</v>
+        <v>-29.99</v>
       </c>
       <c r="M13" t="n">
-        <v>45.27</v>
+        <v>45.18</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="L2" t="n">
-        <v>8.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>11.37</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>15.16</v>
+        <v>14.91</v>
       </c>
       <c r="L3" t="n">
-        <v>28.26</v>
+        <v>27.98</v>
       </c>
       <c r="M3" t="n">
-        <v>15.12</v>
+        <v>15.09</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="G4" t="n">
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="I4" t="n">
         <v>74.40000000000001</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.96</v>
+        <v>5.76</v>
       </c>
       <c r="L4" t="n">
-        <v>16.07</v>
+        <v>15.86</v>
       </c>
       <c r="M4" t="n">
-        <v>22.46</v>
+        <v>22.47</v>
       </c>
       <c r="N4" t="n">
         <v>-15.59</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>16.36</v>
+        <v>14.87</v>
       </c>
       <c r="L5" t="n">
-        <v>54.29</v>
+        <v>52.32</v>
       </c>
       <c r="M5" t="n">
-        <v>32.42</v>
+        <v>32.48</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>6.1</v>
+        <v>5.78</v>
       </c>
       <c r="M6" t="n">
-        <v>11.55</v>
+        <v>11.54</v>
       </c>
       <c r="N6" t="n">
         <v>-10.18</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>66.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="I7" t="n">
         <v>45.2</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="L7" t="n">
-        <v>11.45</v>
+        <v>11.78</v>
       </c>
       <c r="M7" t="n">
-        <v>39.59</v>
+        <v>39.58</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="G8" t="n">
         <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="I8" t="n">
         <v>62.4</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-2.08</v>
+        <v>-1.89</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.99</v>
+        <v>-9.82</v>
       </c>
       <c r="M8" t="n">
-        <v>26.09</v>
+        <v>26.1</v>
       </c>
       <c r="N8" t="n">
         <v>-25.51</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="I9" t="n">
         <v>77.09999999999999</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.35</v>
+        <v>-7.43</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.51</v>
+        <v>-4.59</v>
       </c>
       <c r="M9" t="n">
-        <v>18.49</v>
+        <v>18.48</v>
       </c>
       <c r="N9" t="n">
         <v>-19.76</v>
@@ -1410,7 +1410,7 @@
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="I10" t="n">
         <v>66.2</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="L10" t="n">
-        <v>-10.47</v>
+        <v>-10.39</v>
       </c>
       <c r="M10" t="n">
         <v>24.75</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="I12" t="n">
         <v>56.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-12.41</v>
+        <v>-12.01</v>
       </c>
       <c r="L12" t="n">
-        <v>-21.46</v>
+        <v>-21.1</v>
       </c>
       <c r="M12" t="n">
-        <v>27.65</v>
+        <v>27.66</v>
       </c>
       <c r="N12" t="n">
         <v>-31.32</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43.3</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="I13" t="n">
         <v>22.2</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.15</v>
+        <v>-10.73</v>
       </c>
       <c r="L13" t="n">
-        <v>-29.99</v>
+        <v>-30.44</v>
       </c>
       <c r="M13" t="n">
         <v>45.18</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>75.3</v>
+        <v>74.8</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="L2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="M2" t="n">
-        <v>11.37</v>
+        <v>11.38</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="I4" t="n">
         <v>74.40000000000001</v>
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.76</v>
+        <v>5.62</v>
       </c>
       <c r="L4" t="n">
-        <v>15.86</v>
+        <v>15.71</v>
       </c>
       <c r="M4" t="n">
         <v>22.47</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14.87</v>
+        <v>14.25</v>
       </c>
       <c r="L5" t="n">
-        <v>52.32</v>
+        <v>51.49</v>
       </c>
       <c r="M5" t="n">
-        <v>32.48</v>
+        <v>32.53</v>
       </c>
       <c r="N5" t="n">
         <v>-20.33</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="G6" t="n">
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>74.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>5.78</v>
+        <v>5.93</v>
       </c>
       <c r="M6" t="n">
         <v>11.54</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>73.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>66.7</v>
+        <v>66</v>
       </c>
       <c r="I7" t="n">
         <v>45.2</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>11.78</v>
+        <v>11.39</v>
       </c>
       <c r="M7" t="n">
-        <v>39.58</v>
+        <v>39.59</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>48.9</v>
+        <v>49.7</v>
       </c>
       <c r="I8" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.89</v>
+        <v>-1.45</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.82</v>
+        <v>-9.42</v>
       </c>
       <c r="M8" t="n">
-        <v>26.1</v>
+        <v>26.15</v>
       </c>
       <c r="N8" t="n">
         <v>-25.51</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>37.9</v>
+        <v>38.5</v>
       </c>
       <c r="I9" t="n">
         <v>77.09999999999999</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.43</v>
+        <v>-7.11</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.59</v>
+        <v>-4.26</v>
       </c>
       <c r="M9" t="n">
-        <v>18.48</v>
+        <v>18.51</v>
       </c>
       <c r="N9" t="n">
         <v>-19.76</v>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.9</v>
+        <v>59.6</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>45.2</v>
+        <v>44.2</v>
       </c>
       <c r="I10" t="n">
         <v>66.2</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="L10" t="n">
-        <v>-10.39</v>
+        <v>-10.86</v>
       </c>
       <c r="M10" t="n">
-        <v>24.75</v>
+        <v>24.76</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>20.8</v>
+        <v>19.8</v>
       </c>
       <c r="I12" t="n">
         <v>56.2</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-12.01</v>
+        <v>-12.54</v>
       </c>
       <c r="L12" t="n">
-        <v>-21.1</v>
+        <v>-21.57</v>
       </c>
       <c r="M12" t="n">
-        <v>27.66</v>
+        <v>27.65</v>
       </c>
       <c r="N12" t="n">
         <v>-31.32</v>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="I13" t="n">
         <v>22.2</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.73</v>
+        <v>-10.81</v>
       </c>
       <c r="L13" t="n">
-        <v>-30.44</v>
+        <v>-30.5</v>
       </c>
       <c r="M13" t="n">
         <v>45.18</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -990,7 +990,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="I6" t="n">
         <v>92.90000000000001</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="L6" t="n">
-        <v>5.93</v>
+        <v>5.87</v>
       </c>
       <c r="M6" t="n">
         <v>11.54</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88.2</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>74.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.33</v>
+        <v>4.14</v>
       </c>
       <c r="L2" t="n">
-        <v>8.52</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>11.38</v>
+        <v>11.39</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87.40000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14.91</v>
+        <v>13.03</v>
       </c>
       <c r="L3" t="n">
-        <v>27.98</v>
+        <v>24.28</v>
       </c>
       <c r="M3" t="n">
-        <v>15.09</v>
+        <v>15.04</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>83.7</v>
+        <v>91.8</v>
       </c>
       <c r="I4" t="n">
         <v>74.40000000000001</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.62</v>
+        <v>10.68</v>
       </c>
       <c r="L4" t="n">
-        <v>15.71</v>
+        <v>18.59</v>
       </c>
       <c r="M4" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="N4" t="n">
         <v>-15.59</v>
@@ -965,35 +965,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Da discutere ora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Valuta esposizione graduale con consulente</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>74.3</v>
+        <v>83</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,35 +1001,35 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3.49</v>
+        <v>7.06</v>
       </c>
       <c r="L6" t="n">
-        <v>5.87</v>
+        <v>12.12</v>
       </c>
       <c r="M6" t="n">
-        <v>11.54</v>
+        <v>39.66</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
-        <v>66</v>
+        <v>71.7</v>
       </c>
       <c r="I7" t="n">
-        <v>45.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="L7" t="n">
-        <v>11.39</v>
+        <v>4.26</v>
       </c>
       <c r="M7" t="n">
-        <v>39.59</v>
+        <v>11.56</v>
       </c>
       <c r="N7" t="n">
-        <v>-23.17</v>
+        <v>-10.18</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1390,27 +1390,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59.6</v>
+        <v>60.7</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>44.2</v>
+        <v>47.6</v>
       </c>
       <c r="I10" t="n">
         <v>66.2</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.51</v>
+        <v>3.38</v>
       </c>
       <c r="L10" t="n">
-        <v>-10.86</v>
+        <v>-9.24</v>
       </c>
       <c r="M10" t="n">
-        <v>24.76</v>
+        <v>24.79</v>
       </c>
       <c r="N10" t="n">
         <v>-22.72</v>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>46.6</v>
+        <v>47.3</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>19.8</v>
+        <v>21.8</v>
       </c>
       <c r="I12" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-12.54</v>
+        <v>-10.72</v>
       </c>
       <c r="L12" t="n">
-        <v>-21.57</v>
+        <v>-21.98</v>
       </c>
       <c r="M12" t="n">
-        <v>27.65</v>
+        <v>27.71</v>
       </c>
       <c r="N12" t="n">
         <v>-31.32</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>77.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="I2" t="n">
         <v>95.40000000000001</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4.14</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>8.779999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="M2" t="n">
-        <v>11.39</v>
+        <v>11.43</v>
       </c>
       <c r="N2" t="n">
         <v>-6.55</v>
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="G3" t="n">
         <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>88.5</v>
+        <v>88.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13.03</v>
+        <v>16.77</v>
       </c>
       <c r="L3" t="n">
-        <v>24.28</v>
+        <v>31.8</v>
       </c>
       <c r="M3" t="n">
-        <v>15.04</v>
+        <v>15.25</v>
       </c>
       <c r="N3" t="n">
         <v>-10.32</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>91.8</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>74.40000000000001</v>
+        <v>57</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10.68</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>18.59</v>
+        <v>51.36</v>
       </c>
       <c r="M4" t="n">
-        <v>22.5</v>
+        <v>32.56</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.59</v>
+        <v>-20.33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>82.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>57</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14.25</v>
+        <v>5.47</v>
       </c>
       <c r="L5" t="n">
-        <v>51.49</v>
+        <v>6.84</v>
       </c>
       <c r="M5" t="n">
-        <v>32.53</v>
+        <v>11.57</v>
       </c>
       <c r="N5" t="n">
-        <v>-20.33</v>
+        <v>-10.18</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -965,82 +965,82 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Da discutere ora</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Valuta esposizione graduale con consulente</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Settore interessante: usare ETF/fondo come default, azione singola solo per piccola quota satellite.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>78.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H6" t="n">
-        <v>83</v>
+        <v>67.8</v>
       </c>
       <c r="I6" t="n">
-        <v>45.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7.06</v>
+        <v>1.63</v>
       </c>
       <c r="L6" t="n">
-        <v>12.12</v>
+        <v>11.26</v>
       </c>
       <c r="M6" t="n">
-        <v>39.66</v>
+        <v>22.7</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.17</v>
+        <v>-15.59</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ETF settoriale o basket azioni</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>VVSM.DE</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NVDA|ASML.AS|AMD|STM.MI</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ciclicita e drawdown elevati</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>76.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>71.7</v>
+        <v>52</v>
       </c>
       <c r="I7" t="n">
-        <v>92.90000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.27</v>
+        <v>-5.94</v>
       </c>
       <c r="L7" t="n">
-        <v>4.26</v>
+        <v>1.57</v>
       </c>
       <c r="M7" t="n">
-        <v>11.56</v>
+        <v>40.12</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.18</v>
+        <v>-23.17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF settoriale o basket azioni</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>VVSM.DE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF semiconduttori UCITS / VanEck Semiconductor UCITS</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>NVDA|ASML.AS|AMD|STM.MI</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Fattore abilitante per AI data center auto elettrica e industria</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Ciclicita e drawdown elevati</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>Preferire size piccola o ETF; azioni singole solo se consapevoli del rischio</t>
         </is>
       </c>
     </row>
@@ -1175,35 +1175,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>India e Asia Consumer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="G8" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>49.7</v>
+        <v>36.4</v>
       </c>
       <c r="I8" t="n">
-        <v>62.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1211,35 +1211,35 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-1.45</v>
+        <v>-7.69</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.42</v>
+        <v>-6.25</v>
       </c>
       <c r="M8" t="n">
-        <v>26.15</v>
+        <v>18.5</v>
       </c>
       <c r="N8" t="n">
-        <v>-25.51</v>
+        <v>-19.76</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETF/Fondo paese</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
+          <t>ETF India UCITS / fondo Asia consumer</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>LMT|RTX|BA.L</t>
+          <t>INFY|HDB|RELIANCE.NS</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Valutazioni e rischio valuta/paese</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Da confrontare con esposizione emergenti gia presente in core</t>
         </is>
       </c>
     </row>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India e Asia Consumer</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61.5</v>
+        <v>58.8</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>38.5</v>
+        <v>32.7</v>
       </c>
       <c r="I9" t="n">
-        <v>77.09999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,35 +1316,35 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-7.11</v>
+        <v>-8.24</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.26</v>
+        <v>-10.53</v>
       </c>
       <c r="M9" t="n">
-        <v>18.51</v>
+        <v>26.18</v>
       </c>
       <c r="N9" t="n">
-        <v>-19.76</v>
+        <v>-25.51</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo paese</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NDIA.L</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF India UCITS / fondo Asia consumer</t>
+          <t>ETF difesa/sicurezza UCITS</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>INFY|HDB|RELIANCE.NS</t>
+          <t>LMT|RTX|BA.L</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1360,22 +1360,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Crescita demografica consumi digitalizzazione e manifattura</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Valutazioni e rischio valuta/paese</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da confrontare con esposizione emergenti gia presente in core</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1385,98 +1385,90 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Obbligazionario Globale</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>60.7</v>
+        <v>57.7</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H10" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>66.2</v>
+        <v>50</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-9.24</v>
-      </c>
-      <c r="M10" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-22.72</v>
-      </c>
+          <t>Dati limitati</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF obbligazionario</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>EUNA.MI</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+          <t>ETF global aggregate bond hedged/unhedged</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>9-35%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>Lungo periodo</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio tassi cambio e duration</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da allineare a orizzonte e consulenza Fineco</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1478,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Obbligazionario Globale</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1505,71 +1497,79 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>57.7</v>
+        <v>56.8</v>
       </c>
       <c r="G11" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dati limitati</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Debole o laterale</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-12.19</v>
+      </c>
+      <c r="M11" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-22.72</v>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>ETF obbligazionario</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>EUNA.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ETF global aggregate bond hedged/unhedged</t>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>10</v>
       </c>
-      <c r="T11" t="n">
-        <v>35</v>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>9-35%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Lungo periodo</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Rischio tassi cambio e duration</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Da allineare a orizzonte e consulenza Fineco</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47.3</v>
+        <v>46.2</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>21.8</v>
+        <v>18.8</v>
       </c>
       <c r="I12" t="n">
-        <v>56.1</v>
+        <v>55.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.72</v>
+        <v>-12.79</v>
       </c>
       <c r="L12" t="n">
-        <v>-21.98</v>
+        <v>-22.65</v>
       </c>
       <c r="M12" t="n">
-        <v>27.71</v>
+        <v>27.68</v>
       </c>
       <c r="N12" t="n">
-        <v>-31.32</v>
+        <v>-31.86</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>42.9</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>15.7</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>22.2</v>
+        <v>21.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-10.81</v>
+        <v>-17.4</v>
       </c>
       <c r="L13" t="n">
-        <v>-30.5</v>
+        <v>-35.24</v>
       </c>
       <c r="M13" t="n">
-        <v>45.18</v>
+        <v>45.5</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Core Globale</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -571,13 +571,13 @@
         <v>87.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H2" t="n">
-        <v>72.3</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>95.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -585,62 +585,66 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>15.72</v>
       </c>
       <c r="L2" t="n">
-        <v>7.32</v>
+        <v>30.62</v>
       </c>
       <c r="M2" t="n">
-        <v>11.43</v>
+        <v>15.15</v>
       </c>
       <c r="N2" t="n">
-        <v>-6.55</v>
+        <v>-10.32</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ETF UCITS globale</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+          <t>ETF healthcare globale / fondo sanitario</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>NOVO-B.CO|LLY|JNJ</t>
+        </is>
+      </c>
       <c r="S2" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Lungo periodo</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Base del portafoglio gia diversificata su mercati sviluppati ed emergenti</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Sovrappeso USA e mega cap se gia molto presente</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Usarlo come base; evitare di duplicare troppo con altri globali simili</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -650,7 +654,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Core Globale</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,83 +673,79 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87.3</v>
+        <v>84.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>63.2</v>
       </c>
       <c r="I3" t="n">
-        <v>88.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sopra media 50/200</t>
+          <t>Debole o laterale</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>16.77</v>
+        <v>0.43</v>
       </c>
       <c r="L3" t="n">
-        <v>31.8</v>
+        <v>6.72</v>
       </c>
       <c r="M3" t="n">
-        <v>15.25</v>
+        <v>11.49</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.32</v>
+        <v>-6.55</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF UCITS globale</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
-        </is>
-      </c>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="T3" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Lungo periodo</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Base del portafoglio gia diversificata su mercati sviluppati ed emergenti</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Sovrappeso USA e mega cap se gia molto presente</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Usarlo come base; evitare di duplicare troppo con altri globali simili</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
@@ -783,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8.960000000000001</v>
+        <v>6.29</v>
       </c>
       <c r="L4" t="n">
-        <v>51.36</v>
+        <v>47.65</v>
       </c>
       <c r="M4" t="n">
-        <v>32.56</v>
+        <v>32.77</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>77.7</v>
+        <v>76.8</v>
       </c>
       <c r="G6" t="n">
         <v>86</v>
       </c>
       <c r="H6" t="n">
-        <v>67.8</v>
+        <v>65.5</v>
       </c>
       <c r="I6" t="n">
-        <v>74.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.63</v>
+        <v>0.43</v>
       </c>
       <c r="L6" t="n">
-        <v>11.26</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>22.7</v>
+        <v>22.89</v>
       </c>
       <c r="N6" t="n">
         <v>-15.59</v>
@@ -1075,30 +1075,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monitorare</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Confronta ETF/fondo e costi</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>52</v>
+        <v>48.3</v>
       </c>
       <c r="I7" t="n">
-        <v>44.4</v>
+        <v>43.9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-5.94</v>
+        <v>-7.83</v>
       </c>
       <c r="L7" t="n">
-        <v>1.57</v>
+        <v>-0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>40.12</v>
+        <v>40.47</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60.8</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="I8" t="n">
         <v>77.09999999999999</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.69</v>
+        <v>-7.37</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.25</v>
+        <v>-5.92</v>
       </c>
       <c r="M8" t="n">
-        <v>18.5</v>
+        <v>18.51</v>
       </c>
       <c r="N8" t="n">
         <v>-19.76</v>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
       </c>
       <c r="H9" t="n">
-        <v>32.7</v>
+        <v>32.4</v>
       </c>
       <c r="I9" t="n">
         <v>62.3</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-8.24</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.53</v>
+        <v>-10.73</v>
       </c>
       <c r="M9" t="n">
-        <v>26.18</v>
+        <v>26.2</v>
       </c>
       <c r="N9" t="n">
         <v>-25.51</v>
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>56.8</v>
+        <v>56.2</v>
       </c>
       <c r="G11" t="n">
         <v>68</v>
       </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="I11" t="n">
-        <v>66.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-4.57</v>
+        <v>-5.35</v>
       </c>
       <c r="L11" t="n">
-        <v>-12.19</v>
+        <v>-12.9</v>
       </c>
       <c r="M11" t="n">
-        <v>24.84</v>
+        <v>24.93</v>
       </c>
       <c r="N11" t="n">
-        <v>-22.72</v>
+        <v>-23.11</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>46.2</v>
+        <v>45.5</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>18.8</v>
+        <v>17.2</v>
       </c>
       <c r="I12" t="n">
-        <v>55.7</v>
+        <v>55.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-12.79</v>
+        <v>-13.67</v>
       </c>
       <c r="L12" t="n">
-        <v>-22.65</v>
+        <v>-23.44</v>
       </c>
       <c r="M12" t="n">
-        <v>27.68</v>
+        <v>27.77</v>
       </c>
       <c r="N12" t="n">
-        <v>-31.86</v>
+        <v>-32.55</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-17.4</v>
+        <v>-18</v>
       </c>
       <c r="L13" t="n">
-        <v>-35.24</v>
+        <v>-35.7</v>
       </c>
       <c r="M13" t="n">
-        <v>45.5</v>
+        <v>45.59</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>15.72</v>
+        <v>15.78</v>
       </c>
       <c r="L2" t="n">
-        <v>30.62</v>
+        <v>30.68</v>
       </c>
       <c r="M2" t="n">
         <v>15.15</v>
@@ -679,7 +679,7 @@
         <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>63.2</v>
+        <v>63.4</v>
       </c>
       <c r="I3" t="n">
         <v>95.40000000000001</v>
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="L3" t="n">
-        <v>6.72</v>
+        <v>6.8</v>
       </c>
       <c r="M3" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
       <c r="N3" t="n">
         <v>-6.55</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6.29</v>
+        <v>6.33</v>
       </c>
       <c r="L4" t="n">
-        <v>47.65</v>
+        <v>47.71</v>
       </c>
       <c r="M4" t="n">
-        <v>32.77</v>
+        <v>32.76</v>
       </c>
       <c r="N4" t="n">
         <v>-20.33</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="G5" t="n">
         <v>74</v>
       </c>
       <c r="H5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I5" t="n">
         <v>92.90000000000001</v>
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.47</v>
+        <v>5.64</v>
       </c>
       <c r="L5" t="n">
-        <v>6.84</v>
+        <v>7.01</v>
       </c>
       <c r="M5" t="n">
-        <v>11.57</v>
+        <v>11.58</v>
       </c>
       <c r="N5" t="n">
         <v>-10.18</v>
@@ -990,7 +990,7 @@
         <v>86</v>
       </c>
       <c r="H6" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>73.8</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="L6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="M6" t="n">
         <v>22.89</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="I7" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.83</v>
+        <v>-7.66</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.47</v>
+        <v>-0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>40.47</v>
+        <v>40.44</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="I8" t="n">
         <v>77.09999999999999</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-7.37</v>
+        <v>-7.21</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.92</v>
+        <v>-5.75</v>
       </c>
       <c r="M8" t="n">
         <v>18.51</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.42</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.73</v>
+        <v>-10.7</v>
       </c>
       <c r="M9" t="n">
         <v>26.2</v>
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="G11" t="n">
         <v>68</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
       <c r="I11" t="n">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-5.35</v>
+        <v>-5.23</v>
       </c>
       <c r="L11" t="n">
-        <v>-12.9</v>
+        <v>-12.79</v>
       </c>
       <c r="M11" t="n">
-        <v>24.93</v>
+        <v>24.91</v>
       </c>
       <c r="N11" t="n">
-        <v>-23.11</v>
+        <v>-23.02</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="I12" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-13.67</v>
+        <v>-13.59</v>
       </c>
       <c r="L12" t="n">
-        <v>-23.44</v>
+        <v>-23.37</v>
       </c>
       <c r="M12" t="n">
-        <v>27.77</v>
+        <v>27.76</v>
       </c>
       <c r="N12" t="n">
-        <v>-32.55</v>
+        <v>-32.49</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-18</v>
+        <v>-18.2</v>
       </c>
       <c r="L13" t="n">
-        <v>-35.7</v>
+        <v>-35.86</v>
       </c>
       <c r="M13" t="n">
-        <v>45.59</v>
+        <v>45.62</v>
       </c>
       <c r="N13" t="n">
         <v>-44.85</v>

--- a/AlphaForge_Sector_Compass.xlsx
+++ b/AlphaForge_Sector_Compass.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Core Globale</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -568,16 +568,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>87.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>74.8</v>
       </c>
       <c r="I2" t="n">
-        <v>88.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -585,66 +585,62 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>15.78</v>
+        <v>2.33</v>
       </c>
       <c r="L2" t="n">
-        <v>30.68</v>
+        <v>8.52</v>
       </c>
       <c r="M2" t="n">
-        <v>15.15</v>
+        <v>11.4</v>
       </c>
       <c r="N2" t="n">
-        <v>-10.32</v>
+        <v>-6.55</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF UCITS globale</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>XDWH.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>ETF healthcare globale / fondo sanitario</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>NOVO-B.CO|LLY|JNJ</t>
-        </is>
-      </c>
+          <t>Vanguard FTSE All-World UCITS ETF</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="T2" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>Lungo periodo</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
+          <t>Base del portafoglio gia diversificata su mercati sviluppati ed emergenti</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Rischio regolatorio e concentrazione pharma</t>
+          <t>Sovrappeso USA e mega cap se gia molto presente</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
+          <t>Usarlo come base; evitare di duplicare troppo con altri globali simili</t>
         </is>
       </c>
     </row>
@@ -654,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Core Globale</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -673,79 +669,83 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
-        <v>63.4</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>95.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.51</v>
+        <v>14.91</v>
       </c>
       <c r="L3" t="n">
-        <v>6.8</v>
+        <v>27.98</v>
       </c>
       <c r="M3" t="n">
-        <v>11.48</v>
+        <v>15.12</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.55</v>
+        <v>-10.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ETF UCITS globale</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>XDWH.DE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+          <t>ETF healthcare globale / fondo sanitario</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>NOVO-B.CO|LLY|JNJ</t>
+        </is>
+      </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Lungo periodo</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Base del portafoglio gia diversificata su mercati sviluppati ed emergenti</t>
+          <t>Domanda strutturale demografia farmaci innovazione e qualita difensiva</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Sovrappeso USA e mega cap se gia molto presente</t>
+          <t>Rischio regolatorio e concentrazione pharma</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Usarlo come base; evitare di duplicare troppo con altri globali simili</t>
+          <t>Adatto come satellite difensivo rispetto a tecnologia</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Tecnologia e AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>83.7</v>
       </c>
       <c r="I4" t="n">
-        <v>56.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -791,66 +791,66 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6.33</v>
+        <v>5.62</v>
       </c>
       <c r="L4" t="n">
-        <v>47.71</v>
+        <v>15.71</v>
       </c>
       <c r="M4" t="n">
-        <v>32.76</v>
+        <v>22.52</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.33</v>
+        <v>-15.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ETF tematico</t>
+          <t>ETF/Fondo settoriale</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ISPY.L</t>
+          <t>XDWT.DE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ETF cybersecurity UCITS</t>
+          <t>ETF tecnologia globale / MSCI World Information Technology</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CRWD|PANW|FTNT</t>
+          <t>MSFT|AAPL|GOOGL</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>4-15%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>3-7 anni</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
+          <t>Trend strutturale su software cloud semiconduttori e AI</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Rischio valutazioni e temi gia affollati</t>
+          <t>Valutazioni elevate e concentrazione USA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
+          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>78.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>77.7</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>92.90000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -896,66 +896,66 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.64</v>
+        <v>6.33</v>
       </c>
       <c r="L5" t="n">
-        <v>7.01</v>
+        <v>47.71</v>
       </c>
       <c r="M5" t="n">
-        <v>11.58</v>
+        <v>32.76</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.18</v>
+        <v>-20.33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ETF/Fondo settoriale</t>
+          <t>ETF tematico</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>INFR.MI</t>
+          <t>ISPY.L</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ETF infrastrutture globali / fondo infrastrutture</t>
+          <t>ETF cybersecurity UCITS</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>NEE|ENEL.MI|IBE.MC</t>
+          <t>CRWD|PANW|FTNT</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5+ anni</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Elettrificazione reti data center e investimenti pubblici</t>
+          <t>Spesa IT difensiva legata a sicurezza dati e infrastrutture</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Sensibilita tassi e regolazione</t>
+          <t>Rischio valutazioni e temi gia affollati</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Interessante per stabilizzare portafoglio se poco presente</t>
+          <t>ETF tematico da verificare con consulente per costi e liquidita</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -984,33 +984,33 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76.8</v>
+        <v>77.5</v>
       </c>
       <c r="G6" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>65.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="I6" t="n">
-        <v>73.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
+          <t>Sopra media 50/200</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.38</v>
+        <v>3.49</v>
       </c>
       <c r="L6" t="n">
-        <v>9.9</v>
+        <v>5.87</v>
       </c>
       <c r="M6" t="n">
-        <v>22.89</v>
+        <v>11.56</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.59</v>
+        <v>-10.18</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1019,48 +1019,48 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>XDWT.DE</t>
+          <t>INFR.MI</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ETF tecnologia globale / MSCI World Information Technology</t>
+          <t>ETF infrastrutture globali / fondo infrastrutture</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>MSFT|AAPL|GOOGL</t>
+          <t>NEE|ENEL.MI|IBE.MC</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4-15%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3-7 anni</t>
+          <t>5+ anni</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Trend strutturale su software cloud semiconduttori e AI</t>
+          <t>Elettrificazione reti data center e investimenti pubblici</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Valutazioni elevate e concentrazione USA</t>
+          <t>Sensibilita tassi e regolazione</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Verificare su Fineco ETF UCITS o fondo tecnologia disponibile</t>
+          <t>Interessante per stabilizzare portafoglio se poco presente</t>
         </is>
       </c>
     </row>
@@ -1075,30 +1075,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Monitorare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Confronta ETF/fondo e costi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Potrebbe avere senso come satellite, ma non e' una priorita urgente.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.7</v>
+        <v>72.8</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>48.6</v>
+        <v>66</v>
       </c>
       <c r="I7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-7.66</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.29</v>
+        <v>11.39</v>
       </c>
       <c r="M7" t="n">
-        <v>40.44</v>
+        <v>39.67</v>
       </c>
       <c r="N7" t="n">
         <v>-23.17</v>
@@ -1280,35 +1280,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Difesa e sicurezza</t>
+          <t>Oro e Protezione</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Watchlist strategica</t>
+          <t>Bassa priorita</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aspetta conferma o PAC piccolo</t>
+          <t>Evita o rimanda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
+          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>58.7</v>
+        <v>59.6</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>32.4</v>
+        <v>44.2</v>
       </c>
       <c r="I9" t="n">
-        <v>62.3</v>
+        <v>66.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1316,66 +1316,62 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-8.42</v>
+        <v>1.51</v>
       </c>
       <c r="L9" t="n">
-        <v>-10.7</v>
+        <v>-10.86</v>
       </c>
       <c r="M9" t="n">
-        <v>26.2</v>
+        <v>24.79</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.51</v>
+        <v>-22.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ETF/Fondo tematico</t>
+          <t>ETC/ETF oro</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DFNS.L</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ETF difesa/sicurezza UCITS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>LMT|RTX|BA.L</t>
-        </is>
-      </c>
+          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1-8%</t>
+          <t>2-10%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3-5 anni</t>
+          <t>Ciclo e protezione</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
+          <t>Serve come diversificante in shock o inflazione non come crescita</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Rischio politico etico e concentrazione</t>
+          <t>Puo non produrre rendimento reale in fasi risk-on</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Da discutere con consulente per coerenza personale/ESG</t>
+          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
         </is>
       </c>
     </row>
@@ -1385,90 +1381,102 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Obbligazionario Globale</t>
+          <t>Difesa e sicurezza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bassa priorita</t>
+          <t>Watchlist strategica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evita o rimanda</t>
+          <t>Aspetta conferma o PAC piccolo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Non aggiungere complessita se il portafoglio core e' gia sufficiente.</t>
+          <t>Trend non ancora forte: utile monitorarlo ma senza inseguire.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57.7</v>
+        <v>58.7</v>
       </c>
       <c r="G10" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>32.4</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>62.3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dati limitati</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Debole o laterale</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-8.42</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-25.51</v>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ETF obbligazionario</t>
+          <t>ETF/Fondo tematico</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>EUNA.MI</t>
+          <t>DFNS.L</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ETF global aggregate bond hedged/unhedged</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>ETF difesa/sicurezza UCITS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LMT|RTX|BA.L</t>
+        </is>
+      </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>9-35%</t>
+          <t>1-8%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Lungo periodo</t>
+          <t>3-5 anni</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
+          <t>Spesa pubblica e sicurezza geopolitica come trend pluriennale</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Rischio tassi cambio e duration</t>
+          <t>Rischio politico etico e concentrazione</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Da allineare a orizzonte e consulenza Fineco</t>
+          <t>Da discutere con consulente per coerenza personale/ESG</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1486,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Oro e Protezione</t>
+          <t>Obbligazionario Globale</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1497,79 +1505,71 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>56.3</v>
+        <v>57.7</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H11" t="n">
-        <v>34.8</v>
+        <v>50</v>
       </c>
       <c r="I11" t="n">
-        <v>65.8</v>
+        <v>50</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Debole o laterale</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>-5.23</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-12.79</v>
-      </c>
-      <c r="M11" t="n">
-        <v>24.91</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-23.02</v>
-      </c>
+          <t>Dati limitati</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>ETC/ETF oro</t>
+          <t>ETF obbligazionario</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>EUNA.MI</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ETC oro fisico / fondo multi-asset difensivo</t>
+          <t>ETF global aggregate bond hedged/unhedged</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2-10%</t>
+          <t>9-35%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Ciclo e protezione</t>
+          <t>Lungo periodo</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Serve come diversificante in shock o inflazione non come crescita</t>
+          <t>Riduce volatilita complessiva se calibrato su durata e valuta</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Puo non produrre rendimento reale in fasi risk-on</t>
+          <t>Rischio tassi cambio e duration</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Valutare con consulente per ruolo difensivo e fiscalita</t>
+          <t>Da allineare a orizzonte e consulenza Fineco</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>45.6</v>
+        <v>46.6</v>
       </c>
       <c r="G12" t="n">
         <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>17.3</v>
+        <v>19.8</v>
       </c>
       <c r="I12" t="n">
-        <v>55.2</v>
+        <v>56.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-13.59</v>
+        <v>-12.54</v>
       </c>
       <c r="L12" t="n">
-        <v>-23.37</v>
+        <v>-21.57</v>
       </c>
       <c r="M12" t="n">
-        <v>27.76</v>
+        <v>27.68</v>
       </c>
       <c r="N12" t="n">
-        <v>-32.49</v>
+        <v>-31.32</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
